--- a/Assets/Resources/Excel/Entity_ContestCommentDataBase.xlsx
+++ b/Assets/Resources/Excel/Entity_ContestCommentDataBase.xlsx
@@ -1,21 +1,22 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="27328"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="28526"/>
   <workbookPr defaultThemeVersion="166925"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\aritashogo\Documents\Unity\Okashi_Atlier2\Assets\Excel_Data\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\aritashogo\Documents\Unity\Okashi_Atlier2\Assets\Resources\Excel\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{64C6281E-8BEC-4894-A18C-A4BCC899AFD0}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{FE68621D-2C55-4991-ACF4-21B6AF3DB205}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="780" yWindow="780" windowWidth="23310" windowHeight="12720" activeTab="2" xr2:uid="{1DCE2773-8A3B-4011-B3F4-E2EABC03DB8B}"/>
+    <workbookView xWindow="2025" yWindow="900" windowWidth="25560" windowHeight="14325" firstSheet="1" activeTab="2" xr2:uid="{1DCE2773-8A3B-4011-B3F4-E2EABC03DB8B}"/>
   </bookViews>
   <sheets>
     <sheet name="01_ContestComment" sheetId="1" r:id="rId1"/>
     <sheet name="02_ConComment_D01" sheetId="2" r:id="rId2"/>
     <sheet name="02_ConComment_D100" sheetId="3" r:id="rId3"/>
+    <sheet name="02_ConComment_SPScore" sheetId="4" r:id="rId4"/>
   </sheets>
   <calcPr calcId="191029" concurrentCalc="0"/>
   <extLst>
@@ -35,7 +36,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="701" uniqueCount="200">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="891" uniqueCount="336">
   <si>
     <t>item_Name</t>
     <phoneticPr fontId="3"/>
@@ -2301,6 +2302,1684 @@
   </si>
   <si>
     <t>search_endflag</t>
+    <phoneticPr fontId="2"/>
+  </si>
+  <si>
+    <t>見た目的には子供っぽくは見えませんね..。</t>
+    <rPh sb="0" eb="1">
+      <t>ミ</t>
+    </rPh>
+    <rPh sb="2" eb="3">
+      <t>メ</t>
+    </rPh>
+    <rPh sb="3" eb="4">
+      <t>テキ</t>
+    </rPh>
+    <rPh sb="6" eb="8">
+      <t>コドモ</t>
+    </rPh>
+    <rPh sb="12" eb="13">
+      <t>ミ</t>
+    </rPh>
+    <phoneticPr fontId="2"/>
+  </si>
+  <si>
+    <t>もう少し子供たちが喜ぶ見た目にしないと..。</t>
+    <rPh sb="4" eb="6">
+      <t>コドモ</t>
+    </rPh>
+    <rPh sb="9" eb="10">
+      <t>ヨロコ</t>
+    </rPh>
+    <rPh sb="11" eb="12">
+      <t>ミ</t>
+    </rPh>
+    <rPh sb="13" eb="14">
+      <t>メ</t>
+    </rPh>
+    <phoneticPr fontId="2"/>
+  </si>
+  <si>
+    <t>まだまだ修行が必要ですわね！</t>
+    <rPh sb="4" eb="6">
+      <t>シュギョウ</t>
+    </rPh>
+    <rPh sb="7" eb="9">
+      <t>ヒツヨウ</t>
+    </rPh>
+    <phoneticPr fontId="2"/>
+  </si>
+  <si>
+    <t>SPScore_Kanso</t>
+    <phoneticPr fontId="2"/>
+  </si>
+  <si>
+    <t>かなりいい子供っぽさがでていますね！</t>
+    <rPh sb="5" eb="7">
+      <t>コドモ</t>
+    </rPh>
+    <phoneticPr fontId="2"/>
+  </si>
+  <si>
+    <t>味のバランスはとりつつも、子供たちが喜ぶ見た目で、</t>
+    <rPh sb="13" eb="15">
+      <t>コドモ</t>
+    </rPh>
+    <rPh sb="18" eb="19">
+      <t>ヨロコ</t>
+    </rPh>
+    <rPh sb="20" eb="21">
+      <t>ミ</t>
+    </rPh>
+    <rPh sb="22" eb="23">
+      <t>メ</t>
+    </rPh>
+    <phoneticPr fontId="2"/>
+  </si>
+  <si>
+    <t>かなり良い仕上がりといえるでしょうね！</t>
+    <rPh sb="3" eb="4">
+      <t>ヨ</t>
+    </rPh>
+    <rPh sb="5" eb="7">
+      <t>シア</t>
+    </rPh>
+    <phoneticPr fontId="2"/>
+  </si>
+  <si>
+    <t>あと一つ、抜けたものがあれば・・子供も大喜びではないでしょうか。</t>
+    <rPh sb="2" eb="3">
+      <t>ヒト</t>
+    </rPh>
+    <rPh sb="5" eb="6">
+      <t>ヌ</t>
+    </rPh>
+    <rPh sb="16" eb="18">
+      <t>コドモ</t>
+    </rPh>
+    <rPh sb="19" eb="21">
+      <t>オオヨロコ</t>
+    </rPh>
+    <phoneticPr fontId="2"/>
+  </si>
+  <si>
+    <t>素晴らしいです！</t>
+    <rPh sb="0" eb="2">
+      <t>スバ</t>
+    </rPh>
+    <phoneticPr fontId="2"/>
+  </si>
+  <si>
+    <t>この美しさ.. 華やかな見た目.. 子供たちは大興奮でしょう！</t>
+    <rPh sb="2" eb="3">
+      <t>ウツク</t>
+    </rPh>
+    <rPh sb="8" eb="9">
+      <t>ハナ</t>
+    </rPh>
+    <rPh sb="12" eb="13">
+      <t>ミ</t>
+    </rPh>
+    <rPh sb="14" eb="15">
+      <t>メ</t>
+    </rPh>
+    <rPh sb="18" eb="20">
+      <t>コドモ</t>
+    </rPh>
+    <rPh sb="23" eb="26">
+      <t>ダイコウフン</t>
+    </rPh>
+    <phoneticPr fontId="2"/>
+  </si>
+  <si>
+    <t>子供っぽさについて、まったく文句はございません。</t>
+    <rPh sb="0" eb="2">
+      <t>コドモ</t>
+    </rPh>
+    <rPh sb="14" eb="16">
+      <t>モンク</t>
+    </rPh>
+    <phoneticPr fontId="2"/>
+  </si>
+  <si>
+    <t>子供っぽさ アントワネットの感想になる。</t>
+    <rPh sb="0" eb="2">
+      <t>コドモ</t>
+    </rPh>
+    <rPh sb="14" eb="16">
+      <t>カンソウ</t>
+    </rPh>
+    <phoneticPr fontId="2"/>
+  </si>
+  <si>
+    <t>風らしさ アントワネットの感想になる。</t>
+    <rPh sb="0" eb="1">
+      <t>カゼ</t>
+    </rPh>
+    <rPh sb="13" eb="15">
+      <t>カンソウ</t>
+    </rPh>
+    <phoneticPr fontId="2"/>
+  </si>
+  <si>
+    <t>海らしさ アントワネットの感想になる。</t>
+    <rPh sb="0" eb="1">
+      <t>ウミ</t>
+    </rPh>
+    <rPh sb="13" eb="15">
+      <t>カンソウ</t>
+    </rPh>
+    <phoneticPr fontId="2"/>
+  </si>
+  <si>
+    <t>愛 アントワネットの感想になる。</t>
+    <rPh sb="0" eb="1">
+      <t>アイ</t>
+    </rPh>
+    <rPh sb="10" eb="12">
+      <t>カンソウ</t>
+    </rPh>
+    <phoneticPr fontId="2"/>
+  </si>
+  <si>
+    <t>夏らしさ アントワネットの感想になる。</t>
+    <rPh sb="0" eb="1">
+      <t>ナツ</t>
+    </rPh>
+    <rPh sb="13" eb="15">
+      <t>カンソウ</t>
+    </rPh>
+    <phoneticPr fontId="2"/>
+  </si>
+  <si>
+    <t>大人っぽい アントワネットの感想になる。</t>
+    <rPh sb="0" eb="2">
+      <t>オトナ</t>
+    </rPh>
+    <rPh sb="14" eb="16">
+      <t>カンソウ</t>
+    </rPh>
+    <phoneticPr fontId="2"/>
+  </si>
+  <si>
+    <t>メルヘン アントワネットの感想になる。</t>
+    <rPh sb="13" eb="15">
+      <t>カンソウ</t>
+    </rPh>
+    <phoneticPr fontId="2"/>
+  </si>
+  <si>
+    <t>芸術 アントワネットの感想になる。</t>
+    <rPh sb="0" eb="2">
+      <t>ゲイジュツ</t>
+    </rPh>
+    <rPh sb="11" eb="13">
+      <t>カンソウ</t>
+    </rPh>
+    <phoneticPr fontId="2"/>
+  </si>
+  <si>
+    <t>キラキラ アントワネットの感想になる。</t>
+    <rPh sb="13" eb="15">
+      <t>カンソウ</t>
+    </rPh>
+    <phoneticPr fontId="2"/>
+  </si>
+  <si>
+    <t>和風 アントワネットの感想になる。</t>
+    <rPh sb="0" eb="2">
+      <t>ワフウ</t>
+    </rPh>
+    <rPh sb="11" eb="13">
+      <t>カンソウ</t>
+    </rPh>
+    <phoneticPr fontId="2"/>
+  </si>
+  <si>
+    <t>子供が喜びそうな点ですが..。</t>
+    <rPh sb="0" eb="2">
+      <t>コドモ</t>
+    </rPh>
+    <rPh sb="3" eb="4">
+      <t>ヨロコ</t>
+    </rPh>
+    <rPh sb="8" eb="9">
+      <t>テン</t>
+    </rPh>
+    <phoneticPr fontId="2"/>
+  </si>
+  <si>
+    <t>子供たちが喜ぶには、少し華やかさが足りないといったところでしょうか。</t>
+    <rPh sb="0" eb="2">
+      <t>コドモ</t>
+    </rPh>
+    <rPh sb="5" eb="6">
+      <t>ヨロコ</t>
+    </rPh>
+    <rPh sb="10" eb="11">
+      <t>スコ</t>
+    </rPh>
+    <rPh sb="12" eb="13">
+      <t>ハナ</t>
+    </rPh>
+    <rPh sb="17" eb="18">
+      <t>タ</t>
+    </rPh>
+    <phoneticPr fontId="2"/>
+  </si>
+  <si>
+    <t>これは風らしさを感じません..。</t>
+    <rPh sb="3" eb="4">
+      <t>カゼ</t>
+    </rPh>
+    <rPh sb="8" eb="9">
+      <t>カン</t>
+    </rPh>
+    <phoneticPr fontId="2"/>
+  </si>
+  <si>
+    <t>風をもっと表現してほしいところですね。</t>
+    <rPh sb="0" eb="1">
+      <t>カゼ</t>
+    </rPh>
+    <rPh sb="5" eb="7">
+      <t>ヒョウゲン</t>
+    </rPh>
+    <phoneticPr fontId="2"/>
+  </si>
+  <si>
+    <t>私からは以上になります。</t>
+    <rPh sb="0" eb="1">
+      <t>ワタシ</t>
+    </rPh>
+    <rPh sb="4" eb="6">
+      <t>イジョウ</t>
+    </rPh>
+    <phoneticPr fontId="2"/>
+  </si>
+  <si>
+    <t>素材としては悪くないのですが、</t>
+    <rPh sb="0" eb="2">
+      <t>ソザイ</t>
+    </rPh>
+    <rPh sb="6" eb="7">
+      <t>ワル</t>
+    </rPh>
+    <phoneticPr fontId="2"/>
+  </si>
+  <si>
+    <t>これではふつうのお菓子で、あまり意味がないと思います。</t>
+    <rPh sb="9" eb="11">
+      <t>カシ</t>
+    </rPh>
+    <rPh sb="16" eb="18">
+      <t>イミ</t>
+    </rPh>
+    <rPh sb="22" eb="23">
+      <t>オモ</t>
+    </rPh>
+    <phoneticPr fontId="2"/>
+  </si>
+  <si>
+    <t>かなりいい風感を感じました。</t>
+    <rPh sb="5" eb="6">
+      <t>カゼ</t>
+    </rPh>
+    <rPh sb="6" eb="7">
+      <t>カン</t>
+    </rPh>
+    <rPh sb="8" eb="9">
+      <t>カン</t>
+    </rPh>
+    <phoneticPr fontId="2"/>
+  </si>
+  <si>
+    <t>この見た目、とてもよいと思います。</t>
+    <rPh sb="2" eb="3">
+      <t>ミ</t>
+    </rPh>
+    <rPh sb="4" eb="5">
+      <t>メ</t>
+    </rPh>
+    <rPh sb="12" eb="13">
+      <t>オモ</t>
+    </rPh>
+    <phoneticPr fontId="2"/>
+  </si>
+  <si>
+    <t>後一工夫で、地球を.. 風を感じるおかしになるでしょう。</t>
+    <rPh sb="0" eb="4">
+      <t>アトヒトクフウ</t>
+    </rPh>
+    <rPh sb="6" eb="8">
+      <t>チキュウ</t>
+    </rPh>
+    <rPh sb="12" eb="13">
+      <t>カゼ</t>
+    </rPh>
+    <rPh sb="14" eb="15">
+      <t>カン</t>
+    </rPh>
+    <phoneticPr fontId="2"/>
+  </si>
+  <si>
+    <t>願わくば、これ以上のものができるのを楽しみにしています。</t>
+    <rPh sb="0" eb="1">
+      <t>ネガ</t>
+    </rPh>
+    <rPh sb="7" eb="9">
+      <t>イジョウ</t>
+    </rPh>
+    <rPh sb="18" eb="19">
+      <t>タノ</t>
+    </rPh>
+    <phoneticPr fontId="2"/>
+  </si>
+  <si>
+    <t>この美しさ.. まさに風を象徴したお菓子！</t>
+    <rPh sb="2" eb="3">
+      <t>ウツク</t>
+    </rPh>
+    <rPh sb="11" eb="12">
+      <t>カゼ</t>
+    </rPh>
+    <rPh sb="13" eb="15">
+      <t>ショウチョウ</t>
+    </rPh>
+    <rPh sb="18" eb="20">
+      <t>カシ</t>
+    </rPh>
+    <phoneticPr fontId="2"/>
+  </si>
+  <si>
+    <t>とても美しく、どのコンテストに出しても恥じないものですね。</t>
+    <rPh sb="3" eb="4">
+      <t>ウツク</t>
+    </rPh>
+    <rPh sb="15" eb="16">
+      <t>ダ</t>
+    </rPh>
+    <rPh sb="19" eb="20">
+      <t>ハ</t>
+    </rPh>
+    <phoneticPr fontId="2"/>
+  </si>
+  <si>
+    <t>あなたたちの将来が、とても楽しみです♪</t>
+    <rPh sb="6" eb="8">
+      <t>ショウライ</t>
+    </rPh>
+    <rPh sb="13" eb="14">
+      <t>タノ</t>
+    </rPh>
+    <phoneticPr fontId="2"/>
+  </si>
+  <si>
+    <t>これは海らしさを感じません..。</t>
+    <rPh sb="3" eb="4">
+      <t>ウミ</t>
+    </rPh>
+    <rPh sb="8" eb="9">
+      <t>カン</t>
+    </rPh>
+    <phoneticPr fontId="2"/>
+  </si>
+  <si>
+    <t>海とはなにか.. もっと海を表現してほしいところですね。</t>
+    <rPh sb="0" eb="1">
+      <t>ウミ</t>
+    </rPh>
+    <rPh sb="12" eb="13">
+      <t>ウミ</t>
+    </rPh>
+    <rPh sb="14" eb="16">
+      <t>ヒョウゲン</t>
+    </rPh>
+    <phoneticPr fontId="2"/>
+  </si>
+  <si>
+    <t>ただ海感を、もう少し感じさせてほしいところです。</t>
+    <rPh sb="2" eb="3">
+      <t>ウミ</t>
+    </rPh>
+    <rPh sb="3" eb="4">
+      <t>カン</t>
+    </rPh>
+    <rPh sb="8" eb="9">
+      <t>スコ</t>
+    </rPh>
+    <rPh sb="10" eb="11">
+      <t>カン</t>
+    </rPh>
+    <phoneticPr fontId="2"/>
+  </si>
+  <si>
+    <t>風感を、もう少し感じさせてほしいところです。</t>
+    <rPh sb="0" eb="1">
+      <t>カゼ</t>
+    </rPh>
+    <rPh sb="1" eb="2">
+      <t>カン</t>
+    </rPh>
+    <rPh sb="6" eb="7">
+      <t>スコ</t>
+    </rPh>
+    <rPh sb="8" eb="9">
+      <t>カン</t>
+    </rPh>
+    <phoneticPr fontId="2"/>
+  </si>
+  <si>
+    <t>かなりいい海を感じました。</t>
+    <rPh sb="5" eb="6">
+      <t>ウミ</t>
+    </rPh>
+    <rPh sb="7" eb="8">
+      <t>カン</t>
+    </rPh>
+    <phoneticPr fontId="2"/>
+  </si>
+  <si>
+    <t>この見た目、とても美しいですね。</t>
+    <rPh sb="2" eb="3">
+      <t>ミ</t>
+    </rPh>
+    <rPh sb="4" eb="5">
+      <t>メ</t>
+    </rPh>
+    <rPh sb="9" eb="10">
+      <t>ウツク</t>
+    </rPh>
+    <phoneticPr fontId="2"/>
+  </si>
+  <si>
+    <t>海を象徴するには、及第点といったところでしょう。</t>
+    <rPh sb="0" eb="1">
+      <t>ウミ</t>
+    </rPh>
+    <rPh sb="2" eb="4">
+      <t>ショウチョウ</t>
+    </rPh>
+    <rPh sb="9" eb="12">
+      <t>キュウダイテン</t>
+    </rPh>
+    <phoneticPr fontId="2"/>
+  </si>
+  <si>
+    <t>この美しさ.. まさに海を象徴したお菓子！</t>
+    <rPh sb="2" eb="3">
+      <t>ウツク</t>
+    </rPh>
+    <rPh sb="11" eb="12">
+      <t>ウミ</t>
+    </rPh>
+    <rPh sb="13" eb="15">
+      <t>ショウチョウ</t>
+    </rPh>
+    <rPh sb="18" eb="20">
+      <t>カシ</t>
+    </rPh>
+    <phoneticPr fontId="2"/>
+  </si>
+  <si>
+    <t>とても美しく、食べた瞬間、まるで海のなかできれいなおさかなやサンゴ礁と踊るような・・。</t>
+    <rPh sb="3" eb="4">
+      <t>ウツク</t>
+    </rPh>
+    <rPh sb="7" eb="8">
+      <t>タ</t>
+    </rPh>
+    <rPh sb="10" eb="12">
+      <t>シュンカン</t>
+    </rPh>
+    <rPh sb="16" eb="17">
+      <t>ウミ</t>
+    </rPh>
+    <rPh sb="33" eb="34">
+      <t>ショウ</t>
+    </rPh>
+    <rPh sb="35" eb="36">
+      <t>オド</t>
+    </rPh>
+    <phoneticPr fontId="2"/>
+  </si>
+  <si>
+    <t>はっ！　失礼しました。あなたたちの未来を、とても楽しみにしています♪</t>
+    <rPh sb="4" eb="6">
+      <t>シツレイ</t>
+    </rPh>
+    <rPh sb="17" eb="19">
+      <t>ミライ</t>
+    </rPh>
+    <rPh sb="24" eb="25">
+      <t>タノ</t>
+    </rPh>
+    <phoneticPr fontId="2"/>
+  </si>
+  <si>
+    <t>すこし、愛が足りない感じでしょうか。</t>
+    <rPh sb="4" eb="5">
+      <t>アイ</t>
+    </rPh>
+    <rPh sb="6" eb="7">
+      <t>タ</t>
+    </rPh>
+    <rPh sb="10" eb="11">
+      <t>カン</t>
+    </rPh>
+    <phoneticPr fontId="2"/>
+  </si>
+  <si>
+    <t>もう少しハートを・・情熱を感じさせてほしいところです。</t>
+    <rPh sb="10" eb="12">
+      <t>ジョウネツ</t>
+    </rPh>
+    <rPh sb="13" eb="14">
+      <t>カン</t>
+    </rPh>
+    <phoneticPr fontId="2"/>
+  </si>
+  <si>
+    <t>がんばってください！</t>
+    <phoneticPr fontId="2"/>
+  </si>
+  <si>
+    <t>ただ、少し、愛情が足りていない感じでしょうか。</t>
+    <rPh sb="3" eb="4">
+      <t>スコ</t>
+    </rPh>
+    <rPh sb="6" eb="7">
+      <t>アイ</t>
+    </rPh>
+    <rPh sb="7" eb="8">
+      <t>ジョウ</t>
+    </rPh>
+    <rPh sb="9" eb="10">
+      <t>タ</t>
+    </rPh>
+    <rPh sb="15" eb="16">
+      <t>カン</t>
+    </rPh>
+    <phoneticPr fontId="2"/>
+  </si>
+  <si>
+    <t>愛らしさをもう少し工夫して、出してもらいたいものです。</t>
+    <rPh sb="0" eb="1">
+      <t>アイ</t>
+    </rPh>
+    <rPh sb="7" eb="8">
+      <t>スコ</t>
+    </rPh>
+    <rPh sb="9" eb="11">
+      <t>クフウ</t>
+    </rPh>
+    <rPh sb="14" eb="15">
+      <t>ダ</t>
+    </rPh>
+    <phoneticPr fontId="2"/>
+  </si>
+  <si>
+    <t>次に期待ですね！</t>
+    <rPh sb="0" eb="1">
+      <t>ツギ</t>
+    </rPh>
+    <rPh sb="2" eb="4">
+      <t>キタイ</t>
+    </rPh>
+    <phoneticPr fontId="2"/>
+  </si>
+  <si>
+    <t>かなりいい愛らしさがでております。</t>
+    <rPh sb="5" eb="6">
+      <t>アイ</t>
+    </rPh>
+    <phoneticPr fontId="2"/>
+  </si>
+  <si>
+    <t>味のバランスはとりつつも、愛らしさを感じます。</t>
+    <rPh sb="13" eb="14">
+      <t>アイ</t>
+    </rPh>
+    <rPh sb="18" eb="19">
+      <t>カン</t>
+    </rPh>
+    <phoneticPr fontId="2"/>
+  </si>
+  <si>
+    <t>もう一つ、愛の表現に工夫があれば、パーフェクトでしょう。</t>
+    <rPh sb="2" eb="3">
+      <t>ヒト</t>
+    </rPh>
+    <rPh sb="5" eb="6">
+      <t>アイ</t>
+    </rPh>
+    <rPh sb="7" eb="9">
+      <t>ヒョウゲン</t>
+    </rPh>
+    <rPh sb="10" eb="12">
+      <t>クフウ</t>
+    </rPh>
+    <phoneticPr fontId="2"/>
+  </si>
+  <si>
+    <t>この美しさ.. かわいらしい見た目.. まさに愛のおかしといえます！</t>
+    <rPh sb="2" eb="3">
+      <t>ウツク</t>
+    </rPh>
+    <rPh sb="14" eb="15">
+      <t>ミ</t>
+    </rPh>
+    <rPh sb="16" eb="17">
+      <t>メ</t>
+    </rPh>
+    <rPh sb="23" eb="24">
+      <t>アイ</t>
+    </rPh>
+    <phoneticPr fontId="2"/>
+  </si>
+  <si>
+    <t>一口食べると、とてもこころがあったかくなりました。</t>
+    <rPh sb="0" eb="2">
+      <t>ヒトクチ</t>
+    </rPh>
+    <rPh sb="2" eb="3">
+      <t>タ</t>
+    </rPh>
+    <phoneticPr fontId="2"/>
+  </si>
+  <si>
+    <t>ほんとうに、ありがとうございます♪</t>
+    <phoneticPr fontId="2"/>
+  </si>
+  <si>
+    <t>夏らしさは、あまり感じられない・・といったところでしょうか。</t>
+    <rPh sb="0" eb="1">
+      <t>ナツ</t>
+    </rPh>
+    <rPh sb="9" eb="10">
+      <t>カン</t>
+    </rPh>
+    <phoneticPr fontId="2"/>
+  </si>
+  <si>
+    <t>もう少し夏感を出してほしいところですね。</t>
+    <rPh sb="4" eb="5">
+      <t>ナツ</t>
+    </rPh>
+    <rPh sb="5" eb="6">
+      <t>カン</t>
+    </rPh>
+    <rPh sb="7" eb="8">
+      <t>ダ</t>
+    </rPh>
+    <phoneticPr fontId="2"/>
+  </si>
+  <si>
+    <t>ただ、少し、夏感は薄く感じられました。</t>
+    <rPh sb="3" eb="4">
+      <t>スコ</t>
+    </rPh>
+    <rPh sb="6" eb="7">
+      <t>ナツ</t>
+    </rPh>
+    <rPh sb="7" eb="8">
+      <t>カン</t>
+    </rPh>
+    <rPh sb="9" eb="10">
+      <t>ウス</t>
+    </rPh>
+    <rPh sb="11" eb="12">
+      <t>カン</t>
+    </rPh>
+    <phoneticPr fontId="2"/>
+  </si>
+  <si>
+    <t>仕上げの工夫で、夏感がでると最高ですね。</t>
+    <rPh sb="0" eb="2">
+      <t>シア</t>
+    </rPh>
+    <rPh sb="4" eb="6">
+      <t>クフウ</t>
+    </rPh>
+    <rPh sb="8" eb="10">
+      <t>ナツカン</t>
+    </rPh>
+    <rPh sb="14" eb="16">
+      <t>サイコウ</t>
+    </rPh>
+    <phoneticPr fontId="2"/>
+  </si>
+  <si>
+    <t>これからに期待しております！</t>
+    <rPh sb="5" eb="7">
+      <t>キタイ</t>
+    </rPh>
+    <phoneticPr fontId="2"/>
+  </si>
+  <si>
+    <t>いい夏らしさがでていますね！</t>
+    <rPh sb="2" eb="3">
+      <t>ナツ</t>
+    </rPh>
+    <phoneticPr fontId="2"/>
+  </si>
+  <si>
+    <t>見た目的には、まさにフェスティバルにような、</t>
+    <rPh sb="0" eb="1">
+      <t>ミ</t>
+    </rPh>
+    <rPh sb="2" eb="4">
+      <t>メテキ</t>
+    </rPh>
+    <phoneticPr fontId="2"/>
+  </si>
+  <si>
+    <t>よい夏感を感じます。</t>
+    <rPh sb="2" eb="4">
+      <t>ナツカン</t>
+    </rPh>
+    <rPh sb="5" eb="6">
+      <t>カン</t>
+    </rPh>
+    <phoneticPr fontId="2"/>
+  </si>
+  <si>
+    <t>あと一つ、抜けたものがあれば・・さらに良くなりそうです。</t>
+    <rPh sb="2" eb="3">
+      <t>ヒト</t>
+    </rPh>
+    <rPh sb="5" eb="6">
+      <t>ヌ</t>
+    </rPh>
+    <rPh sb="19" eb="20">
+      <t>ヨ</t>
+    </rPh>
+    <phoneticPr fontId="2"/>
+  </si>
+  <si>
+    <t>この美しさ.. 夏感がマックスで、とても情緒を感じます。</t>
+    <rPh sb="2" eb="3">
+      <t>ウツク</t>
+    </rPh>
+    <rPh sb="8" eb="9">
+      <t>ナツ</t>
+    </rPh>
+    <rPh sb="9" eb="10">
+      <t>カン</t>
+    </rPh>
+    <rPh sb="20" eb="22">
+      <t>ジョウチョ</t>
+    </rPh>
+    <rPh sb="23" eb="24">
+      <t>カン</t>
+    </rPh>
+    <phoneticPr fontId="2"/>
+  </si>
+  <si>
+    <t>夏感は、すばらしく良く出ていると思います！</t>
+    <rPh sb="0" eb="2">
+      <t>ナツカン</t>
+    </rPh>
+    <rPh sb="9" eb="10">
+      <t>ヨ</t>
+    </rPh>
+    <rPh sb="11" eb="12">
+      <t>デ</t>
+    </rPh>
+    <rPh sb="16" eb="17">
+      <t>オモ</t>
+    </rPh>
+    <phoneticPr fontId="2"/>
+  </si>
+  <si>
+    <t>見た目的には大人っぽくは見えませんね..。</t>
+    <rPh sb="0" eb="1">
+      <t>ミ</t>
+    </rPh>
+    <rPh sb="2" eb="3">
+      <t>メ</t>
+    </rPh>
+    <rPh sb="3" eb="4">
+      <t>テキ</t>
+    </rPh>
+    <rPh sb="6" eb="8">
+      <t>オトナ</t>
+    </rPh>
+    <rPh sb="12" eb="13">
+      <t>ミ</t>
+    </rPh>
+    <phoneticPr fontId="2"/>
+  </si>
+  <si>
+    <t>もう少し大人向けの雰囲気を出してほしいです。</t>
+    <rPh sb="4" eb="7">
+      <t>オトナム</t>
+    </rPh>
+    <rPh sb="9" eb="12">
+      <t>フンイキ</t>
+    </rPh>
+    <rPh sb="13" eb="14">
+      <t>ダ</t>
+    </rPh>
+    <phoneticPr fontId="2"/>
+  </si>
+  <si>
+    <t>もう少し仕上げに工夫が必要そうです。</t>
+    <rPh sb="2" eb="3">
+      <t>スコ</t>
+    </rPh>
+    <rPh sb="4" eb="6">
+      <t>シア</t>
+    </rPh>
+    <rPh sb="8" eb="10">
+      <t>クフウ</t>
+    </rPh>
+    <rPh sb="11" eb="13">
+      <t>ヒツヨウ</t>
+    </rPh>
+    <phoneticPr fontId="2"/>
+  </si>
+  <si>
+    <t>かなりいい大人っぽさがでていますね！</t>
+    <rPh sb="5" eb="7">
+      <t>オトナ</t>
+    </rPh>
+    <phoneticPr fontId="2"/>
+  </si>
+  <si>
+    <t>大人向けの渋さが出ておりました。</t>
+    <rPh sb="0" eb="3">
+      <t>オトナム</t>
+    </rPh>
+    <rPh sb="5" eb="6">
+      <t>シブ</t>
+    </rPh>
+    <rPh sb="8" eb="9">
+      <t>デ</t>
+    </rPh>
+    <phoneticPr fontId="2"/>
+  </si>
+  <si>
+    <t>なかなかの仕上がりといえるでしょうね！</t>
+    <rPh sb="5" eb="7">
+      <t>シア</t>
+    </rPh>
+    <phoneticPr fontId="2"/>
+  </si>
+  <si>
+    <t>あと一つ、抜けたものがあれば・・大人も大喜びではないでしょうか。</t>
+    <rPh sb="2" eb="3">
+      <t>ヒト</t>
+    </rPh>
+    <rPh sb="5" eb="6">
+      <t>ヌ</t>
+    </rPh>
+    <rPh sb="16" eb="18">
+      <t>オトナ</t>
+    </rPh>
+    <rPh sb="19" eb="21">
+      <t>オオヨロコ</t>
+    </rPh>
+    <phoneticPr fontId="2"/>
+  </si>
+  <si>
+    <t>この美しさ.. アダルティな見た目.. デートや贈り物にぴったりではないでしょうか。</t>
+    <rPh sb="2" eb="3">
+      <t>ウツク</t>
+    </rPh>
+    <rPh sb="14" eb="15">
+      <t>ミ</t>
+    </rPh>
+    <rPh sb="16" eb="17">
+      <t>メ</t>
+    </rPh>
+    <rPh sb="24" eb="25">
+      <t>オク</t>
+    </rPh>
+    <rPh sb="26" eb="27">
+      <t>モノ</t>
+    </rPh>
+    <phoneticPr fontId="2"/>
+  </si>
+  <si>
+    <t>大人感の仕上がりについて、すばらしくよくでていると思います。</t>
+    <rPh sb="0" eb="3">
+      <t>オトナカン</t>
+    </rPh>
+    <rPh sb="4" eb="6">
+      <t>シア</t>
+    </rPh>
+    <rPh sb="25" eb="26">
+      <t>オモ</t>
+    </rPh>
+    <phoneticPr fontId="2"/>
+  </si>
+  <si>
+    <t>・・これを、かっこいい殿方にプレゼントしてもらうと、もうメロメロです！</t>
+    <rPh sb="11" eb="13">
+      <t>トノガタ</t>
+    </rPh>
+    <phoneticPr fontId="2"/>
+  </si>
+  <si>
+    <t>メルヘンな感じは、残念ながら感じられませんでした。</t>
+    <rPh sb="5" eb="6">
+      <t>カン</t>
+    </rPh>
+    <rPh sb="9" eb="11">
+      <t>ザンネン</t>
+    </rPh>
+    <rPh sb="14" eb="15">
+      <t>カン</t>
+    </rPh>
+    <phoneticPr fontId="2"/>
+  </si>
+  <si>
+    <t>ただ、メルヘンかといわれると、少し物足りなかったようです。</t>
+    <rPh sb="15" eb="16">
+      <t>スコ</t>
+    </rPh>
+    <rPh sb="17" eb="19">
+      <t>モノタ</t>
+    </rPh>
+    <phoneticPr fontId="2"/>
+  </si>
+  <si>
+    <t>次に期待します！</t>
+    <rPh sb="0" eb="1">
+      <t>ツギ</t>
+    </rPh>
+    <rPh sb="2" eb="4">
+      <t>キタイ</t>
+    </rPh>
+    <phoneticPr fontId="2"/>
+  </si>
+  <si>
+    <t>かなりいいメルヘンらしさがでていますね！</t>
+    <phoneticPr fontId="2"/>
+  </si>
+  <si>
+    <t>味のバランスはとりつつも、見た目がかわいいので、</t>
+    <rPh sb="13" eb="14">
+      <t>ミ</t>
+    </rPh>
+    <rPh sb="15" eb="16">
+      <t>メ</t>
+    </rPh>
+    <phoneticPr fontId="2"/>
+  </si>
+  <si>
+    <t>とくに女の子は喜ぶお菓子に仕上がってると思います。</t>
+    <rPh sb="3" eb="4">
+      <t>オンナ</t>
+    </rPh>
+    <rPh sb="5" eb="6">
+      <t>コ</t>
+    </rPh>
+    <rPh sb="7" eb="8">
+      <t>ヨロコ</t>
+    </rPh>
+    <rPh sb="10" eb="12">
+      <t>カシ</t>
+    </rPh>
+    <rPh sb="13" eb="15">
+      <t>シア</t>
+    </rPh>
+    <rPh sb="20" eb="21">
+      <t>オモ</t>
+    </rPh>
+    <phoneticPr fontId="2"/>
+  </si>
+  <si>
+    <t>願わくば、メルヘンさにあと一味あれば.. 最高の見た目になるでしょう。</t>
+    <rPh sb="0" eb="1">
+      <t>ネガ</t>
+    </rPh>
+    <rPh sb="13" eb="15">
+      <t>ヒトアジ</t>
+    </rPh>
+    <rPh sb="21" eb="23">
+      <t>サイコウ</t>
+    </rPh>
+    <rPh sb="24" eb="25">
+      <t>ミ</t>
+    </rPh>
+    <rPh sb="26" eb="27">
+      <t>メ</t>
+    </rPh>
+    <phoneticPr fontId="2"/>
+  </si>
+  <si>
+    <t>この美しさ.. かわいらしい見た目.. 乙女たちはメロメロです。</t>
+    <rPh sb="2" eb="3">
+      <t>ウツク</t>
+    </rPh>
+    <rPh sb="14" eb="15">
+      <t>ミ</t>
+    </rPh>
+    <rPh sb="16" eb="17">
+      <t>メ</t>
+    </rPh>
+    <rPh sb="20" eb="22">
+      <t>オトメ</t>
+    </rPh>
+    <phoneticPr fontId="2"/>
+  </si>
+  <si>
+    <t>メルヘンな世界観が大変よく表現されていると思います。</t>
+    <rPh sb="5" eb="8">
+      <t>セカイカン</t>
+    </rPh>
+    <rPh sb="9" eb="11">
+      <t>タイヘン</t>
+    </rPh>
+    <rPh sb="13" eb="15">
+      <t>ヒョウゲン</t>
+    </rPh>
+    <rPh sb="21" eb="22">
+      <t>オモ</t>
+    </rPh>
+    <phoneticPr fontId="2"/>
+  </si>
+  <si>
+    <t>食べれば食べるほど、心が若返ってくるようですわ！　お～ほっほっほ・・！</t>
+    <rPh sb="0" eb="1">
+      <t>タ</t>
+    </rPh>
+    <rPh sb="4" eb="5">
+      <t>タ</t>
+    </rPh>
+    <rPh sb="10" eb="11">
+      <t>ココロ</t>
+    </rPh>
+    <rPh sb="12" eb="14">
+      <t>ワカガエ</t>
+    </rPh>
+    <phoneticPr fontId="2"/>
+  </si>
+  <si>
+    <t>もっと芸術的な、派手な見た目がほしいですね。</t>
+    <rPh sb="3" eb="5">
+      <t>ゲイジュツ</t>
+    </rPh>
+    <rPh sb="5" eb="6">
+      <t>テキ</t>
+    </rPh>
+    <rPh sb="8" eb="10">
+      <t>ハデ</t>
+    </rPh>
+    <rPh sb="11" eb="12">
+      <t>ミ</t>
+    </rPh>
+    <rPh sb="13" eb="14">
+      <t>メ</t>
+    </rPh>
+    <phoneticPr fontId="2"/>
+  </si>
+  <si>
+    <t>見た目はシンプルなお菓子ですが、ありふれた見た目ともいえます。</t>
+    <rPh sb="0" eb="1">
+      <t>ミ</t>
+    </rPh>
+    <rPh sb="2" eb="3">
+      <t>メ</t>
+    </rPh>
+    <rPh sb="10" eb="12">
+      <t>カシ</t>
+    </rPh>
+    <rPh sb="21" eb="22">
+      <t>ミ</t>
+    </rPh>
+    <rPh sb="23" eb="24">
+      <t>メ</t>
+    </rPh>
+    <phoneticPr fontId="2"/>
+  </si>
+  <si>
+    <t>ただ、やや芸術的というと、少しありふれた見た目でしょうか。</t>
+    <rPh sb="5" eb="7">
+      <t>ゲイジュツ</t>
+    </rPh>
+    <rPh sb="7" eb="8">
+      <t>テキ</t>
+    </rPh>
+    <rPh sb="13" eb="14">
+      <t>スコ</t>
+    </rPh>
+    <rPh sb="20" eb="21">
+      <t>ミ</t>
+    </rPh>
+    <rPh sb="22" eb="23">
+      <t>メ</t>
+    </rPh>
+    <phoneticPr fontId="2"/>
+  </si>
+  <si>
+    <t>もっと、派手な見た目になると、前衛的で嬉しいですね。</t>
+    <rPh sb="4" eb="6">
+      <t>ハデ</t>
+    </rPh>
+    <rPh sb="7" eb="8">
+      <t>ミ</t>
+    </rPh>
+    <rPh sb="9" eb="10">
+      <t>メ</t>
+    </rPh>
+    <rPh sb="15" eb="18">
+      <t>ゼンエイテキ</t>
+    </rPh>
+    <rPh sb="19" eb="20">
+      <t>ウレ</t>
+    </rPh>
+    <phoneticPr fontId="2"/>
+  </si>
+  <si>
+    <t>かなりいい芸術的なおかしといえます。</t>
+    <rPh sb="5" eb="7">
+      <t>ゲイジュツ</t>
+    </rPh>
+    <rPh sb="7" eb="8">
+      <t>テキ</t>
+    </rPh>
+    <phoneticPr fontId="2"/>
+  </si>
+  <si>
+    <t>味のバランスはとりつつも、前衛的な攻めた見せ方で、</t>
+    <rPh sb="13" eb="15">
+      <t>ゼンエイ</t>
+    </rPh>
+    <rPh sb="15" eb="16">
+      <t>テキ</t>
+    </rPh>
+    <rPh sb="17" eb="18">
+      <t>セ</t>
+    </rPh>
+    <rPh sb="20" eb="21">
+      <t>ミ</t>
+    </rPh>
+    <rPh sb="22" eb="23">
+      <t>カタ</t>
+    </rPh>
+    <phoneticPr fontId="2"/>
+  </si>
+  <si>
+    <t>あまり見たことがないおかしが高評価につながりました。</t>
+    <rPh sb="3" eb="4">
+      <t>ミ</t>
+    </rPh>
+    <rPh sb="14" eb="17">
+      <t>コウヒョウカ</t>
+    </rPh>
+    <phoneticPr fontId="2"/>
+  </si>
+  <si>
+    <t>あと一つ、抜けたものがあれば・・最高のおかしになるでしょう。</t>
+    <rPh sb="2" eb="3">
+      <t>ヒト</t>
+    </rPh>
+    <rPh sb="5" eb="6">
+      <t>ヌ</t>
+    </rPh>
+    <rPh sb="16" eb="18">
+      <t>サイコウ</t>
+    </rPh>
+    <phoneticPr fontId="2"/>
+  </si>
+  <si>
+    <t>この美しさ.. 前衛的な見た目.. とても大興奮です！</t>
+    <rPh sb="2" eb="3">
+      <t>ウツク</t>
+    </rPh>
+    <rPh sb="8" eb="11">
+      <t>ゼンエイテキ</t>
+    </rPh>
+    <rPh sb="12" eb="13">
+      <t>ミ</t>
+    </rPh>
+    <rPh sb="14" eb="15">
+      <t>メ</t>
+    </rPh>
+    <rPh sb="21" eb="22">
+      <t>ダイ</t>
+    </rPh>
+    <rPh sb="22" eb="24">
+      <t>コウフン</t>
+    </rPh>
+    <phoneticPr fontId="2"/>
+  </si>
+  <si>
+    <t>芸術的といえば、まさにこのお菓子といえるのではないでしょうか。</t>
+    <rPh sb="0" eb="3">
+      <t>ゲイジュツテキ</t>
+    </rPh>
+    <rPh sb="14" eb="16">
+      <t>カシ</t>
+    </rPh>
+    <phoneticPr fontId="2"/>
+  </si>
+  <si>
+    <t>パティシエだけでなく、アーティストとしての才能が光りますね！　お～ほっほっほ・・。</t>
+    <rPh sb="21" eb="23">
+      <t>サイノウ</t>
+    </rPh>
+    <rPh sb="24" eb="25">
+      <t>ヒカ</t>
+    </rPh>
+    <phoneticPr fontId="2"/>
+  </si>
+  <si>
+    <t>風らしさについてですが..。</t>
+    <rPh sb="0" eb="1">
+      <t>カゼ</t>
+    </rPh>
+    <phoneticPr fontId="2"/>
+  </si>
+  <si>
+    <t>海らしさですが..。</t>
+    <rPh sb="0" eb="1">
+      <t>ウミ</t>
+    </rPh>
+    <phoneticPr fontId="2"/>
+  </si>
+  <si>
+    <t>愛のおかしということですが..。</t>
+    <rPh sb="0" eb="1">
+      <t>アイ</t>
+    </rPh>
+    <phoneticPr fontId="2"/>
+  </si>
+  <si>
+    <t>夏らしさについてですが..。</t>
+    <rPh sb="0" eb="1">
+      <t>ナツ</t>
+    </rPh>
+    <phoneticPr fontId="2"/>
+  </si>
+  <si>
+    <t>大人のおかしということですが..。</t>
+    <rPh sb="0" eb="2">
+      <t>オトナ</t>
+    </rPh>
+    <phoneticPr fontId="2"/>
+  </si>
+  <si>
+    <t>子供向けのおかしについてですが..。</t>
+    <rPh sb="0" eb="2">
+      <t>コドモ</t>
+    </rPh>
+    <rPh sb="2" eb="3">
+      <t>ム</t>
+    </rPh>
+    <phoneticPr fontId="2"/>
+  </si>
+  <si>
+    <t>メルヘンらしさですが..。</t>
+    <phoneticPr fontId="2"/>
+  </si>
+  <si>
+    <t>キラキラ感のあるおかしですが..。</t>
+    <rPh sb="4" eb="5">
+      <t>カン</t>
+    </rPh>
+    <phoneticPr fontId="2"/>
+  </si>
+  <si>
+    <t>あまりキラキラ感はでていないようでした。</t>
+    <rPh sb="7" eb="8">
+      <t>カン</t>
+    </rPh>
+    <phoneticPr fontId="2"/>
+  </si>
+  <si>
+    <t>もっと、キラキラがほしいところです。</t>
+    <phoneticPr fontId="2"/>
+  </si>
+  <si>
+    <t>芸術的なおかしという点でいうと..。</t>
+    <rPh sb="0" eb="3">
+      <t>ゲイジュツテキ</t>
+    </rPh>
+    <rPh sb="10" eb="11">
+      <t>テン</t>
+    </rPh>
+    <phoneticPr fontId="2"/>
+  </si>
+  <si>
+    <t>ただ、少しキラキラ感や華やかさについては、足りないというのが正直な感想です。</t>
+    <rPh sb="3" eb="4">
+      <t>スコ</t>
+    </rPh>
+    <rPh sb="9" eb="10">
+      <t>カン</t>
+    </rPh>
+    <rPh sb="11" eb="12">
+      <t>ハナ</t>
+    </rPh>
+    <rPh sb="21" eb="22">
+      <t>タ</t>
+    </rPh>
+    <rPh sb="30" eb="32">
+      <t>ショウジキ</t>
+    </rPh>
+    <rPh sb="33" eb="35">
+      <t>カンソウ</t>
+    </rPh>
+    <phoneticPr fontId="2"/>
+  </si>
+  <si>
+    <t>せっかくなので、もう少しキラキラ感がでるとなおよいですね。</t>
+    <rPh sb="10" eb="11">
+      <t>スコ</t>
+    </rPh>
+    <rPh sb="16" eb="17">
+      <t>カン</t>
+    </rPh>
+    <phoneticPr fontId="2"/>
+  </si>
+  <si>
+    <t>いいキラキラ感がでておりました。</t>
+    <rPh sb="6" eb="7">
+      <t>カン</t>
+    </rPh>
+    <phoneticPr fontId="2"/>
+  </si>
+  <si>
+    <t>味のバランスはとりつつも、お菓子のキラキラ感がでており、</t>
+    <rPh sb="14" eb="16">
+      <t>カシ</t>
+    </rPh>
+    <rPh sb="21" eb="22">
+      <t>カン</t>
+    </rPh>
+    <phoneticPr fontId="2"/>
+  </si>
+  <si>
+    <t>かなり美しい仕上がりといえるでしょう！</t>
+    <rPh sb="3" eb="4">
+      <t>ウツク</t>
+    </rPh>
+    <rPh sb="6" eb="8">
+      <t>シア</t>
+    </rPh>
+    <phoneticPr fontId="2"/>
+  </si>
+  <si>
+    <t>あと一つ、抜けたものがあれば・・キラキラ好きにもたまらないのではないでしょうか。</t>
+    <rPh sb="2" eb="3">
+      <t>ヒト</t>
+    </rPh>
+    <rPh sb="5" eb="6">
+      <t>ヌ</t>
+    </rPh>
+    <rPh sb="20" eb="21">
+      <t>ス</t>
+    </rPh>
+    <phoneticPr fontId="2"/>
+  </si>
+  <si>
+    <t>この.. キラキラ感.. まさに宝石のような美しさです。</t>
+    <rPh sb="9" eb="10">
+      <t>カン</t>
+    </rPh>
+    <rPh sb="16" eb="18">
+      <t>ホウセキ</t>
+    </rPh>
+    <rPh sb="22" eb="23">
+      <t>ウツク</t>
+    </rPh>
+    <phoneticPr fontId="2"/>
+  </si>
+  <si>
+    <t>キラキラ具合については、まったく文句がありません。すばらしい！</t>
+    <rPh sb="4" eb="6">
+      <t>グアイ</t>
+    </rPh>
+    <rPh sb="16" eb="18">
+      <t>モンク</t>
+    </rPh>
+    <phoneticPr fontId="2"/>
+  </si>
+  <si>
+    <t>和風感のあるおかしですが..。</t>
+    <rPh sb="0" eb="3">
+      <t>ワフウカン</t>
+    </rPh>
+    <phoneticPr fontId="2"/>
+  </si>
+  <si>
+    <t>あまり、和風という感じではなかったようです。</t>
+    <rPh sb="4" eb="6">
+      <t>ワフウ</t>
+    </rPh>
+    <rPh sb="9" eb="10">
+      <t>カン</t>
+    </rPh>
+    <phoneticPr fontId="2"/>
+  </si>
+  <si>
+    <t>ただ、和風感については、少し物足りないようです。</t>
+    <rPh sb="3" eb="5">
+      <t>ワフウ</t>
+    </rPh>
+    <rPh sb="5" eb="6">
+      <t>カン</t>
+    </rPh>
+    <rPh sb="12" eb="13">
+      <t>スコ</t>
+    </rPh>
+    <rPh sb="14" eb="16">
+      <t>モノタ</t>
+    </rPh>
+    <phoneticPr fontId="2"/>
+  </si>
+  <si>
+    <t>もっと少し和を感じる雰囲気がほしかったですわね。</t>
+    <rPh sb="5" eb="6">
+      <t>ワ</t>
+    </rPh>
+    <rPh sb="7" eb="8">
+      <t>カン</t>
+    </rPh>
+    <rPh sb="10" eb="13">
+      <t>フンイキ</t>
+    </rPh>
+    <phoneticPr fontId="2"/>
+  </si>
+  <si>
+    <t>もう少し、和の、わびさびに工夫が必要そうです。</t>
+    <rPh sb="2" eb="3">
+      <t>スコ</t>
+    </rPh>
+    <rPh sb="5" eb="6">
+      <t>ワ</t>
+    </rPh>
+    <rPh sb="13" eb="15">
+      <t>クフウ</t>
+    </rPh>
+    <rPh sb="16" eb="18">
+      <t>ヒツヨウ</t>
+    </rPh>
+    <phoneticPr fontId="2"/>
+  </si>
+  <si>
+    <t>難しいかもしれませんが、期待しております！</t>
+    <rPh sb="0" eb="1">
+      <t>ムズカ</t>
+    </rPh>
+    <rPh sb="12" eb="14">
+      <t>キタイ</t>
+    </rPh>
+    <phoneticPr fontId="2"/>
+  </si>
+  <si>
+    <t>かなりいい和風感がでていますね！</t>
+    <rPh sb="5" eb="8">
+      <t>ワフウカン</t>
+    </rPh>
+    <phoneticPr fontId="2"/>
+  </si>
+  <si>
+    <t>仕上がりについては、及第点ではないでしょうか。</t>
+    <rPh sb="0" eb="2">
+      <t>シア</t>
+    </rPh>
+    <rPh sb="10" eb="13">
+      <t>キュウダイテン</t>
+    </rPh>
+    <phoneticPr fontId="2"/>
+  </si>
+  <si>
+    <t>あと一つ、抜けたものがあれば・・最高の和風のおかしになりそうです。</t>
+    <rPh sb="2" eb="3">
+      <t>ヒト</t>
+    </rPh>
+    <rPh sb="5" eb="6">
+      <t>ヌ</t>
+    </rPh>
+    <rPh sb="16" eb="18">
+      <t>サイコウ</t>
+    </rPh>
+    <rPh sb="19" eb="21">
+      <t>ワフウ</t>
+    </rPh>
+    <phoneticPr fontId="2"/>
+  </si>
+  <si>
+    <t>この美しさ.. 和風感のある見た目.. とても情緒を感じます。</t>
+    <rPh sb="2" eb="3">
+      <t>ウツク</t>
+    </rPh>
+    <rPh sb="8" eb="10">
+      <t>ワフウ</t>
+    </rPh>
+    <rPh sb="10" eb="11">
+      <t>カン</t>
+    </rPh>
+    <rPh sb="14" eb="15">
+      <t>ミ</t>
+    </rPh>
+    <rPh sb="16" eb="17">
+      <t>メ</t>
+    </rPh>
+    <rPh sb="23" eb="25">
+      <t>ジョウチョ</t>
+    </rPh>
+    <rPh sb="26" eb="27">
+      <t>カン</t>
+    </rPh>
+    <phoneticPr fontId="2"/>
+  </si>
+  <si>
+    <t>わたしのお家に永遠に飾りたいぐらいですわ！　お～ほっほっほ..。</t>
+    <rPh sb="5" eb="6">
+      <t>ウチ</t>
+    </rPh>
+    <rPh sb="7" eb="9">
+      <t>エイエン</t>
+    </rPh>
+    <rPh sb="10" eb="11">
+      <t>カザ</t>
+    </rPh>
+    <phoneticPr fontId="2"/>
+  </si>
+  <si>
+    <t>オリエンタルな雰囲気がでており、よいお菓子だと思います。</t>
+    <rPh sb="7" eb="10">
+      <t>フンイキ</t>
+    </rPh>
+    <rPh sb="19" eb="21">
+      <t>カシ</t>
+    </rPh>
+    <rPh sb="23" eb="24">
+      <t>オモ</t>
+    </rPh>
+    <phoneticPr fontId="2"/>
+  </si>
+  <si>
+    <t>これはまさに、東洋の国.. 京そのものを表現してるといえるでしょう。</t>
+    <rPh sb="7" eb="9">
+      <t>トウヨウ</t>
+    </rPh>
+    <rPh sb="10" eb="11">
+      <t>クニ</t>
+    </rPh>
+    <rPh sb="14" eb="15">
+      <t>キョウ</t>
+    </rPh>
+    <rPh sb="20" eb="22">
+      <t>ヒョウゲン</t>
+    </rPh>
+    <phoneticPr fontId="2"/>
+  </si>
+  <si>
+    <t>以上です。</t>
+    <rPh sb="0" eb="2">
+      <t>イジョウ</t>
+    </rPh>
+    <phoneticPr fontId="2"/>
+  </si>
+  <si>
+    <t>ただ、大人が喜ぶには少し渋さが足りないといったところでしょうか。</t>
+    <rPh sb="3" eb="5">
+      <t>オトナ</t>
+    </rPh>
+    <rPh sb="6" eb="7">
+      <t>ヨロコ</t>
+    </rPh>
+    <rPh sb="10" eb="11">
+      <t>スコ</t>
+    </rPh>
+    <rPh sb="12" eb="13">
+      <t>シブ</t>
+    </rPh>
+    <rPh sb="15" eb="16">
+      <t>タ</t>
+    </rPh>
+    <phoneticPr fontId="2"/>
+  </si>
+  <si>
+    <t>もう少しアダルティさを感じさせる工夫が必要そうです。</t>
+    <rPh sb="2" eb="3">
+      <t>スコ</t>
+    </rPh>
+    <rPh sb="11" eb="12">
+      <t>カン</t>
+    </rPh>
+    <rPh sb="16" eb="18">
+      <t>クフウ</t>
+    </rPh>
+    <rPh sb="19" eb="21">
+      <t>ヒツヨウ</t>
+    </rPh>
+    <phoneticPr fontId="2"/>
+  </si>
+  <si>
+    <t>もう少しメルヘンな夢の世界に仕上げて頂ければ、嬉しいです。</t>
+    <rPh sb="2" eb="3">
+      <t>スコ</t>
+    </rPh>
+    <rPh sb="9" eb="10">
+      <t>ユメ</t>
+    </rPh>
+    <rPh sb="11" eb="13">
+      <t>セカイ</t>
+    </rPh>
+    <rPh sb="14" eb="16">
+      <t>シア</t>
+    </rPh>
+    <rPh sb="18" eb="19">
+      <t>イタダ</t>
+    </rPh>
+    <rPh sb="23" eb="24">
+      <t>ウレ</t>
+    </rPh>
+    <phoneticPr fontId="2"/>
+  </si>
+  <si>
+    <t>もっとメルヘンさが必要ですね。</t>
+    <rPh sb="9" eb="11">
+      <t>ヒツヨウ</t>
+    </rPh>
     <phoneticPr fontId="2"/>
   </si>
 </sst>
@@ -2377,16 +4056,13 @@
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="5">
+  <cellXfs count="4">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1"/>
     <xf numFmtId="0" fontId="1" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1"/>
     <xf numFmtId="0" fontId="0" fillId="4" borderId="0" xfId="0" applyFill="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFill="1">
       <alignment vertical="center"/>
     </xf>
   </cellXfs>
@@ -5458,7 +7134,7 @@
       </c>
     </row>
     <row r="3" spans="1:10" x14ac:dyDescent="0.4">
-      <c r="A3" s="4">
+      <c r="A3">
         <f t="shared" ref="A3:A37" si="0">ROW()-2+20000</f>
         <v>20001</v>
       </c>
@@ -5489,7 +7165,7 @@
       </c>
     </row>
     <row r="4" spans="1:10" x14ac:dyDescent="0.4">
-      <c r="A4" s="4">
+      <c r="A4">
         <f t="shared" si="0"/>
         <v>20002</v>
       </c>
@@ -5520,7 +7196,7 @@
       </c>
     </row>
     <row r="5" spans="1:10" x14ac:dyDescent="0.4">
-      <c r="A5" s="4">
+      <c r="A5">
         <f t="shared" si="0"/>
         <v>20003</v>
       </c>
@@ -5551,7 +7227,7 @@
       </c>
     </row>
     <row r="6" spans="1:10" x14ac:dyDescent="0.4">
-      <c r="A6" s="4">
+      <c r="A6">
         <f t="shared" si="0"/>
         <v>20004</v>
       </c>
@@ -5582,7 +7258,7 @@
       </c>
     </row>
     <row r="7" spans="1:10" x14ac:dyDescent="0.4">
-      <c r="A7" s="4">
+      <c r="A7">
         <f t="shared" si="0"/>
         <v>20005</v>
       </c>
@@ -5613,7 +7289,7 @@
       </c>
     </row>
     <row r="8" spans="1:10" x14ac:dyDescent="0.4">
-      <c r="A8" s="4">
+      <c r="A8">
         <f t="shared" si="0"/>
         <v>20006</v>
       </c>
@@ -5644,7 +7320,7 @@
       </c>
     </row>
     <row r="9" spans="1:10" x14ac:dyDescent="0.4">
-      <c r="A9" s="4">
+      <c r="A9">
         <f t="shared" si="0"/>
         <v>20007</v>
       </c>
@@ -5675,7 +7351,7 @@
       </c>
     </row>
     <row r="10" spans="1:10" x14ac:dyDescent="0.4">
-      <c r="A10" s="4">
+      <c r="A10">
         <f t="shared" si="0"/>
         <v>20008</v>
       </c>
@@ -5706,7 +7382,7 @@
       </c>
     </row>
     <row r="11" spans="1:10" x14ac:dyDescent="0.4">
-      <c r="A11" s="4">
+      <c r="A11">
         <f t="shared" si="0"/>
         <v>20009</v>
       </c>
@@ -5737,7 +7413,7 @@
       </c>
     </row>
     <row r="12" spans="1:10" x14ac:dyDescent="0.4">
-      <c r="A12" s="4">
+      <c r="A12">
         <f t="shared" si="0"/>
         <v>20010</v>
       </c>
@@ -5768,7 +7444,7 @@
       </c>
     </row>
     <row r="13" spans="1:10" x14ac:dyDescent="0.4">
-      <c r="A13" s="4">
+      <c r="A13">
         <f t="shared" si="0"/>
         <v>20011</v>
       </c>
@@ -5832,7 +7508,7 @@
       </c>
     </row>
     <row r="15" spans="1:10" x14ac:dyDescent="0.4">
-      <c r="A15" s="4">
+      <c r="A15">
         <f t="shared" si="0"/>
         <v>20013</v>
       </c>
@@ -5863,7 +7539,7 @@
       </c>
     </row>
     <row r="16" spans="1:10" x14ac:dyDescent="0.4">
-      <c r="A16" s="4">
+      <c r="A16">
         <f t="shared" si="0"/>
         <v>20014</v>
       </c>
@@ -5894,7 +7570,7 @@
       </c>
     </row>
     <row r="17" spans="1:10" x14ac:dyDescent="0.4">
-      <c r="A17" s="4">
+      <c r="A17">
         <f t="shared" si="0"/>
         <v>20015</v>
       </c>
@@ -5925,7 +7601,7 @@
       </c>
     </row>
     <row r="18" spans="1:10" x14ac:dyDescent="0.4">
-      <c r="A18" s="4">
+      <c r="A18">
         <f t="shared" si="0"/>
         <v>20016</v>
       </c>
@@ -5956,7 +7632,7 @@
       </c>
     </row>
     <row r="19" spans="1:10" x14ac:dyDescent="0.4">
-      <c r="A19" s="4">
+      <c r="A19">
         <f t="shared" si="0"/>
         <v>20017</v>
       </c>
@@ -5987,7 +7663,7 @@
       </c>
     </row>
     <row r="20" spans="1:10" x14ac:dyDescent="0.4">
-      <c r="A20" s="4">
+      <c r="A20">
         <f t="shared" si="0"/>
         <v>20018</v>
       </c>
@@ -6018,7 +7694,7 @@
       </c>
     </row>
     <row r="21" spans="1:10" x14ac:dyDescent="0.4">
-      <c r="A21" s="4">
+      <c r="A21">
         <f t="shared" si="0"/>
         <v>20019</v>
       </c>
@@ -6049,7 +7725,7 @@
       </c>
     </row>
     <row r="22" spans="1:10" x14ac:dyDescent="0.4">
-      <c r="A22" s="4">
+      <c r="A22">
         <f t="shared" si="0"/>
         <v>20020</v>
       </c>
@@ -6080,7 +7756,7 @@
       </c>
     </row>
     <row r="23" spans="1:10" x14ac:dyDescent="0.4">
-      <c r="A23" s="4">
+      <c r="A23">
         <f t="shared" si="0"/>
         <v>20021</v>
       </c>
@@ -6111,7 +7787,7 @@
       </c>
     </row>
     <row r="24" spans="1:10" x14ac:dyDescent="0.4">
-      <c r="A24" s="4">
+      <c r="A24">
         <f t="shared" si="0"/>
         <v>20022</v>
       </c>
@@ -6142,7 +7818,7 @@
       </c>
     </row>
     <row r="25" spans="1:10" x14ac:dyDescent="0.4">
-      <c r="A25" s="4">
+      <c r="A25">
         <f t="shared" si="0"/>
         <v>20023</v>
       </c>
@@ -6206,7 +7882,7 @@
       </c>
     </row>
     <row r="27" spans="1:10" x14ac:dyDescent="0.4">
-      <c r="A27" s="4">
+      <c r="A27">
         <f t="shared" si="0"/>
         <v>20025</v>
       </c>
@@ -6237,7 +7913,7 @@
       </c>
     </row>
     <row r="28" spans="1:10" x14ac:dyDescent="0.4">
-      <c r="A28" s="4">
+      <c r="A28">
         <f t="shared" si="0"/>
         <v>20026</v>
       </c>
@@ -6268,7 +7944,7 @@
       </c>
     </row>
     <row r="29" spans="1:10" x14ac:dyDescent="0.4">
-      <c r="A29" s="4">
+      <c r="A29">
         <f t="shared" si="0"/>
         <v>20027</v>
       </c>
@@ -6299,7 +7975,7 @@
       </c>
     </row>
     <row r="30" spans="1:10" x14ac:dyDescent="0.4">
-      <c r="A30" s="4">
+      <c r="A30">
         <f t="shared" si="0"/>
         <v>20028</v>
       </c>
@@ -6330,7 +8006,7 @@
       </c>
     </row>
     <row r="31" spans="1:10" x14ac:dyDescent="0.4">
-      <c r="A31" s="4">
+      <c r="A31">
         <f t="shared" si="0"/>
         <v>20029</v>
       </c>
@@ -6361,7 +8037,7 @@
       </c>
     </row>
     <row r="32" spans="1:10" x14ac:dyDescent="0.4">
-      <c r="A32" s="4">
+      <c r="A32">
         <f t="shared" si="0"/>
         <v>20030</v>
       </c>
@@ -6392,7 +8068,7 @@
       </c>
     </row>
     <row r="33" spans="1:10" x14ac:dyDescent="0.4">
-      <c r="A33" s="4">
+      <c r="A33">
         <f t="shared" si="0"/>
         <v>20031</v>
       </c>
@@ -6423,7 +8099,7 @@
       </c>
     </row>
     <row r="34" spans="1:10" x14ac:dyDescent="0.4">
-      <c r="A34" s="4">
+      <c r="A34">
         <f t="shared" si="0"/>
         <v>20032</v>
       </c>
@@ -6454,7 +8130,7 @@
       </c>
     </row>
     <row r="35" spans="1:10" x14ac:dyDescent="0.4">
-      <c r="A35" s="4">
+      <c r="A35">
         <f t="shared" si="0"/>
         <v>20033</v>
       </c>
@@ -6485,7 +8161,7 @@
       </c>
     </row>
     <row r="36" spans="1:10" x14ac:dyDescent="0.4">
-      <c r="A36" s="4">
+      <c r="A36">
         <f t="shared" si="0"/>
         <v>20034</v>
       </c>
@@ -6516,7 +8192,7 @@
       </c>
     </row>
     <row r="37" spans="1:10" x14ac:dyDescent="0.4">
-      <c r="A37" s="4">
+      <c r="A37">
         <f t="shared" si="0"/>
         <v>20035</v>
       </c>
@@ -6633,12 +8309,12 @@
       </c>
     </row>
     <row r="3" spans="1:10" x14ac:dyDescent="0.4">
-      <c r="A3" s="4">
+      <c r="A3">
         <f t="shared" ref="A3:A13" si="0">ROW()-2+100000</f>
         <v>100001</v>
       </c>
       <c r="B3">
-        <f>INDEX(B:B,MATCH(100000,B:B,0),1)+(ROW()-MATCH(100000,B:B,0))</f>
+        <f t="shared" ref="B3:B13" si="1">INDEX(B:B,MATCH(100000,B:B,0),1)+(ROW()-MATCH(100000,B:B,0))</f>
         <v>100001</v>
       </c>
       <c r="D3">
@@ -6664,12 +8340,12 @@
       </c>
     </row>
     <row r="4" spans="1:10" x14ac:dyDescent="0.4">
-      <c r="A4" s="4">
+      <c r="A4">
         <f t="shared" si="0"/>
         <v>100002</v>
       </c>
       <c r="B4">
-        <f>INDEX(B:B,MATCH(100000,B:B,0),1)+(ROW()-MATCH(100000,B:B,0))</f>
+        <f t="shared" si="1"/>
         <v>100002</v>
       </c>
       <c r="D4">
@@ -6695,12 +8371,12 @@
       </c>
     </row>
     <row r="5" spans="1:10" x14ac:dyDescent="0.4">
-      <c r="A5" s="4">
+      <c r="A5">
         <f t="shared" si="0"/>
         <v>100003</v>
       </c>
       <c r="B5">
-        <f>INDEX(B:B,MATCH(100000,B:B,0),1)+(ROW()-MATCH(100000,B:B,0))</f>
+        <f t="shared" si="1"/>
         <v>100003</v>
       </c>
       <c r="D5">
@@ -6726,12 +8402,12 @@
       </c>
     </row>
     <row r="6" spans="1:10" x14ac:dyDescent="0.4">
-      <c r="A6" s="4">
+      <c r="A6">
         <f t="shared" si="0"/>
         <v>100004</v>
       </c>
       <c r="B6">
-        <f>INDEX(B:B,MATCH(100000,B:B,0),1)+(ROW()-MATCH(100000,B:B,0))</f>
+        <f t="shared" si="1"/>
         <v>100004</v>
       </c>
       <c r="D6">
@@ -6757,12 +8433,12 @@
       </c>
     </row>
     <row r="7" spans="1:10" x14ac:dyDescent="0.4">
-      <c r="A7" s="4">
+      <c r="A7">
         <f t="shared" si="0"/>
         <v>100005</v>
       </c>
       <c r="B7">
-        <f>INDEX(B:B,MATCH(100000,B:B,0),1)+(ROW()-MATCH(100000,B:B,0))</f>
+        <f t="shared" si="1"/>
         <v>100005</v>
       </c>
       <c r="D7">
@@ -6788,12 +8464,12 @@
       </c>
     </row>
     <row r="8" spans="1:10" x14ac:dyDescent="0.4">
-      <c r="A8" s="4">
+      <c r="A8">
         <f t="shared" si="0"/>
         <v>100006</v>
       </c>
       <c r="B8">
-        <f>INDEX(B:B,MATCH(100000,B:B,0),1)+(ROW()-MATCH(100000,B:B,0))</f>
+        <f t="shared" si="1"/>
         <v>100006</v>
       </c>
       <c r="D8">
@@ -6819,12 +8495,12 @@
       </c>
     </row>
     <row r="9" spans="1:10" x14ac:dyDescent="0.4">
-      <c r="A9" s="4">
+      <c r="A9">
         <f t="shared" si="0"/>
         <v>100007</v>
       </c>
       <c r="B9">
-        <f>INDEX(B:B,MATCH(100000,B:B,0),1)+(ROW()-MATCH(100000,B:B,0))</f>
+        <f t="shared" si="1"/>
         <v>100007</v>
       </c>
       <c r="D9">
@@ -6850,12 +8526,12 @@
       </c>
     </row>
     <row r="10" spans="1:10" x14ac:dyDescent="0.4">
-      <c r="A10" s="4">
+      <c r="A10">
         <f t="shared" si="0"/>
         <v>100008</v>
       </c>
       <c r="B10">
-        <f>INDEX(B:B,MATCH(100000,B:B,0),1)+(ROW()-MATCH(100000,B:B,0))</f>
+        <f t="shared" si="1"/>
         <v>100008</v>
       </c>
       <c r="D10">
@@ -6881,12 +8557,12 @@
       </c>
     </row>
     <row r="11" spans="1:10" x14ac:dyDescent="0.4">
-      <c r="A11" s="4">
+      <c r="A11">
         <f t="shared" si="0"/>
         <v>100009</v>
       </c>
       <c r="B11">
-        <f>INDEX(B:B,MATCH(100000,B:B,0),1)+(ROW()-MATCH(100000,B:B,0))</f>
+        <f t="shared" si="1"/>
         <v>100009</v>
       </c>
       <c r="D11">
@@ -6912,12 +8588,12 @@
       </c>
     </row>
     <row r="12" spans="1:10" x14ac:dyDescent="0.4">
-      <c r="A12" s="4">
+      <c r="A12">
         <f t="shared" si="0"/>
         <v>100010</v>
       </c>
       <c r="B12">
-        <f>INDEX(B:B,MATCH(100000,B:B,0),1)+(ROW()-MATCH(100000,B:B,0))</f>
+        <f t="shared" si="1"/>
         <v>100010</v>
       </c>
       <c r="D12">
@@ -6943,12 +8619,12 @@
       </c>
     </row>
     <row r="13" spans="1:10" x14ac:dyDescent="0.4">
-      <c r="A13" s="4">
+      <c r="A13">
         <f t="shared" si="0"/>
         <v>100011</v>
       </c>
       <c r="B13">
-        <f>INDEX(B:B,MATCH(100000,B:B,0),1)+(ROW()-MATCH(100000,B:B,0))</f>
+        <f t="shared" si="1"/>
         <v>100011</v>
       </c>
       <c r="D13">
@@ -6970,6 +8646,1229 @@
         <v>12</v>
       </c>
       <c r="J13">
+        <v>1</v>
+      </c>
+    </row>
+  </sheetData>
+  <phoneticPr fontId="2"/>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <pageSetup paperSize="9" orientation="portrait" horizontalDpi="4294967293" r:id="rId1"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{9500FC91-1FB0-4EAB-8606-F1FAC3BC7200}">
+  <dimension ref="A1:J41"/>
+  <sheetFormatPr defaultRowHeight="18.75" x14ac:dyDescent="0.4"/>
+  <cols>
+    <col min="2" max="2" width="8.75" customWidth="1"/>
+    <col min="3" max="3" width="14" customWidth="1"/>
+    <col min="4" max="4" width="6.375" customWidth="1"/>
+    <col min="5" max="5" width="23.5" customWidth="1"/>
+    <col min="6" max="6" width="22.75" customWidth="1"/>
+    <col min="7" max="7" width="19.5" customWidth="1"/>
+    <col min="8" max="9" width="20.25" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:10" x14ac:dyDescent="0.2">
+      <c r="A1" s="1" t="s">
+        <v>2</v>
+      </c>
+      <c r="B1" s="1" t="s">
+        <v>1</v>
+      </c>
+      <c r="C1" s="1" t="s">
+        <v>0</v>
+      </c>
+      <c r="D1" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="E1" s="1" t="s">
+        <v>4</v>
+      </c>
+      <c r="F1" s="1" t="s">
+        <v>5</v>
+      </c>
+      <c r="G1" s="1" t="s">
+        <v>6</v>
+      </c>
+      <c r="H1" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="I1" s="1" t="s">
+        <v>8</v>
+      </c>
+      <c r="J1" s="2" t="s">
+        <v>199</v>
+      </c>
+    </row>
+    <row r="2" spans="1:10" s="3" customFormat="1" x14ac:dyDescent="0.4">
+      <c r="A2">
+        <f>ROW()-2+1000000</f>
+        <v>1000000</v>
+      </c>
+      <c r="B2" s="3">
+        <v>1000100</v>
+      </c>
+      <c r="C2" s="3" t="s">
+        <v>203</v>
+      </c>
+      <c r="D2" s="3">
+        <v>0</v>
+      </c>
+      <c r="E2" s="3" t="s">
+        <v>208</v>
+      </c>
+      <c r="F2" s="3" t="s">
+        <v>232</v>
+      </c>
+      <c r="G2" s="3" t="s">
+        <v>233</v>
+      </c>
+      <c r="H2" s="3" t="s">
+        <v>234</v>
+      </c>
+      <c r="I2" s="3" t="s">
+        <v>212</v>
+      </c>
+      <c r="J2" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="3" spans="1:10" x14ac:dyDescent="0.4">
+      <c r="A3">
+        <f t="shared" ref="A3:A41" si="0">ROW()-2+1000000</f>
+        <v>1000001</v>
+      </c>
+      <c r="B3">
+        <f>INDEX(B:B,MATCH(1000100,B:B,0),1)+(ROW()-MATCH(1000100,B:B,0))</f>
+        <v>1000101</v>
+      </c>
+      <c r="D3">
+        <v>1</v>
+      </c>
+      <c r="E3" t="s">
+        <v>228</v>
+      </c>
+      <c r="F3" t="s">
+        <v>229</v>
+      </c>
+      <c r="G3" t="s">
+        <v>230</v>
+      </c>
+      <c r="H3" t="s">
+        <v>231</v>
+      </c>
+      <c r="J3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="4" spans="1:10" x14ac:dyDescent="0.4">
+      <c r="A4">
+        <f t="shared" si="0"/>
+        <v>1000002</v>
+      </c>
+      <c r="B4">
+        <f t="shared" ref="B4:B5" si="1">INDEX(B:B,MATCH(1000100,B:B,0),1)+(ROW()-MATCH(1000100,B:B,0))</f>
+        <v>1000102</v>
+      </c>
+      <c r="D4">
+        <v>2</v>
+      </c>
+      <c r="E4" t="s">
+        <v>226</v>
+      </c>
+      <c r="F4" t="s">
+        <v>238</v>
+      </c>
+      <c r="G4" t="s">
+        <v>227</v>
+      </c>
+      <c r="H4" t="s">
+        <v>202</v>
+      </c>
+      <c r="J4">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="5" spans="1:10" x14ac:dyDescent="0.4">
+      <c r="A5">
+        <f t="shared" si="0"/>
+        <v>1000003</v>
+      </c>
+      <c r="B5">
+        <f t="shared" si="1"/>
+        <v>1000103</v>
+      </c>
+      <c r="D5">
+        <v>3</v>
+      </c>
+      <c r="E5" t="s">
+        <v>299</v>
+      </c>
+      <c r="F5" t="s">
+        <v>223</v>
+      </c>
+      <c r="G5" t="s">
+        <v>224</v>
+      </c>
+      <c r="H5" t="s">
+        <v>225</v>
+      </c>
+      <c r="J5">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="6" spans="1:10" s="3" customFormat="1" x14ac:dyDescent="0.4">
+      <c r="A6">
+        <f>ROW()-2+1000000</f>
+        <v>1000004</v>
+      </c>
+      <c r="B6" s="3">
+        <v>1000200</v>
+      </c>
+      <c r="C6" s="3" t="s">
+        <v>203</v>
+      </c>
+      <c r="D6" s="3">
+        <v>0</v>
+      </c>
+      <c r="E6" s="3" t="s">
+        <v>208</v>
+      </c>
+      <c r="F6" s="3" t="s">
+        <v>242</v>
+      </c>
+      <c r="G6" s="3" t="s">
+        <v>243</v>
+      </c>
+      <c r="H6" s="3" t="s">
+        <v>244</v>
+      </c>
+      <c r="I6" s="3" t="s">
+        <v>213</v>
+      </c>
+      <c r="J6" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="7" spans="1:10" x14ac:dyDescent="0.4">
+      <c r="A7">
+        <f t="shared" si="0"/>
+        <v>1000005</v>
+      </c>
+      <c r="B7">
+        <f>INDEX(B:B,MATCH(1000200,B:B,0),1)+(ROW()-MATCH(1000200,B:B,0))</f>
+        <v>1000201</v>
+      </c>
+      <c r="D7">
+        <v>1</v>
+      </c>
+      <c r="E7" t="s">
+        <v>239</v>
+      </c>
+      <c r="F7" t="s">
+        <v>240</v>
+      </c>
+      <c r="G7" t="s">
+        <v>241</v>
+      </c>
+      <c r="H7" t="s">
+        <v>231</v>
+      </c>
+      <c r="J7">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="8" spans="1:10" x14ac:dyDescent="0.4">
+      <c r="A8">
+        <f t="shared" si="0"/>
+        <v>1000006</v>
+      </c>
+      <c r="B8">
+        <f t="shared" ref="B8:B9" si="2">INDEX(B:B,MATCH(1000200,B:B,0),1)+(ROW()-MATCH(1000200,B:B,0))</f>
+        <v>1000202</v>
+      </c>
+      <c r="D8">
+        <v>2</v>
+      </c>
+      <c r="E8" t="s">
+        <v>226</v>
+      </c>
+      <c r="F8" t="s">
+        <v>237</v>
+      </c>
+      <c r="G8" t="s">
+        <v>227</v>
+      </c>
+      <c r="H8" t="s">
+        <v>202</v>
+      </c>
+      <c r="J8">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="9" spans="1:10" x14ac:dyDescent="0.4">
+      <c r="A9">
+        <f t="shared" si="0"/>
+        <v>1000007</v>
+      </c>
+      <c r="B9">
+        <f t="shared" si="2"/>
+        <v>1000203</v>
+      </c>
+      <c r="D9">
+        <v>3</v>
+      </c>
+      <c r="E9" t="s">
+        <v>300</v>
+      </c>
+      <c r="F9" t="s">
+        <v>235</v>
+      </c>
+      <c r="G9" t="s">
+        <v>236</v>
+      </c>
+      <c r="H9" t="s">
+        <v>225</v>
+      </c>
+      <c r="J9">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="10" spans="1:10" s="3" customFormat="1" x14ac:dyDescent="0.4">
+      <c r="A10">
+        <f>ROW()-2+1000000</f>
+        <v>1000008</v>
+      </c>
+      <c r="B10" s="3">
+        <v>1000300</v>
+      </c>
+      <c r="C10" s="3" t="s">
+        <v>203</v>
+      </c>
+      <c r="D10" s="3">
+        <v>0</v>
+      </c>
+      <c r="E10" s="3" t="s">
+        <v>208</v>
+      </c>
+      <c r="F10" s="3" t="s">
+        <v>254</v>
+      </c>
+      <c r="G10" s="3" t="s">
+        <v>255</v>
+      </c>
+      <c r="H10" s="3" t="s">
+        <v>256</v>
+      </c>
+      <c r="I10" s="3" t="s">
+        <v>214</v>
+      </c>
+      <c r="J10" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="11" spans="1:10" x14ac:dyDescent="0.4">
+      <c r="A11">
+        <f t="shared" si="0"/>
+        <v>1000009</v>
+      </c>
+      <c r="B11">
+        <f>INDEX(B:B,MATCH(1000300,B:B,0),1)+(ROW()-MATCH(1000300,B:B,0))</f>
+        <v>1000301</v>
+      </c>
+      <c r="D11">
+        <v>1</v>
+      </c>
+      <c r="E11" t="s">
+        <v>251</v>
+      </c>
+      <c r="F11" t="s">
+        <v>252</v>
+      </c>
+      <c r="G11" t="s">
+        <v>206</v>
+      </c>
+      <c r="H11" t="s">
+        <v>253</v>
+      </c>
+      <c r="J11">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="12" spans="1:10" x14ac:dyDescent="0.4">
+      <c r="A12">
+        <f t="shared" si="0"/>
+        <v>1000010</v>
+      </c>
+      <c r="B12">
+        <f t="shared" ref="B12:B13" si="3">INDEX(B:B,MATCH(1000300,B:B,0),1)+(ROW()-MATCH(1000300,B:B,0))</f>
+        <v>1000302</v>
+      </c>
+      <c r="D12">
+        <v>2</v>
+      </c>
+      <c r="E12" t="s">
+        <v>23</v>
+      </c>
+      <c r="F12" t="s">
+        <v>248</v>
+      </c>
+      <c r="G12" t="s">
+        <v>249</v>
+      </c>
+      <c r="H12" t="s">
+        <v>250</v>
+      </c>
+      <c r="J12">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="13" spans="1:10" x14ac:dyDescent="0.4">
+      <c r="A13">
+        <f t="shared" si="0"/>
+        <v>1000011</v>
+      </c>
+      <c r="B13">
+        <f t="shared" si="3"/>
+        <v>1000303</v>
+      </c>
+      <c r="D13">
+        <v>3</v>
+      </c>
+      <c r="E13" t="s">
+        <v>301</v>
+      </c>
+      <c r="F13" t="s">
+        <v>245</v>
+      </c>
+      <c r="G13" t="s">
+        <v>246</v>
+      </c>
+      <c r="H13" t="s">
+        <v>247</v>
+      </c>
+      <c r="J13">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="14" spans="1:10" s="3" customFormat="1" x14ac:dyDescent="0.4">
+      <c r="A14">
+        <f>ROW()-2+1000000</f>
+        <v>1000012</v>
+      </c>
+      <c r="B14" s="3">
+        <v>1000400</v>
+      </c>
+      <c r="C14" s="3" t="s">
+        <v>203</v>
+      </c>
+      <c r="D14" s="3">
+        <v>0</v>
+      </c>
+      <c r="E14" s="3" t="s">
+        <v>208</v>
+      </c>
+      <c r="F14" s="3" t="s">
+        <v>266</v>
+      </c>
+      <c r="G14" s="3" t="s">
+        <v>267</v>
+      </c>
+      <c r="H14" s="3" t="s">
+        <v>18</v>
+      </c>
+      <c r="I14" s="3" t="s">
+        <v>215</v>
+      </c>
+      <c r="J14" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="15" spans="1:10" x14ac:dyDescent="0.4">
+      <c r="A15">
+        <f t="shared" si="0"/>
+        <v>1000013</v>
+      </c>
+      <c r="B15">
+        <f>INDEX(B:B,MATCH(1000400,B:B,0),1)+(ROW()-MATCH(1000400,B:B,0))</f>
+        <v>1000401</v>
+      </c>
+      <c r="D15">
+        <v>1</v>
+      </c>
+      <c r="E15" t="s">
+        <v>262</v>
+      </c>
+      <c r="F15" t="s">
+        <v>263</v>
+      </c>
+      <c r="G15" t="s">
+        <v>264</v>
+      </c>
+      <c r="H15" t="s">
+        <v>265</v>
+      </c>
+      <c r="J15">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="16" spans="1:10" x14ac:dyDescent="0.4">
+      <c r="A16">
+        <f t="shared" si="0"/>
+        <v>1000014</v>
+      </c>
+      <c r="B16">
+        <f t="shared" ref="B16:B17" si="4">INDEX(B:B,MATCH(1000400,B:B,0),1)+(ROW()-MATCH(1000400,B:B,0))</f>
+        <v>1000402</v>
+      </c>
+      <c r="D16">
+        <v>2</v>
+      </c>
+      <c r="E16" t="s">
+        <v>23</v>
+      </c>
+      <c r="F16" t="s">
+        <v>259</v>
+      </c>
+      <c r="G16" t="s">
+        <v>260</v>
+      </c>
+      <c r="H16" t="s">
+        <v>261</v>
+      </c>
+      <c r="J16">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="17" spans="1:10" x14ac:dyDescent="0.4">
+      <c r="A17">
+        <f t="shared" si="0"/>
+        <v>1000015</v>
+      </c>
+      <c r="B17">
+        <f t="shared" si="4"/>
+        <v>1000403</v>
+      </c>
+      <c r="D17">
+        <v>3</v>
+      </c>
+      <c r="E17" t="s">
+        <v>302</v>
+      </c>
+      <c r="F17" t="s">
+        <v>257</v>
+      </c>
+      <c r="G17" t="s">
+        <v>258</v>
+      </c>
+      <c r="H17" t="s">
+        <v>202</v>
+      </c>
+      <c r="J17">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="18" spans="1:10" s="3" customFormat="1" x14ac:dyDescent="0.4">
+      <c r="A18">
+        <f>ROW()-2+1000000</f>
+        <v>1000016</v>
+      </c>
+      <c r="B18" s="3">
+        <v>1000500</v>
+      </c>
+      <c r="C18" s="3" t="s">
+        <v>203</v>
+      </c>
+      <c r="D18" s="3">
+        <v>0</v>
+      </c>
+      <c r="E18" s="3" t="s">
+        <v>208</v>
+      </c>
+      <c r="F18" s="3" t="s">
+        <v>275</v>
+      </c>
+      <c r="G18" s="3" t="s">
+        <v>276</v>
+      </c>
+      <c r="H18" s="3" t="s">
+        <v>277</v>
+      </c>
+      <c r="I18" s="3" t="s">
+        <v>216</v>
+      </c>
+      <c r="J18" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="19" spans="1:10" x14ac:dyDescent="0.4">
+      <c r="A19">
+        <f t="shared" si="0"/>
+        <v>1000017</v>
+      </c>
+      <c r="B19">
+        <f>INDEX(B:B,MATCH(1000500,B:B,0),1)+(ROW()-MATCH(1000500,B:B,0))</f>
+        <v>1000501</v>
+      </c>
+      <c r="D19">
+        <v>1</v>
+      </c>
+      <c r="E19" t="s">
+        <v>271</v>
+      </c>
+      <c r="F19" t="s">
+        <v>272</v>
+      </c>
+      <c r="G19" t="s">
+        <v>273</v>
+      </c>
+      <c r="H19" t="s">
+        <v>274</v>
+      </c>
+      <c r="J19">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="20" spans="1:10" x14ac:dyDescent="0.4">
+      <c r="A20">
+        <f t="shared" si="0"/>
+        <v>1000018</v>
+      </c>
+      <c r="B20">
+        <f>INDEX(B:B,MATCH(1000500,B:B,0),1)+(ROW()-MATCH(1000500,B:B,0))</f>
+        <v>1000502</v>
+      </c>
+      <c r="D20">
+        <v>2</v>
+      </c>
+      <c r="E20" t="s">
+        <v>23</v>
+      </c>
+      <c r="F20" t="s">
+        <v>332</v>
+      </c>
+      <c r="G20" t="s">
+        <v>333</v>
+      </c>
+      <c r="H20" t="s">
+        <v>247</v>
+      </c>
+      <c r="J20">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="21" spans="1:10" x14ac:dyDescent="0.4">
+      <c r="A21">
+        <f t="shared" si="0"/>
+        <v>1000019</v>
+      </c>
+      <c r="B21">
+        <f>INDEX(B:B,MATCH(1000500,B:B,0),1)+(ROW()-MATCH(1000500,B:B,0))</f>
+        <v>1000503</v>
+      </c>
+      <c r="D21">
+        <v>3</v>
+      </c>
+      <c r="E21" t="s">
+        <v>303</v>
+      </c>
+      <c r="F21" t="s">
+        <v>268</v>
+      </c>
+      <c r="G21" t="s">
+        <v>269</v>
+      </c>
+      <c r="H21" t="s">
+        <v>202</v>
+      </c>
+      <c r="J21">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="22" spans="1:10" s="3" customFormat="1" x14ac:dyDescent="0.4">
+      <c r="A22">
+        <f>ROW()-2+1000000</f>
+        <v>1000020</v>
+      </c>
+      <c r="B22" s="3">
+        <v>1000600</v>
+      </c>
+      <c r="C22" s="3" t="s">
+        <v>203</v>
+      </c>
+      <c r="D22" s="3">
+        <v>0</v>
+      </c>
+      <c r="E22" s="3" t="s">
+        <v>208</v>
+      </c>
+      <c r="F22" s="3" t="s">
+        <v>209</v>
+      </c>
+      <c r="G22" s="3" t="s">
+        <v>210</v>
+      </c>
+      <c r="H22" s="3" t="s">
+        <v>18</v>
+      </c>
+      <c r="I22" s="3" t="s">
+        <v>211</v>
+      </c>
+      <c r="J22" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="23" spans="1:10" x14ac:dyDescent="0.4">
+      <c r="A23">
+        <f t="shared" si="0"/>
+        <v>1000021</v>
+      </c>
+      <c r="B23">
+        <f>INDEX(B:B,MATCH(1000600,B:B,0),1)+(ROW()-MATCH(1000600,B:B,0))</f>
+        <v>1000601</v>
+      </c>
+      <c r="D23">
+        <v>1</v>
+      </c>
+      <c r="E23" t="s">
+        <v>204</v>
+      </c>
+      <c r="F23" t="s">
+        <v>205</v>
+      </c>
+      <c r="G23" t="s">
+        <v>206</v>
+      </c>
+      <c r="H23" t="s">
+        <v>207</v>
+      </c>
+      <c r="J23">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="24" spans="1:10" x14ac:dyDescent="0.4">
+      <c r="A24">
+        <f t="shared" si="0"/>
+        <v>1000022</v>
+      </c>
+      <c r="B24">
+        <f t="shared" ref="B24:B25" si="5">INDEX(B:B,MATCH(1000600,B:B,0),1)+(ROW()-MATCH(1000600,B:B,0))</f>
+        <v>1000602</v>
+      </c>
+      <c r="D24">
+        <v>2</v>
+      </c>
+      <c r="E24" t="s">
+        <v>221</v>
+      </c>
+      <c r="F24" t="s">
+        <v>222</v>
+      </c>
+      <c r="G24" t="s">
+        <v>270</v>
+      </c>
+      <c r="H24" t="s">
+        <v>331</v>
+      </c>
+      <c r="J24">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="25" spans="1:10" x14ac:dyDescent="0.4">
+      <c r="A25">
+        <f t="shared" si="0"/>
+        <v>1000023</v>
+      </c>
+      <c r="B25">
+        <f t="shared" si="5"/>
+        <v>1000603</v>
+      </c>
+      <c r="D25">
+        <v>3</v>
+      </c>
+      <c r="E25" t="s">
+        <v>304</v>
+      </c>
+      <c r="F25" t="s">
+        <v>200</v>
+      </c>
+      <c r="G25" t="s">
+        <v>201</v>
+      </c>
+      <c r="H25" t="s">
+        <v>202</v>
+      </c>
+      <c r="J25">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="26" spans="1:10" s="3" customFormat="1" x14ac:dyDescent="0.4">
+      <c r="A26">
+        <f>ROW()-2+1000000</f>
+        <v>1000024</v>
+      </c>
+      <c r="B26" s="3">
+        <v>1000700</v>
+      </c>
+      <c r="C26" s="3" t="s">
+        <v>203</v>
+      </c>
+      <c r="D26" s="3">
+        <v>0</v>
+      </c>
+      <c r="E26" s="3" t="s">
+        <v>208</v>
+      </c>
+      <c r="F26" s="3" t="s">
+        <v>285</v>
+      </c>
+      <c r="G26" s="3" t="s">
+        <v>286</v>
+      </c>
+      <c r="H26" s="3" t="s">
+        <v>287</v>
+      </c>
+      <c r="I26" s="3" t="s">
+        <v>217</v>
+      </c>
+      <c r="J26" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="27" spans="1:10" x14ac:dyDescent="0.4">
+      <c r="A27">
+        <f t="shared" si="0"/>
+        <v>1000025</v>
+      </c>
+      <c r="B27">
+        <f>INDEX(B:B,MATCH(1000700,B:B,0),1)+(ROW()-MATCH(1000700,B:B,0))</f>
+        <v>1000701</v>
+      </c>
+      <c r="D27">
+        <v>1</v>
+      </c>
+      <c r="E27" t="s">
+        <v>281</v>
+      </c>
+      <c r="F27" t="s">
+        <v>282</v>
+      </c>
+      <c r="G27" t="s">
+        <v>283</v>
+      </c>
+      <c r="H27" t="s">
+        <v>284</v>
+      </c>
+      <c r="J27">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="28" spans="1:10" x14ac:dyDescent="0.4">
+      <c r="A28">
+        <f t="shared" si="0"/>
+        <v>1000026</v>
+      </c>
+      <c r="B28">
+        <f t="shared" ref="B28:B29" si="6">INDEX(B:B,MATCH(1000700,B:B,0),1)+(ROW()-MATCH(1000700,B:B,0))</f>
+        <v>1000702</v>
+      </c>
+      <c r="D28">
+        <v>2</v>
+      </c>
+      <c r="E28" t="s">
+        <v>23</v>
+      </c>
+      <c r="F28" t="s">
+        <v>279</v>
+      </c>
+      <c r="G28" t="s">
+        <v>334</v>
+      </c>
+      <c r="H28" t="s">
+        <v>280</v>
+      </c>
+      <c r="J28">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="29" spans="1:10" x14ac:dyDescent="0.4">
+      <c r="A29">
+        <f t="shared" si="0"/>
+        <v>1000027</v>
+      </c>
+      <c r="B29">
+        <f t="shared" si="6"/>
+        <v>1000703</v>
+      </c>
+      <c r="D29">
+        <v>3</v>
+      </c>
+      <c r="E29" t="s">
+        <v>305</v>
+      </c>
+      <c r="F29" t="s">
+        <v>278</v>
+      </c>
+      <c r="G29" t="s">
+        <v>335</v>
+      </c>
+      <c r="H29" t="s">
+        <v>202</v>
+      </c>
+      <c r="J29">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="30" spans="1:10" s="3" customFormat="1" x14ac:dyDescent="0.4">
+      <c r="A30">
+        <f>ROW()-2+1000000</f>
+        <v>1000028</v>
+      </c>
+      <c r="B30" s="3">
+        <v>1000800</v>
+      </c>
+      <c r="C30" s="3" t="s">
+        <v>203</v>
+      </c>
+      <c r="D30" s="3">
+        <v>0</v>
+      </c>
+      <c r="E30" s="3" t="s">
+        <v>208</v>
+      </c>
+      <c r="F30" s="3" t="s">
+        <v>296</v>
+      </c>
+      <c r="G30" s="3" t="s">
+        <v>297</v>
+      </c>
+      <c r="H30" s="3" t="s">
+        <v>298</v>
+      </c>
+      <c r="I30" s="3" t="s">
+        <v>218</v>
+      </c>
+      <c r="J30" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="31" spans="1:10" x14ac:dyDescent="0.4">
+      <c r="A31">
+        <f t="shared" si="0"/>
+        <v>1000029</v>
+      </c>
+      <c r="B31">
+        <f>INDEX(B:B,MATCH(1000800,B:B,0),1)+(ROW()-MATCH(1000800,B:B,0))</f>
+        <v>1000801</v>
+      </c>
+      <c r="D31">
+        <v>1</v>
+      </c>
+      <c r="E31" t="s">
+        <v>292</v>
+      </c>
+      <c r="F31" t="s">
+        <v>293</v>
+      </c>
+      <c r="G31" t="s">
+        <v>294</v>
+      </c>
+      <c r="H31" t="s">
+        <v>295</v>
+      </c>
+      <c r="J31">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="32" spans="1:10" x14ac:dyDescent="0.4">
+      <c r="A32">
+        <f t="shared" si="0"/>
+        <v>1000030</v>
+      </c>
+      <c r="B32">
+        <f t="shared" ref="B32:B33" si="7">INDEX(B:B,MATCH(1000800,B:B,0),1)+(ROW()-MATCH(1000800,B:B,0))</f>
+        <v>1000802</v>
+      </c>
+      <c r="D32">
+        <v>2</v>
+      </c>
+      <c r="E32" t="s">
+        <v>23</v>
+      </c>
+      <c r="F32" t="s">
+        <v>290</v>
+      </c>
+      <c r="G32" t="s">
+        <v>291</v>
+      </c>
+      <c r="H32" t="s">
+        <v>247</v>
+      </c>
+      <c r="J32">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="33" spans="1:10" x14ac:dyDescent="0.4">
+      <c r="A33">
+        <f t="shared" si="0"/>
+        <v>1000031</v>
+      </c>
+      <c r="B33">
+        <f t="shared" si="7"/>
+        <v>1000803</v>
+      </c>
+      <c r="D33">
+        <v>3</v>
+      </c>
+      <c r="E33" t="s">
+        <v>309</v>
+      </c>
+      <c r="F33" t="s">
+        <v>289</v>
+      </c>
+      <c r="G33" t="s">
+        <v>288</v>
+      </c>
+      <c r="H33" t="s">
+        <v>202</v>
+      </c>
+      <c r="J33">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="34" spans="1:10" s="3" customFormat="1" x14ac:dyDescent="0.4">
+      <c r="A34">
+        <f>ROW()-2+1000000</f>
+        <v>1000032</v>
+      </c>
+      <c r="B34" s="3">
+        <v>1000900</v>
+      </c>
+      <c r="C34" s="3" t="s">
+        <v>203</v>
+      </c>
+      <c r="D34" s="3">
+        <v>0</v>
+      </c>
+      <c r="E34" s="3" t="s">
+        <v>208</v>
+      </c>
+      <c r="F34" s="3" t="s">
+        <v>316</v>
+      </c>
+      <c r="G34" s="3" t="s">
+        <v>317</v>
+      </c>
+      <c r="H34" s="3" t="s">
+        <v>18</v>
+      </c>
+      <c r="I34" s="3" t="s">
+        <v>219</v>
+      </c>
+      <c r="J34" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="35" spans="1:10" x14ac:dyDescent="0.4">
+      <c r="A35">
+        <f t="shared" si="0"/>
+        <v>1000033</v>
+      </c>
+      <c r="B35">
+        <f>INDEX(B:B,MATCH(1000900,B:B,0),1)+(ROW()-MATCH(1000900,B:B,0))</f>
+        <v>1000901</v>
+      </c>
+      <c r="D35">
+        <v>1</v>
+      </c>
+      <c r="E35" t="s">
+        <v>312</v>
+      </c>
+      <c r="F35" t="s">
+        <v>313</v>
+      </c>
+      <c r="G35" t="s">
+        <v>314</v>
+      </c>
+      <c r="H35" t="s">
+        <v>315</v>
+      </c>
+      <c r="J35">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="36" spans="1:10" x14ac:dyDescent="0.4">
+      <c r="A36">
+        <f t="shared" si="0"/>
+        <v>1000034</v>
+      </c>
+      <c r="B36">
+        <f t="shared" ref="B36:B37" si="8">INDEX(B:B,MATCH(1000900,B:B,0),1)+(ROW()-MATCH(1000900,B:B,0))</f>
+        <v>1000902</v>
+      </c>
+      <c r="D36">
+        <v>2</v>
+      </c>
+      <c r="E36" t="s">
+        <v>23</v>
+      </c>
+      <c r="F36" t="s">
+        <v>310</v>
+      </c>
+      <c r="G36" t="s">
+        <v>311</v>
+      </c>
+      <c r="H36" t="s">
+        <v>261</v>
+      </c>
+      <c r="J36">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="37" spans="1:10" x14ac:dyDescent="0.4">
+      <c r="A37">
+        <f t="shared" si="0"/>
+        <v>1000035</v>
+      </c>
+      <c r="B37">
+        <f t="shared" si="8"/>
+        <v>1000903</v>
+      </c>
+      <c r="D37">
+        <v>3</v>
+      </c>
+      <c r="E37" t="s">
+        <v>306</v>
+      </c>
+      <c r="F37" t="s">
+        <v>307</v>
+      </c>
+      <c r="G37" t="s">
+        <v>308</v>
+      </c>
+      <c r="H37" t="s">
+        <v>202</v>
+      </c>
+      <c r="J37">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="38" spans="1:10" s="3" customFormat="1" x14ac:dyDescent="0.4">
+      <c r="A38">
+        <f>ROW()-2+1000000</f>
+        <v>1000036</v>
+      </c>
+      <c r="B38" s="3">
+        <v>1001000</v>
+      </c>
+      <c r="C38" s="3" t="s">
+        <v>203</v>
+      </c>
+      <c r="D38" s="3">
+        <v>0</v>
+      </c>
+      <c r="E38" s="3" t="s">
+        <v>208</v>
+      </c>
+      <c r="F38" s="3" t="s">
+        <v>327</v>
+      </c>
+      <c r="G38" s="3" t="s">
+        <v>330</v>
+      </c>
+      <c r="H38" s="3" t="s">
+        <v>328</v>
+      </c>
+      <c r="I38" s="3" t="s">
+        <v>220</v>
+      </c>
+      <c r="J38" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="39" spans="1:10" x14ac:dyDescent="0.4">
+      <c r="A39">
+        <f t="shared" si="0"/>
+        <v>1000037</v>
+      </c>
+      <c r="B39">
+        <f>INDEX(B:B,MATCH(1001000,B:B,0),1)+(ROW()-MATCH(1001000,B:B,0))</f>
+        <v>1001001</v>
+      </c>
+      <c r="D39">
+        <v>1</v>
+      </c>
+      <c r="E39" t="s">
+        <v>324</v>
+      </c>
+      <c r="F39" t="s">
+        <v>329</v>
+      </c>
+      <c r="G39" t="s">
+        <v>325</v>
+      </c>
+      <c r="H39" t="s">
+        <v>326</v>
+      </c>
+      <c r="J39">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="40" spans="1:10" x14ac:dyDescent="0.4">
+      <c r="A40">
+        <f t="shared" si="0"/>
+        <v>1000038</v>
+      </c>
+      <c r="B40">
+        <f t="shared" ref="B40:B41" si="9">INDEX(B:B,MATCH(1001000,B:B,0),1)+(ROW()-MATCH(1001000,B:B,0))</f>
+        <v>1001002</v>
+      </c>
+      <c r="D40">
+        <v>2</v>
+      </c>
+      <c r="E40" t="s">
+        <v>23</v>
+      </c>
+      <c r="F40" t="s">
+        <v>320</v>
+      </c>
+      <c r="G40" t="s">
+        <v>322</v>
+      </c>
+      <c r="H40" t="s">
+        <v>323</v>
+      </c>
+      <c r="J40">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="41" spans="1:10" x14ac:dyDescent="0.4">
+      <c r="A41">
+        <f t="shared" si="0"/>
+        <v>1000039</v>
+      </c>
+      <c r="B41">
+        <f t="shared" si="9"/>
+        <v>1001003</v>
+      </c>
+      <c r="D41">
+        <v>3</v>
+      </c>
+      <c r="E41" t="s">
+        <v>318</v>
+      </c>
+      <c r="F41" t="s">
+        <v>319</v>
+      </c>
+      <c r="G41" t="s">
+        <v>321</v>
+      </c>
+      <c r="H41" t="s">
+        <v>247</v>
+      </c>
+      <c r="J41">
         <v>1</v>
       </c>
     </row>

--- a/Assets/Resources/Excel/Entity_ContestCommentDataBase.xlsx
+++ b/Assets/Resources/Excel/Entity_ContestCommentDataBase.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="28526"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29231"/>
   <workbookPr defaultThemeVersion="166925"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\aritashogo\Documents\Unity\Okashi_Atlier2\Assets\Resources\Excel\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{FE68621D-2C55-4991-ACF4-21B6AF3DB205}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{0AB64A4F-07B3-4F5C-97FE-29FAE15B5212}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="2025" yWindow="900" windowWidth="25560" windowHeight="14325" firstSheet="1" activeTab="2" xr2:uid="{1DCE2773-8A3B-4011-B3F4-E2EABC03DB8B}"/>
+    <workbookView xWindow="915" yWindow="390" windowWidth="25485" windowHeight="14370" activeTab="2" xr2:uid="{1DCE2773-8A3B-4011-B3F4-E2EABC03DB8B}"/>
   </bookViews>
   <sheets>
     <sheet name="01_ContestComment" sheetId="1" r:id="rId1"/>
@@ -36,7 +36,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="891" uniqueCount="336">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1013" uniqueCount="383">
   <si>
     <t>item_Name</t>
     <phoneticPr fontId="3"/>
@@ -3979,6 +3979,617 @@
     <t>もっとメルヘンさが必要ですね。</t>
     <rPh sb="9" eb="11">
       <t>ヒツヨウ</t>
+    </rPh>
+    <phoneticPr fontId="2"/>
+  </si>
+  <si>
+    <t>Coffee_Default</t>
+    <phoneticPr fontId="2"/>
+  </si>
+  <si>
+    <t>・・胸にすくような、この味わい深い香り。</t>
+    <rPh sb="2" eb="3">
+      <t>ムネ</t>
+    </rPh>
+    <rPh sb="12" eb="13">
+      <t>アジ</t>
+    </rPh>
+    <rPh sb="15" eb="16">
+      <t>ブカ</t>
+    </rPh>
+    <rPh sb="17" eb="18">
+      <t>カオ</t>
+    </rPh>
+    <phoneticPr fontId="2"/>
+  </si>
+  <si>
+    <t>う～ん、とてもいい香りじゃ。</t>
+    <rPh sb="9" eb="10">
+      <t>カオ</t>
+    </rPh>
+    <phoneticPr fontId="2"/>
+  </si>
+  <si>
+    <t>..どこか懐かしい、癒される香り。神の香りじゃ！</t>
+    <rPh sb="5" eb="6">
+      <t>ナツ</t>
+    </rPh>
+    <rPh sb="10" eb="11">
+      <t>イヤ</t>
+    </rPh>
+    <rPh sb="14" eb="15">
+      <t>カオ</t>
+    </rPh>
+    <rPh sb="17" eb="18">
+      <t>カミ</t>
+    </rPh>
+    <rPh sb="19" eb="20">
+      <t>カオ</t>
+    </rPh>
+    <phoneticPr fontId="2"/>
+  </si>
+  <si>
+    <t>うむ。</t>
+    <phoneticPr fontId="2"/>
+  </si>
+  <si>
+    <t>芳醇な香り。まさに、お菓子にぴったりじゃろう。</t>
+    <rPh sb="0" eb="2">
+      <t>ホウジュン</t>
+    </rPh>
+    <rPh sb="3" eb="4">
+      <t>カオ</t>
+    </rPh>
+    <rPh sb="11" eb="13">
+      <t>カシ</t>
+    </rPh>
+    <phoneticPr fontId="2"/>
+  </si>
+  <si>
+    <t>しいていえばもう一つ、香りに味わい深さが欲しいところかの。</t>
+    <rPh sb="8" eb="9">
+      <t>ヒト</t>
+    </rPh>
+    <rPh sb="11" eb="12">
+      <t>カオ</t>
+    </rPh>
+    <rPh sb="14" eb="15">
+      <t>アジ</t>
+    </rPh>
+    <rPh sb="17" eb="18">
+      <t>ブカ</t>
+    </rPh>
+    <rPh sb="20" eb="21">
+      <t>ホ</t>
+    </rPh>
+    <phoneticPr fontId="2"/>
+  </si>
+  <si>
+    <t>さすがは、アイツの息子.. といったところじゃ。</t>
+    <phoneticPr fontId="2"/>
+  </si>
+  <si>
+    <t>ふむむ..。</t>
+    <phoneticPr fontId="2"/>
+  </si>
+  <si>
+    <t>うむ。悪くはないが。..まだ少し素材本来の香りが足りていないようじゃ。</t>
+    <rPh sb="3" eb="4">
+      <t>ワル</t>
+    </rPh>
+    <rPh sb="14" eb="15">
+      <t>スコ</t>
+    </rPh>
+    <rPh sb="16" eb="18">
+      <t>ソザイ</t>
+    </rPh>
+    <rPh sb="18" eb="20">
+      <t>ホンライ</t>
+    </rPh>
+    <rPh sb="21" eb="22">
+      <t>カオ</t>
+    </rPh>
+    <rPh sb="24" eb="25">
+      <t>タ</t>
+    </rPh>
+    <phoneticPr fontId="2"/>
+  </si>
+  <si>
+    <t>もう少し、素材自体が持つ香りを引き出してほしいところかの。</t>
+    <rPh sb="2" eb="3">
+      <t>スコ</t>
+    </rPh>
+    <rPh sb="5" eb="7">
+      <t>ソザイ</t>
+    </rPh>
+    <rPh sb="7" eb="9">
+      <t>ジタイ</t>
+    </rPh>
+    <rPh sb="10" eb="11">
+      <t>モ</t>
+    </rPh>
+    <rPh sb="12" eb="13">
+      <t>カオ</t>
+    </rPh>
+    <rPh sb="15" eb="16">
+      <t>ヒ</t>
+    </rPh>
+    <rPh sb="17" eb="18">
+      <t>ダ</t>
+    </rPh>
+    <phoneticPr fontId="2"/>
+  </si>
+  <si>
+    <t>香りじゃが..。むぉぉ..。</t>
+    <rPh sb="0" eb="1">
+      <t>カオ</t>
+    </rPh>
+    <phoneticPr fontId="2"/>
+  </si>
+  <si>
+    <t>これは、全く香りが足りていないの..。</t>
+    <rPh sb="4" eb="5">
+      <t>マッタ</t>
+    </rPh>
+    <rPh sb="6" eb="7">
+      <t>カオ</t>
+    </rPh>
+    <rPh sb="9" eb="10">
+      <t>タ</t>
+    </rPh>
+    <phoneticPr fontId="2"/>
+  </si>
+  <si>
+    <t>まだまだ、素材のもつ良い香りを引き出せるはずじゃ。</t>
+    <rPh sb="5" eb="7">
+      <t>ソザイ</t>
+    </rPh>
+    <rPh sb="10" eb="11">
+      <t>ヨ</t>
+    </rPh>
+    <rPh sb="12" eb="13">
+      <t>カオ</t>
+    </rPh>
+    <rPh sb="15" eb="16">
+      <t>ヒ</t>
+    </rPh>
+    <rPh sb="17" eb="18">
+      <t>ダ</t>
+    </rPh>
+    <phoneticPr fontId="2"/>
+  </si>
+  <si>
+    <t>いやぁ、これは素晴らしい！</t>
+    <rPh sb="7" eb="9">
+      <t>スバ</t>
+    </rPh>
+    <phoneticPr fontId="2"/>
+  </si>
+  <si>
+    <t>香り.. そして味わいの調和が絶妙で、思わず笑顔になってしまいます。</t>
+    <rPh sb="0" eb="1">
+      <t>カオ</t>
+    </rPh>
+    <rPh sb="8" eb="9">
+      <t>アジ</t>
+    </rPh>
+    <rPh sb="12" eb="14">
+      <t>チョウワ</t>
+    </rPh>
+    <rPh sb="15" eb="17">
+      <t>ゼツミョウ</t>
+    </rPh>
+    <rPh sb="19" eb="20">
+      <t>オモ</t>
+    </rPh>
+    <rPh sb="22" eb="24">
+      <t>エガオ</t>
+    </rPh>
+    <phoneticPr fontId="2"/>
+  </si>
+  <si>
+    <t>香りと味との調和も悪くない。</t>
+    <rPh sb="0" eb="1">
+      <t>カオ</t>
+    </rPh>
+    <rPh sb="3" eb="4">
+      <t>アジ</t>
+    </rPh>
+    <rPh sb="6" eb="8">
+      <t>チョウワ</t>
+    </rPh>
+    <rPh sb="9" eb="10">
+      <t>ワル</t>
+    </rPh>
+    <phoneticPr fontId="2"/>
+  </si>
+  <si>
+    <t>まだ素材自体の味わいを引き出してるとは言い難いようです。</t>
+    <rPh sb="2" eb="4">
+      <t>ソザイ</t>
+    </rPh>
+    <rPh sb="4" eb="6">
+      <t>ジタイ</t>
+    </rPh>
+    <rPh sb="7" eb="8">
+      <t>アジ</t>
+    </rPh>
+    <rPh sb="11" eb="12">
+      <t>ヒ</t>
+    </rPh>
+    <rPh sb="13" eb="14">
+      <t>ダ</t>
+    </rPh>
+    <rPh sb="19" eb="20">
+      <t>イ</t>
+    </rPh>
+    <rPh sb="21" eb="22">
+      <t>ガタ</t>
+    </rPh>
+    <phoneticPr fontId="2"/>
+  </si>
+  <si>
+    <t>素材の味わいの引き出しが重要ですね。</t>
+    <rPh sb="0" eb="2">
+      <t>ソザイ</t>
+    </rPh>
+    <rPh sb="3" eb="4">
+      <t>アジ</t>
+    </rPh>
+    <rPh sb="7" eb="8">
+      <t>ヒ</t>
+    </rPh>
+    <rPh sb="9" eb="10">
+      <t>ダ</t>
+    </rPh>
+    <rPh sb="12" eb="14">
+      <t>ジュウヨウ</t>
+    </rPh>
+    <phoneticPr fontId="2"/>
+  </si>
+  <si>
+    <t>味、香りとも、これは少し、工夫が必要そうですね。</t>
+    <rPh sb="2" eb="3">
+      <t>カオ</t>
+    </rPh>
+    <phoneticPr fontId="2"/>
+  </si>
+  <si>
+    <t>素晴らしくお上品な見た目でしたわ。</t>
+    <rPh sb="9" eb="10">
+      <t>ミ</t>
+    </rPh>
+    <rPh sb="11" eb="12">
+      <t>メ</t>
+    </rPh>
+    <phoneticPr fontId="2"/>
+  </si>
+  <si>
+    <t>この美しさ..、格式の高さを感じます。王宮で出すにふさわしい華やかさですわ。</t>
+    <rPh sb="2" eb="3">
+      <t>ウツク</t>
+    </rPh>
+    <rPh sb="8" eb="10">
+      <t>カクシキ</t>
+    </rPh>
+    <rPh sb="11" eb="12">
+      <t>タカ</t>
+    </rPh>
+    <rPh sb="14" eb="15">
+      <t>カン</t>
+    </rPh>
+    <rPh sb="19" eb="21">
+      <t>オウキュウ</t>
+    </rPh>
+    <rPh sb="22" eb="23">
+      <t>ダ</t>
+    </rPh>
+    <rPh sb="30" eb="31">
+      <t>ハナ</t>
+    </rPh>
+    <phoneticPr fontId="2"/>
+  </si>
+  <si>
+    <t>素材に自然に調和がとれており、見る者に心地よさを与えてくれるでしょう。</t>
+    <rPh sb="0" eb="2">
+      <t>ソザイ</t>
+    </rPh>
+    <rPh sb="3" eb="5">
+      <t>シゼン</t>
+    </rPh>
+    <rPh sb="6" eb="8">
+      <t>チョウワ</t>
+    </rPh>
+    <rPh sb="15" eb="16">
+      <t>ミ</t>
+    </rPh>
+    <rPh sb="17" eb="18">
+      <t>モノ</t>
+    </rPh>
+    <rPh sb="19" eb="21">
+      <t>ココチ</t>
+    </rPh>
+    <rPh sb="24" eb="25">
+      <t>アタ</t>
+    </rPh>
+    <phoneticPr fontId="2"/>
+  </si>
+  <si>
+    <t>少しみずぼらしさを感じますわね..。</t>
+    <rPh sb="0" eb="1">
+      <t>スコ</t>
+    </rPh>
+    <rPh sb="9" eb="10">
+      <t>カン</t>
+    </rPh>
+    <phoneticPr fontId="2"/>
+  </si>
+  <si>
+    <t>Juice_Default</t>
+    <phoneticPr fontId="2"/>
+  </si>
+  <si>
+    <t>のどの奥から全身にエネルギーが染みわたって、元気が湧いてくるぞい！</t>
+    <rPh sb="3" eb="4">
+      <t>オク</t>
+    </rPh>
+    <rPh sb="6" eb="8">
+      <t>ゼンシン</t>
+    </rPh>
+    <rPh sb="15" eb="16">
+      <t>シ</t>
+    </rPh>
+    <rPh sb="22" eb="24">
+      <t>ゲンキ</t>
+    </rPh>
+    <rPh sb="25" eb="26">
+      <t>ワ</t>
+    </rPh>
+    <phoneticPr fontId="2"/>
+  </si>
+  <si>
+    <t>このグビグビ感・・、もう止まらん！！神ののどごしじゃ！！</t>
+    <rPh sb="6" eb="7">
+      <t>カン</t>
+    </rPh>
+    <rPh sb="12" eb="13">
+      <t>ト</t>
+    </rPh>
+    <rPh sb="18" eb="19">
+      <t>カミ</t>
+    </rPh>
+    <phoneticPr fontId="2"/>
+  </si>
+  <si>
+    <t>かなり良いのどごし。味も鮮烈で、これはお菓子にも合いそうな飲み物じゃの。</t>
+    <rPh sb="3" eb="4">
+      <t>ヨ</t>
+    </rPh>
+    <rPh sb="10" eb="11">
+      <t>アジ</t>
+    </rPh>
+    <rPh sb="12" eb="14">
+      <t>センレツ</t>
+    </rPh>
+    <rPh sb="20" eb="22">
+      <t>カシ</t>
+    </rPh>
+    <rPh sb="24" eb="25">
+      <t>ア</t>
+    </rPh>
+    <rPh sb="29" eb="30">
+      <t>ノ</t>
+    </rPh>
+    <rPh sb="31" eb="32">
+      <t>モノ</t>
+    </rPh>
+    <phoneticPr fontId="2"/>
+  </si>
+  <si>
+    <t>あと一つ、のどごしにもう少しキレ味が欲しいところかの。</t>
+    <rPh sb="2" eb="3">
+      <t>ヒト</t>
+    </rPh>
+    <rPh sb="12" eb="13">
+      <t>スコ</t>
+    </rPh>
+    <rPh sb="16" eb="17">
+      <t>アジ</t>
+    </rPh>
+    <rPh sb="18" eb="19">
+      <t>ホ</t>
+    </rPh>
+    <phoneticPr fontId="2"/>
+  </si>
+  <si>
+    <t>グビビ..うむ。</t>
+    <phoneticPr fontId="2"/>
+  </si>
+  <si>
+    <t>ゴクリ..むむ..。</t>
+    <phoneticPr fontId="2"/>
+  </si>
+  <si>
+    <t>ゴクゴクッ！！　かぁぁぁぁ～！！これは素晴らしいのどごしじゃ！！</t>
+    <rPh sb="19" eb="21">
+      <t>スバ</t>
+    </rPh>
+    <phoneticPr fontId="2"/>
+  </si>
+  <si>
+    <t>う～む。悪くはないが。..少し、のどごしとしては物足りないかのう。</t>
+    <rPh sb="4" eb="5">
+      <t>ワル</t>
+    </rPh>
+    <rPh sb="13" eb="14">
+      <t>スコ</t>
+    </rPh>
+    <rPh sb="24" eb="26">
+      <t>モノタ</t>
+    </rPh>
+    <phoneticPr fontId="2"/>
+  </si>
+  <si>
+    <t>もう少し鮮烈さが欲しいところじゃ。</t>
+    <rPh sb="2" eb="3">
+      <t>スコ</t>
+    </rPh>
+    <rPh sb="4" eb="6">
+      <t>センレツ</t>
+    </rPh>
+    <rPh sb="8" eb="9">
+      <t>ホ</t>
+    </rPh>
+    <phoneticPr fontId="2"/>
+  </si>
+  <si>
+    <t>のどごしじゃが..。これは、のどごしを全く感じないのう。</t>
+    <rPh sb="19" eb="20">
+      <t>マッタ</t>
+    </rPh>
+    <rPh sb="21" eb="22">
+      <t>カン</t>
+    </rPh>
+    <phoneticPr fontId="2"/>
+  </si>
+  <si>
+    <t>グ..。むぅ..。</t>
+    <phoneticPr fontId="2"/>
+  </si>
+  <si>
+    <t>まだまだ、素材のもつ味わいを引き出せるはずじゃ。</t>
+    <rPh sb="5" eb="7">
+      <t>ソザイ</t>
+    </rPh>
+    <rPh sb="10" eb="11">
+      <t>アジ</t>
+    </rPh>
+    <rPh sb="14" eb="15">
+      <t>ヒ</t>
+    </rPh>
+    <rPh sb="16" eb="17">
+      <t>ダ</t>
+    </rPh>
+    <phoneticPr fontId="2"/>
+  </si>
+  <si>
+    <t>いやぁ、これは素晴らしいのどごし！</t>
+    <rPh sb="7" eb="9">
+      <t>スバ</t>
+    </rPh>
+    <phoneticPr fontId="2"/>
+  </si>
+  <si>
+    <t>味わいが鮮烈で、のどにキリリと、素材のうまみを感じます！</t>
+    <rPh sb="0" eb="1">
+      <t>アジ</t>
+    </rPh>
+    <rPh sb="4" eb="6">
+      <t>センレツ</t>
+    </rPh>
+    <rPh sb="16" eb="18">
+      <t>ソザイ</t>
+    </rPh>
+    <rPh sb="23" eb="24">
+      <t>カン</t>
+    </rPh>
+    <phoneticPr fontId="2"/>
+  </si>
+  <si>
+    <t>おお。これはおいしいですね。</t>
+    <phoneticPr fontId="2"/>
+  </si>
+  <si>
+    <t>のどごし、味わいとの調和がよくとれていて、バランスが良いと思います。</t>
+    <rPh sb="5" eb="6">
+      <t>アジ</t>
+    </rPh>
+    <rPh sb="10" eb="12">
+      <t>チョウワ</t>
+    </rPh>
+    <rPh sb="26" eb="27">
+      <t>ヨ</t>
+    </rPh>
+    <rPh sb="29" eb="30">
+      <t>オモ</t>
+    </rPh>
+    <phoneticPr fontId="2"/>
+  </si>
+  <si>
+    <t>むむ。のどごしは決して悪いわけではありませんが、</t>
+    <phoneticPr fontId="2"/>
+  </si>
+  <si>
+    <t>素材本来の味わいが、少し薄く感じますね。</t>
+    <rPh sb="0" eb="2">
+      <t>ソザイ</t>
+    </rPh>
+    <rPh sb="2" eb="4">
+      <t>ホンライ</t>
+    </rPh>
+    <rPh sb="5" eb="6">
+      <t>アジ</t>
+    </rPh>
+    <rPh sb="10" eb="11">
+      <t>スコ</t>
+    </rPh>
+    <rPh sb="12" eb="13">
+      <t>ウス</t>
+    </rPh>
+    <rPh sb="14" eb="15">
+      <t>カン</t>
+    </rPh>
+    <phoneticPr fontId="2"/>
+  </si>
+  <si>
+    <t>味、もしくはのどごしに、今一つ調和が欠けているようです。</t>
+    <rPh sb="0" eb="1">
+      <t>アジ</t>
+    </rPh>
+    <rPh sb="12" eb="13">
+      <t>イマ</t>
+    </rPh>
+    <rPh sb="13" eb="14">
+      <t>ヒト</t>
+    </rPh>
+    <rPh sb="15" eb="17">
+      <t>チョウワ</t>
+    </rPh>
+    <rPh sb="18" eb="19">
+      <t>カ</t>
+    </rPh>
+    <phoneticPr fontId="2"/>
+  </si>
+  <si>
+    <t>味、のどごしとも、これは少し、工夫が必要そうですね。</t>
+    <phoneticPr fontId="2"/>
+  </si>
+  <si>
+    <t>素晴らしい見た目、エクッセレントです！！</t>
+    <rPh sb="5" eb="6">
+      <t>ミ</t>
+    </rPh>
+    <rPh sb="7" eb="8">
+      <t>メ</t>
+    </rPh>
+    <phoneticPr fontId="2"/>
+  </si>
+  <si>
+    <t>この美しさ..、心が浮き立つようにワクワクを感じました。</t>
+    <rPh sb="2" eb="3">
+      <t>ウツク</t>
+    </rPh>
+    <rPh sb="8" eb="9">
+      <t>ココロ</t>
+    </rPh>
+    <rPh sb="10" eb="11">
+      <t>ウ</t>
+    </rPh>
+    <rPh sb="12" eb="13">
+      <t>タ</t>
+    </rPh>
+    <rPh sb="22" eb="23">
+      <t>カン</t>
     </rPh>
     <phoneticPr fontId="2"/>
   </si>
@@ -8231,7 +8842,7 @@
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{45641A99-B1F8-4C39-AB73-847198772904}">
-  <dimension ref="A1:J13"/>
+  <dimension ref="A1:J37"/>
   <sheetFormatPr defaultRowHeight="18.75" x14ac:dyDescent="0.4"/>
   <cols>
     <col min="2" max="2" width="8.75" customWidth="1"/>
@@ -8310,11 +8921,11 @@
     </row>
     <row r="3" spans="1:10" x14ac:dyDescent="0.4">
       <c r="A3">
-        <f t="shared" ref="A3:A13" si="0">ROW()-2+100000</f>
+        <f t="shared" ref="A3:A37" si="0">ROW()-2+100000</f>
         <v>100001</v>
       </c>
       <c r="B3">
-        <f t="shared" ref="B3:B13" si="1">INDEX(B:B,MATCH(100000,B:B,0),1)+(ROW()-MATCH(100000,B:B,0))</f>
+        <f t="shared" ref="B3:B37" si="1">INDEX(B:B,MATCH(100000,B:B,0),1)+(ROW()-MATCH(100000,B:B,0))</f>
         <v>100001</v>
       </c>
       <c r="D3">
@@ -8646,6 +9257,754 @@
         <v>12</v>
       </c>
       <c r="J13">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="14" spans="1:10" s="3" customFormat="1" x14ac:dyDescent="0.4">
+      <c r="A14" s="3">
+        <f>ROW()-2+100000</f>
+        <v>100012</v>
+      </c>
+      <c r="B14" s="3">
+        <v>100000</v>
+      </c>
+      <c r="C14" s="3" t="s">
+        <v>336</v>
+      </c>
+      <c r="D14" s="3">
+        <v>0</v>
+      </c>
+      <c r="E14" s="3" t="s">
+        <v>350</v>
+      </c>
+      <c r="F14" s="3" t="s">
+        <v>351</v>
+      </c>
+      <c r="G14" s="3" t="s">
+        <v>52</v>
+      </c>
+      <c r="H14" s="3" t="s">
+        <v>86</v>
+      </c>
+      <c r="I14" s="3" t="s">
+        <v>9</v>
+      </c>
+      <c r="J14" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="15" spans="1:10" x14ac:dyDescent="0.4">
+      <c r="A15">
+        <f t="shared" si="0"/>
+        <v>100013</v>
+      </c>
+      <c r="B15">
+        <f t="shared" si="1"/>
+        <v>100013</v>
+      </c>
+      <c r="D15">
+        <v>1</v>
+      </c>
+      <c r="E15" t="s">
+        <v>16</v>
+      </c>
+      <c r="F15" t="s">
+        <v>352</v>
+      </c>
+      <c r="G15" t="s">
+        <v>85</v>
+      </c>
+      <c r="H15" t="s">
+        <v>14</v>
+      </c>
+      <c r="I15" t="s">
+        <v>10</v>
+      </c>
+      <c r="J15">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="16" spans="1:10" x14ac:dyDescent="0.4">
+      <c r="A16">
+        <f t="shared" si="0"/>
+        <v>100014</v>
+      </c>
+      <c r="B16">
+        <f t="shared" si="1"/>
+        <v>100014</v>
+      </c>
+      <c r="D16">
+        <v>2</v>
+      </c>
+      <c r="E16" t="s">
+        <v>54</v>
+      </c>
+      <c r="F16" t="s">
+        <v>353</v>
+      </c>
+      <c r="G16" t="s">
+        <v>354</v>
+      </c>
+      <c r="H16" t="s">
+        <v>22</v>
+      </c>
+      <c r="I16" t="s">
+        <v>11</v>
+      </c>
+      <c r="J16">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="17" spans="1:10" x14ac:dyDescent="0.4">
+      <c r="A17">
+        <f t="shared" si="0"/>
+        <v>100015</v>
+      </c>
+      <c r="B17">
+        <f t="shared" si="1"/>
+        <v>100015</v>
+      </c>
+      <c r="D17">
+        <v>3</v>
+      </c>
+      <c r="E17" t="s">
+        <v>27</v>
+      </c>
+      <c r="F17" t="s">
+        <v>355</v>
+      </c>
+      <c r="G17" t="s">
+        <v>28</v>
+      </c>
+      <c r="H17" t="s">
+        <v>30</v>
+      </c>
+      <c r="I17" t="s">
+        <v>12</v>
+      </c>
+      <c r="J17">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="18" spans="1:10" x14ac:dyDescent="0.4">
+      <c r="A18">
+        <f t="shared" si="0"/>
+        <v>100016</v>
+      </c>
+      <c r="B18">
+        <f t="shared" si="1"/>
+        <v>100016</v>
+      </c>
+      <c r="D18">
+        <v>4</v>
+      </c>
+      <c r="E18" t="s">
+        <v>356</v>
+      </c>
+      <c r="F18" t="s">
+        <v>357</v>
+      </c>
+      <c r="G18" t="s">
+        <v>42</v>
+      </c>
+      <c r="H18" t="s">
+        <v>18</v>
+      </c>
+      <c r="I18" t="s">
+        <v>36</v>
+      </c>
+      <c r="J18">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="19" spans="1:10" x14ac:dyDescent="0.4">
+      <c r="A19">
+        <f t="shared" si="0"/>
+        <v>100017</v>
+      </c>
+      <c r="B19">
+        <f t="shared" si="1"/>
+        <v>100017</v>
+      </c>
+      <c r="D19">
+        <v>5</v>
+      </c>
+      <c r="E19" t="s">
+        <v>44</v>
+      </c>
+      <c r="F19" t="s">
+        <v>358</v>
+      </c>
+      <c r="G19" t="s">
+        <v>83</v>
+      </c>
+      <c r="H19" t="s">
+        <v>17</v>
+      </c>
+      <c r="I19" t="s">
+        <v>10</v>
+      </c>
+      <c r="J19">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="20" spans="1:10" x14ac:dyDescent="0.4">
+      <c r="A20">
+        <f t="shared" si="0"/>
+        <v>100018</v>
+      </c>
+      <c r="B20">
+        <f t="shared" si="1"/>
+        <v>100018</v>
+      </c>
+      <c r="D20">
+        <v>6</v>
+      </c>
+      <c r="E20" t="s">
+        <v>23</v>
+      </c>
+      <c r="F20" t="s">
+        <v>79</v>
+      </c>
+      <c r="G20" t="s">
+        <v>78</v>
+      </c>
+      <c r="H20" t="s">
+        <v>48</v>
+      </c>
+      <c r="I20" t="s">
+        <v>11</v>
+      </c>
+      <c r="J20">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="21" spans="1:10" x14ac:dyDescent="0.4">
+      <c r="A21">
+        <f t="shared" si="0"/>
+        <v>100019</v>
+      </c>
+      <c r="B21">
+        <f t="shared" si="1"/>
+        <v>100019</v>
+      </c>
+      <c r="D21">
+        <v>7</v>
+      </c>
+      <c r="E21" t="s">
+        <v>31</v>
+      </c>
+      <c r="F21" t="s">
+        <v>49</v>
+      </c>
+      <c r="G21" t="s">
+        <v>80</v>
+      </c>
+      <c r="H21" t="s">
+        <v>359</v>
+      </c>
+      <c r="I21" t="s">
+        <v>12</v>
+      </c>
+      <c r="J21">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="22" spans="1:10" x14ac:dyDescent="0.4">
+      <c r="A22">
+        <f t="shared" si="0"/>
+        <v>100020</v>
+      </c>
+      <c r="B22">
+        <f t="shared" si="1"/>
+        <v>100020</v>
+      </c>
+      <c r="D22">
+        <v>8</v>
+      </c>
+      <c r="E22" t="s">
+        <v>338</v>
+      </c>
+      <c r="F22" t="s">
+        <v>337</v>
+      </c>
+      <c r="G22" t="s">
+        <v>339</v>
+      </c>
+      <c r="H22" t="s">
+        <v>38</v>
+      </c>
+      <c r="I22" t="s">
+        <v>37</v>
+      </c>
+      <c r="J22">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="23" spans="1:10" x14ac:dyDescent="0.4">
+      <c r="A23">
+        <f t="shared" si="0"/>
+        <v>100021</v>
+      </c>
+      <c r="B23">
+        <f t="shared" si="1"/>
+        <v>100021</v>
+      </c>
+      <c r="D23">
+        <v>9</v>
+      </c>
+      <c r="E23" t="s">
+        <v>340</v>
+      </c>
+      <c r="F23" t="s">
+        <v>341</v>
+      </c>
+      <c r="G23" t="s">
+        <v>342</v>
+      </c>
+      <c r="H23" t="s">
+        <v>343</v>
+      </c>
+      <c r="I23" t="s">
+        <v>10</v>
+      </c>
+      <c r="J23">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="24" spans="1:10" x14ac:dyDescent="0.4">
+      <c r="A24">
+        <f t="shared" si="0"/>
+        <v>100022</v>
+      </c>
+      <c r="B24">
+        <f t="shared" si="1"/>
+        <v>100022</v>
+      </c>
+      <c r="D24">
+        <v>10</v>
+      </c>
+      <c r="E24" t="s">
+        <v>344</v>
+      </c>
+      <c r="F24" t="s">
+        <v>345</v>
+      </c>
+      <c r="G24" t="s">
+        <v>346</v>
+      </c>
+      <c r="H24" t="s">
+        <v>26</v>
+      </c>
+      <c r="I24" t="s">
+        <v>11</v>
+      </c>
+      <c r="J24">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="25" spans="1:10" x14ac:dyDescent="0.4">
+      <c r="A25">
+        <f t="shared" si="0"/>
+        <v>100023</v>
+      </c>
+      <c r="B25">
+        <f t="shared" si="1"/>
+        <v>100023</v>
+      </c>
+      <c r="D25">
+        <v>11</v>
+      </c>
+      <c r="E25" t="s">
+        <v>347</v>
+      </c>
+      <c r="F25" t="s">
+        <v>348</v>
+      </c>
+      <c r="G25" t="s">
+        <v>349</v>
+      </c>
+      <c r="H25" t="s">
+        <v>88</v>
+      </c>
+      <c r="I25" t="s">
+        <v>12</v>
+      </c>
+      <c r="J25">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="26" spans="1:10" s="3" customFormat="1" x14ac:dyDescent="0.4">
+      <c r="A26" s="3">
+        <f>ROW()-2+100000</f>
+        <v>100024</v>
+      </c>
+      <c r="B26" s="3">
+        <v>100000</v>
+      </c>
+      <c r="C26" s="3" t="s">
+        <v>360</v>
+      </c>
+      <c r="D26" s="3">
+        <v>0</v>
+      </c>
+      <c r="E26" s="3" t="s">
+        <v>373</v>
+      </c>
+      <c r="F26" s="3" t="s">
+        <v>374</v>
+      </c>
+      <c r="G26" s="3" t="s">
+        <v>52</v>
+      </c>
+      <c r="H26" s="3" t="s">
+        <v>86</v>
+      </c>
+      <c r="I26" s="3" t="s">
+        <v>9</v>
+      </c>
+      <c r="J26" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="27" spans="1:10" x14ac:dyDescent="0.4">
+      <c r="A27">
+        <f t="shared" si="0"/>
+        <v>100025</v>
+      </c>
+      <c r="B27">
+        <f t="shared" si="1"/>
+        <v>100025</v>
+      </c>
+      <c r="D27">
+        <v>1</v>
+      </c>
+      <c r="E27" t="s">
+        <v>375</v>
+      </c>
+      <c r="F27" t="s">
+        <v>376</v>
+      </c>
+      <c r="G27" t="s">
+        <v>85</v>
+      </c>
+      <c r="H27" t="s">
+        <v>14</v>
+      </c>
+      <c r="I27" t="s">
+        <v>10</v>
+      </c>
+      <c r="J27">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="28" spans="1:10" x14ac:dyDescent="0.4">
+      <c r="A28">
+        <f t="shared" si="0"/>
+        <v>100026</v>
+      </c>
+      <c r="B28">
+        <f t="shared" si="1"/>
+        <v>100026</v>
+      </c>
+      <c r="D28">
+        <v>2</v>
+      </c>
+      <c r="E28" t="s">
+        <v>377</v>
+      </c>
+      <c r="F28" t="s">
+        <v>378</v>
+      </c>
+      <c r="G28" t="s">
+        <v>379</v>
+      </c>
+      <c r="H28" t="s">
+        <v>22</v>
+      </c>
+      <c r="I28" t="s">
+        <v>11</v>
+      </c>
+      <c r="J28">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="29" spans="1:10" x14ac:dyDescent="0.4">
+      <c r="A29">
+        <f t="shared" si="0"/>
+        <v>100027</v>
+      </c>
+      <c r="B29">
+        <f t="shared" si="1"/>
+        <v>100027</v>
+      </c>
+      <c r="D29">
+        <v>3</v>
+      </c>
+      <c r="E29" t="s">
+        <v>27</v>
+      </c>
+      <c r="F29" t="s">
+        <v>380</v>
+      </c>
+      <c r="G29" t="s">
+        <v>28</v>
+      </c>
+      <c r="H29" t="s">
+        <v>30</v>
+      </c>
+      <c r="I29" t="s">
+        <v>12</v>
+      </c>
+      <c r="J29">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="30" spans="1:10" x14ac:dyDescent="0.4">
+      <c r="A30">
+        <f t="shared" si="0"/>
+        <v>100028</v>
+      </c>
+      <c r="B30">
+        <f t="shared" si="1"/>
+        <v>100028</v>
+      </c>
+      <c r="D30">
+        <v>4</v>
+      </c>
+      <c r="E30" t="s">
+        <v>381</v>
+      </c>
+      <c r="F30" t="s">
+        <v>382</v>
+      </c>
+      <c r="G30" t="s">
+        <v>42</v>
+      </c>
+      <c r="H30" t="s">
+        <v>18</v>
+      </c>
+      <c r="I30" t="s">
+        <v>36</v>
+      </c>
+      <c r="J30">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="31" spans="1:10" x14ac:dyDescent="0.4">
+      <c r="A31">
+        <f t="shared" si="0"/>
+        <v>100029</v>
+      </c>
+      <c r="B31">
+        <f t="shared" si="1"/>
+        <v>100029</v>
+      </c>
+      <c r="D31">
+        <v>5</v>
+      </c>
+      <c r="E31" t="s">
+        <v>44</v>
+      </c>
+      <c r="F31" t="s">
+        <v>358</v>
+      </c>
+      <c r="G31" t="s">
+        <v>83</v>
+      </c>
+      <c r="H31" t="s">
+        <v>17</v>
+      </c>
+      <c r="I31" t="s">
+        <v>10</v>
+      </c>
+      <c r="J31">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="32" spans="1:10" x14ac:dyDescent="0.4">
+      <c r="A32">
+        <f t="shared" si="0"/>
+        <v>100030</v>
+      </c>
+      <c r="B32">
+        <f t="shared" si="1"/>
+        <v>100030</v>
+      </c>
+      <c r="D32">
+        <v>6</v>
+      </c>
+      <c r="E32" t="s">
+        <v>23</v>
+      </c>
+      <c r="F32" t="s">
+        <v>79</v>
+      </c>
+      <c r="G32" t="s">
+        <v>78</v>
+      </c>
+      <c r="H32" t="s">
+        <v>48</v>
+      </c>
+      <c r="I32" t="s">
+        <v>11</v>
+      </c>
+      <c r="J32">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="33" spans="1:10" x14ac:dyDescent="0.4">
+      <c r="A33">
+        <f t="shared" si="0"/>
+        <v>100031</v>
+      </c>
+      <c r="B33">
+        <f t="shared" si="1"/>
+        <v>100031</v>
+      </c>
+      <c r="D33">
+        <v>7</v>
+      </c>
+      <c r="E33" t="s">
+        <v>31</v>
+      </c>
+      <c r="F33" t="s">
+        <v>49</v>
+      </c>
+      <c r="G33" t="s">
+        <v>80</v>
+      </c>
+      <c r="H33" t="s">
+        <v>359</v>
+      </c>
+      <c r="I33" t="s">
+        <v>12</v>
+      </c>
+      <c r="J33">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="34" spans="1:10" x14ac:dyDescent="0.4">
+      <c r="A34">
+        <f t="shared" si="0"/>
+        <v>100032</v>
+      </c>
+      <c r="B34">
+        <f t="shared" si="1"/>
+        <v>100032</v>
+      </c>
+      <c r="D34">
+        <v>8</v>
+      </c>
+      <c r="E34" t="s">
+        <v>367</v>
+      </c>
+      <c r="F34" t="s">
+        <v>361</v>
+      </c>
+      <c r="G34" t="s">
+        <v>362</v>
+      </c>
+      <c r="H34" t="s">
+        <v>38</v>
+      </c>
+      <c r="I34" t="s">
+        <v>37</v>
+      </c>
+      <c r="J34">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="35" spans="1:10" x14ac:dyDescent="0.4">
+      <c r="A35">
+        <f t="shared" si="0"/>
+        <v>100033</v>
+      </c>
+      <c r="B35">
+        <f t="shared" si="1"/>
+        <v>100033</v>
+      </c>
+      <c r="D35">
+        <v>9</v>
+      </c>
+      <c r="E35" t="s">
+        <v>365</v>
+      </c>
+      <c r="F35" t="s">
+        <v>363</v>
+      </c>
+      <c r="G35" t="s">
+        <v>364</v>
+      </c>
+      <c r="H35" t="s">
+        <v>343</v>
+      </c>
+      <c r="I35" t="s">
+        <v>10</v>
+      </c>
+      <c r="J35">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="36" spans="1:10" x14ac:dyDescent="0.4">
+      <c r="A36">
+        <f t="shared" si="0"/>
+        <v>100034</v>
+      </c>
+      <c r="B36">
+        <f t="shared" si="1"/>
+        <v>100034</v>
+      </c>
+      <c r="D36">
+        <v>10</v>
+      </c>
+      <c r="E36" t="s">
+        <v>366</v>
+      </c>
+      <c r="F36" t="s">
+        <v>368</v>
+      </c>
+      <c r="G36" t="s">
+        <v>369</v>
+      </c>
+      <c r="H36" t="s">
+        <v>26</v>
+      </c>
+      <c r="I36" t="s">
+        <v>11</v>
+      </c>
+      <c r="J36">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="37" spans="1:10" x14ac:dyDescent="0.4">
+      <c r="A37">
+        <f t="shared" si="0"/>
+        <v>100035</v>
+      </c>
+      <c r="B37">
+        <f t="shared" si="1"/>
+        <v>100035</v>
+      </c>
+      <c r="D37">
+        <v>11</v>
+      </c>
+      <c r="E37" t="s">
+        <v>371</v>
+      </c>
+      <c r="F37" t="s">
+        <v>370</v>
+      </c>
+      <c r="G37" t="s">
+        <v>372</v>
+      </c>
+      <c r="H37" t="s">
+        <v>88</v>
+      </c>
+      <c r="I37" t="s">
+        <v>12</v>
+      </c>
+      <c r="J37">
         <v>1</v>
       </c>
     </row>

--- a/Assets/Resources/Excel/Entity_ContestCommentDataBase.xlsx
+++ b/Assets/Resources/Excel/Entity_ContestCommentDataBase.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\aritashogo\Documents\Unity\Okashi_Atlier2\Assets\Resources\Excel\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{0AB64A4F-07B3-4F5C-97FE-29FAE15B5212}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{0C7E4AF3-2A0F-4C93-B87B-23D223729081}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="915" yWindow="390" windowWidth="25485" windowHeight="14370" activeTab="2" xr2:uid="{1DCE2773-8A3B-4011-B3F4-E2EABC03DB8B}"/>
   </bookViews>
@@ -36,7 +36,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1013" uniqueCount="383">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1135" uniqueCount="387">
   <si>
     <t>item_Name</t>
     <phoneticPr fontId="3"/>
@@ -4361,47 +4361,6 @@
     <phoneticPr fontId="2"/>
   </si>
   <si>
-    <t>かなり良いのどごし。味も鮮烈で、これはお菓子にも合いそうな飲み物じゃの。</t>
-    <rPh sb="3" eb="4">
-      <t>ヨ</t>
-    </rPh>
-    <rPh sb="10" eb="11">
-      <t>アジ</t>
-    </rPh>
-    <rPh sb="12" eb="14">
-      <t>センレツ</t>
-    </rPh>
-    <rPh sb="20" eb="22">
-      <t>カシ</t>
-    </rPh>
-    <rPh sb="24" eb="25">
-      <t>ア</t>
-    </rPh>
-    <rPh sb="29" eb="30">
-      <t>ノ</t>
-    </rPh>
-    <rPh sb="31" eb="32">
-      <t>モノ</t>
-    </rPh>
-    <phoneticPr fontId="2"/>
-  </si>
-  <si>
-    <t>あと一つ、のどごしにもう少しキレ味が欲しいところかの。</t>
-    <rPh sb="2" eb="3">
-      <t>ヒト</t>
-    </rPh>
-    <rPh sb="12" eb="13">
-      <t>スコ</t>
-    </rPh>
-    <rPh sb="16" eb="17">
-      <t>アジ</t>
-    </rPh>
-    <rPh sb="18" eb="19">
-      <t>ホ</t>
-    </rPh>
-    <phoneticPr fontId="2"/>
-  </si>
-  <si>
     <t>グビビ..うむ。</t>
     <phoneticPr fontId="2"/>
   </si>
@@ -4473,13 +4432,6 @@
     <phoneticPr fontId="2"/>
   </si>
   <si>
-    <t>いやぁ、これは素晴らしいのどごし！</t>
-    <rPh sb="7" eb="9">
-      <t>スバ</t>
-    </rPh>
-    <phoneticPr fontId="2"/>
-  </si>
-  <si>
     <t>味わいが鮮烈で、のどにキリリと、素材のうまみを感じます！</t>
     <rPh sb="0" eb="1">
       <t>アジ</t>
@@ -4496,26 +4448,6 @@
     <phoneticPr fontId="2"/>
   </si>
   <si>
-    <t>おお。これはおいしいですね。</t>
-    <phoneticPr fontId="2"/>
-  </si>
-  <si>
-    <t>のどごし、味わいとの調和がよくとれていて、バランスが良いと思います。</t>
-    <rPh sb="5" eb="6">
-      <t>アジ</t>
-    </rPh>
-    <rPh sb="10" eb="12">
-      <t>チョウワ</t>
-    </rPh>
-    <rPh sb="26" eb="27">
-      <t>ヨ</t>
-    </rPh>
-    <rPh sb="29" eb="30">
-      <t>オモ</t>
-    </rPh>
-    <phoneticPr fontId="2"/>
-  </si>
-  <si>
     <t>むむ。のどごしは決して悪いわけではありませんが、</t>
     <phoneticPr fontId="2"/>
   </si>
@@ -4591,6 +4523,111 @@
     <rPh sb="22" eb="23">
       <t>カン</t>
     </rPh>
+    <phoneticPr fontId="2"/>
+  </si>
+  <si>
+    <t>かなり良いグビグビ感。味も鮮烈で、これはお菓子にも合いそうな飲み物じゃの。</t>
+    <rPh sb="3" eb="4">
+      <t>ヨ</t>
+    </rPh>
+    <rPh sb="9" eb="10">
+      <t>カン</t>
+    </rPh>
+    <rPh sb="11" eb="12">
+      <t>アジ</t>
+    </rPh>
+    <rPh sb="13" eb="15">
+      <t>センレツ</t>
+    </rPh>
+    <rPh sb="21" eb="23">
+      <t>カシ</t>
+    </rPh>
+    <rPh sb="25" eb="26">
+      <t>ア</t>
+    </rPh>
+    <rPh sb="30" eb="31">
+      <t>ノ</t>
+    </rPh>
+    <rPh sb="32" eb="33">
+      <t>モノ</t>
+    </rPh>
+    <phoneticPr fontId="2"/>
+  </si>
+  <si>
+    <t>のどごしにもう少しキレ味が欲しいところかの。</t>
+    <rPh sb="7" eb="8">
+      <t>スコ</t>
+    </rPh>
+    <rPh sb="11" eb="12">
+      <t>アジ</t>
+    </rPh>
+    <rPh sb="13" eb="14">
+      <t>ホ</t>
+    </rPh>
+    <phoneticPr fontId="2"/>
+  </si>
+  <si>
+    <t>コンテスト個別にコメント指定可能</t>
+    <rPh sb="5" eb="7">
+      <t>コベツ</t>
+    </rPh>
+    <rPh sb="12" eb="14">
+      <t>シテイ</t>
+    </rPh>
+    <rPh sb="14" eb="16">
+      <t>カノウ</t>
+    </rPh>
+    <phoneticPr fontId="2"/>
+  </si>
+  <si>
+    <t>コンテスト共通のコメント</t>
+    <rPh sb="5" eb="7">
+      <t>キョウツウ</t>
+    </rPh>
+    <phoneticPr fontId="2"/>
+  </si>
+  <si>
+    <t>Soda_Default</t>
+    <phoneticPr fontId="2"/>
+  </si>
+  <si>
+    <t>いやぁ、これは素晴らしいシュワシュワ感！</t>
+    <rPh sb="7" eb="9">
+      <t>スバ</t>
+    </rPh>
+    <rPh sb="18" eb="19">
+      <t>カン</t>
+    </rPh>
+    <phoneticPr fontId="2"/>
+  </si>
+  <si>
+    <t>おお。これは.. かなりの爽やかさ！</t>
+    <rPh sb="13" eb="14">
+      <t>サワ</t>
+    </rPh>
+    <phoneticPr fontId="2"/>
+  </si>
+  <si>
+    <t>シュワシュワ感と味わいとの調和がよくとれていて、バランスが良いと思います。</t>
+    <rPh sb="6" eb="7">
+      <t>カン</t>
+    </rPh>
+    <rPh sb="8" eb="9">
+      <t>アジ</t>
+    </rPh>
+    <rPh sb="13" eb="15">
+      <t>チョウワ</t>
+    </rPh>
+    <rPh sb="29" eb="30">
+      <t>ヨ</t>
+    </rPh>
+    <rPh sb="32" eb="33">
+      <t>オモ</t>
+    </rPh>
+    <phoneticPr fontId="2"/>
+  </si>
+  <si>
+    <t>Tea_Default</t>
     <phoneticPr fontId="2"/>
   </si>
 </sst>
@@ -7738,7 +7775,7 @@
         <v>86</v>
       </c>
       <c r="I2" s="3" t="s">
-        <v>9</v>
+        <v>380</v>
       </c>
       <c r="J2" s="3">
         <v>0</v>
@@ -8842,7 +8879,7 @@
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{45641A99-B1F8-4C39-AB73-847198772904}">
-  <dimension ref="A1:J37"/>
+  <dimension ref="A1:J61"/>
   <sheetFormatPr defaultRowHeight="18.75" x14ac:dyDescent="0.4"/>
   <cols>
     <col min="2" max="2" width="8.75" customWidth="1"/>
@@ -8913,7 +8950,7 @@
         <v>86</v>
       </c>
       <c r="I2" s="3" t="s">
-        <v>9</v>
+        <v>381</v>
       </c>
       <c r="J2" s="3">
         <v>0</v>
@@ -8921,11 +8958,11 @@
     </row>
     <row r="3" spans="1:10" x14ac:dyDescent="0.4">
       <c r="A3">
-        <f t="shared" ref="A3:A37" si="0">ROW()-2+100000</f>
+        <f t="shared" ref="A3:A61" si="0">ROW()-2+100000</f>
         <v>100001</v>
       </c>
       <c r="B3">
-        <f t="shared" ref="B3:B37" si="1">INDEX(B:B,MATCH(100000,B:B,0),1)+(ROW()-MATCH(100000,B:B,0))</f>
+        <f>INDEX(B:B,MATCH(100000,B:B,0),1)+(ROW()-MATCH(100000,B:B,0))</f>
         <v>100001</v>
       </c>
       <c r="D3">
@@ -8956,7 +8993,7 @@
         <v>100002</v>
       </c>
       <c r="B4">
-        <f t="shared" si="1"/>
+        <f>INDEX(B:B,MATCH(100000,B:B,0),1)+(ROW()-MATCH(100000,B:B,0))</f>
         <v>100002</v>
       </c>
       <c r="D4">
@@ -8987,7 +9024,7 @@
         <v>100003</v>
       </c>
       <c r="B5">
-        <f t="shared" si="1"/>
+        <f>INDEX(B:B,MATCH(100000,B:B,0),1)+(ROW()-MATCH(100000,B:B,0))</f>
         <v>100003</v>
       </c>
       <c r="D5">
@@ -9018,7 +9055,7 @@
         <v>100004</v>
       </c>
       <c r="B6">
-        <f t="shared" si="1"/>
+        <f>INDEX(B:B,MATCH(100000,B:B,0),1)+(ROW()-MATCH(100000,B:B,0))</f>
         <v>100004</v>
       </c>
       <c r="D6">
@@ -9049,7 +9086,7 @@
         <v>100005</v>
       </c>
       <c r="B7">
-        <f t="shared" si="1"/>
+        <f>INDEX(B:B,MATCH(100000,B:B,0),1)+(ROW()-MATCH(100000,B:B,0))</f>
         <v>100005</v>
       </c>
       <c r="D7">
@@ -9080,7 +9117,7 @@
         <v>100006</v>
       </c>
       <c r="B8">
-        <f t="shared" si="1"/>
+        <f>INDEX(B:B,MATCH(100000,B:B,0),1)+(ROW()-MATCH(100000,B:B,0))</f>
         <v>100006</v>
       </c>
       <c r="D8">
@@ -9111,7 +9148,7 @@
         <v>100007</v>
       </c>
       <c r="B9">
-        <f t="shared" si="1"/>
+        <f>INDEX(B:B,MATCH(100000,B:B,0),1)+(ROW()-MATCH(100000,B:B,0))</f>
         <v>100007</v>
       </c>
       <c r="D9">
@@ -9142,7 +9179,7 @@
         <v>100008</v>
       </c>
       <c r="B10">
-        <f t="shared" si="1"/>
+        <f>INDEX(B:B,MATCH(100000,B:B,0),1)+(ROW()-MATCH(100000,B:B,0))</f>
         <v>100008</v>
       </c>
       <c r="D10">
@@ -9173,7 +9210,7 @@
         <v>100009</v>
       </c>
       <c r="B11">
-        <f t="shared" si="1"/>
+        <f>INDEX(B:B,MATCH(100000,B:B,0),1)+(ROW()-MATCH(100000,B:B,0))</f>
         <v>100009</v>
       </c>
       <c r="D11">
@@ -9204,7 +9241,7 @@
         <v>100010</v>
       </c>
       <c r="B12">
-        <f t="shared" si="1"/>
+        <f>INDEX(B:B,MATCH(100000,B:B,0),1)+(ROW()-MATCH(100000,B:B,0))</f>
         <v>100010</v>
       </c>
       <c r="D12">
@@ -9235,7 +9272,7 @@
         <v>100011</v>
       </c>
       <c r="B13">
-        <f t="shared" si="1"/>
+        <f>INDEX(B:B,MATCH(100000,B:B,0),1)+(ROW()-MATCH(100000,B:B,0))</f>
         <v>100011</v>
       </c>
       <c r="D13">
@@ -9299,7 +9336,7 @@
         <v>100013</v>
       </c>
       <c r="B15">
-        <f t="shared" si="1"/>
+        <f>INDEX(B:B,MATCH(100000,B:B,0),1)+(ROW()-MATCH(100000,B:B,0))</f>
         <v>100013</v>
       </c>
       <c r="D15">
@@ -9330,7 +9367,7 @@
         <v>100014</v>
       </c>
       <c r="B16">
-        <f t="shared" si="1"/>
+        <f>INDEX(B:B,MATCH(100000,B:B,0),1)+(ROW()-MATCH(100000,B:B,0))</f>
         <v>100014</v>
       </c>
       <c r="D16">
@@ -9361,7 +9398,7 @@
         <v>100015</v>
       </c>
       <c r="B17">
-        <f t="shared" si="1"/>
+        <f>INDEX(B:B,MATCH(100000,B:B,0),1)+(ROW()-MATCH(100000,B:B,0))</f>
         <v>100015</v>
       </c>
       <c r="D17">
@@ -9392,7 +9429,7 @@
         <v>100016</v>
       </c>
       <c r="B18">
-        <f t="shared" si="1"/>
+        <f>INDEX(B:B,MATCH(100000,B:B,0),1)+(ROW()-MATCH(100000,B:B,0))</f>
         <v>100016</v>
       </c>
       <c r="D18">
@@ -9423,7 +9460,7 @@
         <v>100017</v>
       </c>
       <c r="B19">
-        <f t="shared" si="1"/>
+        <f>INDEX(B:B,MATCH(100000,B:B,0),1)+(ROW()-MATCH(100000,B:B,0))</f>
         <v>100017</v>
       </c>
       <c r="D19">
@@ -9454,7 +9491,7 @@
         <v>100018</v>
       </c>
       <c r="B20">
-        <f t="shared" si="1"/>
+        <f>INDEX(B:B,MATCH(100000,B:B,0),1)+(ROW()-MATCH(100000,B:B,0))</f>
         <v>100018</v>
       </c>
       <c r="D20">
@@ -9485,7 +9522,7 @@
         <v>100019</v>
       </c>
       <c r="B21">
-        <f t="shared" si="1"/>
+        <f>INDEX(B:B,MATCH(100000,B:B,0),1)+(ROW()-MATCH(100000,B:B,0))</f>
         <v>100019</v>
       </c>
       <c r="D21">
@@ -9516,7 +9553,7 @@
         <v>100020</v>
       </c>
       <c r="B22">
-        <f t="shared" si="1"/>
+        <f>INDEX(B:B,MATCH(100000,B:B,0),1)+(ROW()-MATCH(100000,B:B,0))</f>
         <v>100020</v>
       </c>
       <c r="D22">
@@ -9547,7 +9584,7 @@
         <v>100021</v>
       </c>
       <c r="B23">
-        <f t="shared" si="1"/>
+        <f>INDEX(B:B,MATCH(100000,B:B,0),1)+(ROW()-MATCH(100000,B:B,0))</f>
         <v>100021</v>
       </c>
       <c r="D23">
@@ -9578,7 +9615,7 @@
         <v>100022</v>
       </c>
       <c r="B24">
-        <f t="shared" si="1"/>
+        <f>INDEX(B:B,MATCH(100000,B:B,0),1)+(ROW()-MATCH(100000,B:B,0))</f>
         <v>100022</v>
       </c>
       <c r="D24">
@@ -9609,7 +9646,7 @@
         <v>100023</v>
       </c>
       <c r="B25">
-        <f t="shared" si="1"/>
+        <f>INDEX(B:B,MATCH(100000,B:B,0),1)+(ROW()-MATCH(100000,B:B,0))</f>
         <v>100023</v>
       </c>
       <c r="D25">
@@ -9643,16 +9680,16 @@
         <v>100000</v>
       </c>
       <c r="C26" s="3" t="s">
-        <v>360</v>
+        <v>386</v>
       </c>
       <c r="D26" s="3">
         <v>0</v>
       </c>
       <c r="E26" s="3" t="s">
-        <v>373</v>
+        <v>124</v>
       </c>
       <c r="F26" s="3" t="s">
-        <v>374</v>
+        <v>122</v>
       </c>
       <c r="G26" s="3" t="s">
         <v>52</v>
@@ -9673,17 +9710,17 @@
         <v>100025</v>
       </c>
       <c r="B27">
-        <f t="shared" si="1"/>
+        <f>INDEX(B:B,MATCH(100000,B:B,0),1)+(ROW()-MATCH(100000,B:B,0))</f>
         <v>100025</v>
       </c>
       <c r="D27">
         <v>1</v>
       </c>
       <c r="E27" t="s">
-        <v>375</v>
+        <v>123</v>
       </c>
       <c r="F27" t="s">
-        <v>376</v>
+        <v>125</v>
       </c>
       <c r="G27" t="s">
         <v>85</v>
@@ -9704,20 +9741,20 @@
         <v>100026</v>
       </c>
       <c r="B28">
-        <f t="shared" si="1"/>
+        <f>INDEX(B:B,MATCH(100000,B:B,0),1)+(ROW()-MATCH(100000,B:B,0))</f>
         <v>100026</v>
       </c>
       <c r="D28">
         <v>2</v>
       </c>
       <c r="E28" t="s">
-        <v>377</v>
+        <v>126</v>
       </c>
       <c r="F28" t="s">
-        <v>378</v>
+        <v>128</v>
       </c>
       <c r="G28" t="s">
-        <v>379</v>
+        <v>127</v>
       </c>
       <c r="H28" t="s">
         <v>22</v>
@@ -9735,17 +9772,17 @@
         <v>100027</v>
       </c>
       <c r="B29">
-        <f t="shared" si="1"/>
+        <f>INDEX(B:B,MATCH(100000,B:B,0),1)+(ROW()-MATCH(100000,B:B,0))</f>
         <v>100027</v>
       </c>
       <c r="D29">
         <v>3</v>
       </c>
       <c r="E29" t="s">
-        <v>27</v>
+        <v>129</v>
       </c>
       <c r="F29" t="s">
-        <v>380</v>
+        <v>130</v>
       </c>
       <c r="G29" t="s">
         <v>28</v>
@@ -9766,17 +9803,17 @@
         <v>100028</v>
       </c>
       <c r="B30">
-        <f t="shared" si="1"/>
+        <f>INDEX(B:B,MATCH(100000,B:B,0),1)+(ROW()-MATCH(100000,B:B,0))</f>
         <v>100028</v>
       </c>
       <c r="D30">
         <v>4</v>
       </c>
       <c r="E30" t="s">
-        <v>381</v>
+        <v>43</v>
       </c>
       <c r="F30" t="s">
-        <v>382</v>
+        <v>82</v>
       </c>
       <c r="G30" t="s">
         <v>42</v>
@@ -9797,7 +9834,7 @@
         <v>100029</v>
       </c>
       <c r="B31">
-        <f t="shared" si="1"/>
+        <f>INDEX(B:B,MATCH(100000,B:B,0),1)+(ROW()-MATCH(100000,B:B,0))</f>
         <v>100029</v>
       </c>
       <c r="D31">
@@ -9807,7 +9844,7 @@
         <v>44</v>
       </c>
       <c r="F31" t="s">
-        <v>358</v>
+        <v>45</v>
       </c>
       <c r="G31" t="s">
         <v>83</v>
@@ -9828,7 +9865,7 @@
         <v>100030</v>
       </c>
       <c r="B32">
-        <f t="shared" si="1"/>
+        <f>INDEX(B:B,MATCH(100000,B:B,0),1)+(ROW()-MATCH(100000,B:B,0))</f>
         <v>100030</v>
       </c>
       <c r="D32">
@@ -9859,7 +9896,7 @@
         <v>100031</v>
       </c>
       <c r="B33">
-        <f t="shared" si="1"/>
+        <f>INDEX(B:B,MATCH(100000,B:B,0),1)+(ROW()-MATCH(100000,B:B,0))</f>
         <v>100031</v>
       </c>
       <c r="D33">
@@ -9875,7 +9912,7 @@
         <v>80</v>
       </c>
       <c r="H33" t="s">
-        <v>359</v>
+        <v>50</v>
       </c>
       <c r="I33" t="s">
         <v>12</v>
@@ -9890,20 +9927,20 @@
         <v>100032</v>
       </c>
       <c r="B34">
-        <f t="shared" si="1"/>
+        <f>INDEX(B:B,MATCH(100000,B:B,0),1)+(ROW()-MATCH(100000,B:B,0))</f>
         <v>100032</v>
       </c>
       <c r="D34">
         <v>8</v>
       </c>
       <c r="E34" t="s">
-        <v>367</v>
+        <v>94</v>
       </c>
       <c r="F34" t="s">
-        <v>361</v>
+        <v>95</v>
       </c>
       <c r="G34" t="s">
-        <v>362</v>
+        <v>96</v>
       </c>
       <c r="H34" t="s">
         <v>38</v>
@@ -9921,23 +9958,23 @@
         <v>100033</v>
       </c>
       <c r="B35">
-        <f t="shared" si="1"/>
+        <f>INDEX(B:B,MATCH(100000,B:B,0),1)+(ROW()-MATCH(100000,B:B,0))</f>
         <v>100033</v>
       </c>
       <c r="D35">
         <v>9</v>
       </c>
       <c r="E35" t="s">
-        <v>365</v>
+        <v>97</v>
       </c>
       <c r="F35" t="s">
-        <v>363</v>
+        <v>98</v>
       </c>
       <c r="G35" t="s">
-        <v>364</v>
+        <v>99</v>
       </c>
       <c r="H35" t="s">
-        <v>343</v>
+        <v>20</v>
       </c>
       <c r="I35" t="s">
         <v>10</v>
@@ -9952,20 +9989,20 @@
         <v>100034</v>
       </c>
       <c r="B36">
-        <f t="shared" si="1"/>
+        <f>INDEX(B:B,MATCH(100000,B:B,0),1)+(ROW()-MATCH(100000,B:B,0))</f>
         <v>100034</v>
       </c>
       <c r="D36">
         <v>10</v>
       </c>
       <c r="E36" t="s">
-        <v>366</v>
+        <v>100</v>
       </c>
       <c r="F36" t="s">
-        <v>368</v>
+        <v>101</v>
       </c>
       <c r="G36" t="s">
-        <v>369</v>
+        <v>102</v>
       </c>
       <c r="H36" t="s">
         <v>26</v>
@@ -9983,28 +10020,776 @@
         <v>100035</v>
       </c>
       <c r="B37">
-        <f t="shared" si="1"/>
+        <f>INDEX(B:B,MATCH(100000,B:B,0),1)+(ROW()-MATCH(100000,B:B,0))</f>
         <v>100035</v>
       </c>
       <c r="D37">
         <v>11</v>
       </c>
       <c r="E37" t="s">
-        <v>371</v>
+        <v>104</v>
       </c>
       <c r="F37" t="s">
-        <v>370</v>
+        <v>103</v>
       </c>
       <c r="G37" t="s">
-        <v>372</v>
+        <v>121</v>
       </c>
       <c r="H37" t="s">
-        <v>88</v>
+        <v>105</v>
       </c>
       <c r="I37" t="s">
         <v>12</v>
       </c>
       <c r="J37">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="38" spans="1:10" s="3" customFormat="1" x14ac:dyDescent="0.4">
+      <c r="A38" s="3">
+        <f>ROW()-2+100000</f>
+        <v>100036</v>
+      </c>
+      <c r="B38" s="3">
+        <v>100000</v>
+      </c>
+      <c r="C38" s="3" t="s">
+        <v>360</v>
+      </c>
+      <c r="D38" s="3">
+        <v>0</v>
+      </c>
+      <c r="E38" s="3" t="s">
+        <v>131</v>
+      </c>
+      <c r="F38" s="3" t="s">
+        <v>132</v>
+      </c>
+      <c r="G38" s="3" t="s">
+        <v>52</v>
+      </c>
+      <c r="H38" s="3" t="s">
+        <v>86</v>
+      </c>
+      <c r="I38" s="3" t="s">
+        <v>9</v>
+      </c>
+      <c r="J38" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="39" spans="1:10" x14ac:dyDescent="0.4">
+      <c r="A39">
+        <f t="shared" si="0"/>
+        <v>100037</v>
+      </c>
+      <c r="B39">
+        <f>INDEX(B:B,MATCH(100000,B:B,0),1)+(ROW()-MATCH(100000,B:B,0))</f>
+        <v>100037</v>
+      </c>
+      <c r="D39">
+        <v>1</v>
+      </c>
+      <c r="E39" t="s">
+        <v>133</v>
+      </c>
+      <c r="F39" t="s">
+        <v>134</v>
+      </c>
+      <c r="G39" t="s">
+        <v>85</v>
+      </c>
+      <c r="H39" t="s">
+        <v>14</v>
+      </c>
+      <c r="I39" t="s">
+        <v>10</v>
+      </c>
+      <c r="J39">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="40" spans="1:10" x14ac:dyDescent="0.4">
+      <c r="A40">
+        <f t="shared" si="0"/>
+        <v>100038</v>
+      </c>
+      <c r="B40">
+        <f>INDEX(B:B,MATCH(100000,B:B,0),1)+(ROW()-MATCH(100000,B:B,0))</f>
+        <v>100038</v>
+      </c>
+      <c r="D40">
+        <v>2</v>
+      </c>
+      <c r="E40" t="s">
+        <v>195</v>
+      </c>
+      <c r="F40" t="s">
+        <v>196</v>
+      </c>
+      <c r="G40" t="s">
+        <v>84</v>
+      </c>
+      <c r="H40" t="s">
+        <v>22</v>
+      </c>
+      <c r="I40" t="s">
+        <v>11</v>
+      </c>
+      <c r="J40">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="41" spans="1:10" x14ac:dyDescent="0.4">
+      <c r="A41">
+        <f t="shared" si="0"/>
+        <v>100039</v>
+      </c>
+      <c r="B41">
+        <f>INDEX(B:B,MATCH(100000,B:B,0),1)+(ROW()-MATCH(100000,B:B,0))</f>
+        <v>100039</v>
+      </c>
+      <c r="D41">
+        <v>3</v>
+      </c>
+      <c r="E41" t="s">
+        <v>135</v>
+      </c>
+      <c r="F41" t="s">
+        <v>197</v>
+      </c>
+      <c r="G41" t="s">
+        <v>136</v>
+      </c>
+      <c r="H41" t="s">
+        <v>137</v>
+      </c>
+      <c r="I41" t="s">
+        <v>12</v>
+      </c>
+      <c r="J41">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="42" spans="1:10" x14ac:dyDescent="0.4">
+      <c r="A42">
+        <f t="shared" si="0"/>
+        <v>100040</v>
+      </c>
+      <c r="B42">
+        <f>INDEX(B:B,MATCH(100000,B:B,0),1)+(ROW()-MATCH(100000,B:B,0))</f>
+        <v>100040</v>
+      </c>
+      <c r="D42">
+        <v>4</v>
+      </c>
+      <c r="E42" t="s">
+        <v>43</v>
+      </c>
+      <c r="F42" t="s">
+        <v>82</v>
+      </c>
+      <c r="G42" t="s">
+        <v>42</v>
+      </c>
+      <c r="H42" t="s">
+        <v>18</v>
+      </c>
+      <c r="I42" t="s">
+        <v>36</v>
+      </c>
+      <c r="J42">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="43" spans="1:10" x14ac:dyDescent="0.4">
+      <c r="A43">
+        <f t="shared" si="0"/>
+        <v>100041</v>
+      </c>
+      <c r="B43">
+        <f>INDEX(B:B,MATCH(100000,B:B,0),1)+(ROW()-MATCH(100000,B:B,0))</f>
+        <v>100041</v>
+      </c>
+      <c r="D43">
+        <v>5</v>
+      </c>
+      <c r="E43" t="s">
+        <v>44</v>
+      </c>
+      <c r="F43" t="s">
+        <v>45</v>
+      </c>
+      <c r="G43" t="s">
+        <v>83</v>
+      </c>
+      <c r="H43" t="s">
+        <v>17</v>
+      </c>
+      <c r="I43" t="s">
+        <v>10</v>
+      </c>
+      <c r="J43">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="44" spans="1:10" x14ac:dyDescent="0.4">
+      <c r="A44">
+        <f t="shared" si="0"/>
+        <v>100042</v>
+      </c>
+      <c r="B44">
+        <f>INDEX(B:B,MATCH(100000,B:B,0),1)+(ROW()-MATCH(100000,B:B,0))</f>
+        <v>100042</v>
+      </c>
+      <c r="D44">
+        <v>6</v>
+      </c>
+      <c r="E44" t="s">
+        <v>23</v>
+      </c>
+      <c r="F44" t="s">
+        <v>79</v>
+      </c>
+      <c r="G44" t="s">
+        <v>78</v>
+      </c>
+      <c r="H44" t="s">
+        <v>48</v>
+      </c>
+      <c r="I44" t="s">
+        <v>11</v>
+      </c>
+      <c r="J44">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="45" spans="1:10" x14ac:dyDescent="0.4">
+      <c r="A45">
+        <f t="shared" si="0"/>
+        <v>100043</v>
+      </c>
+      <c r="B45">
+        <f>INDEX(B:B,MATCH(100000,B:B,0),1)+(ROW()-MATCH(100000,B:B,0))</f>
+        <v>100043</v>
+      </c>
+      <c r="D45">
+        <v>7</v>
+      </c>
+      <c r="E45" t="s">
+        <v>31</v>
+      </c>
+      <c r="F45" t="s">
+        <v>49</v>
+      </c>
+      <c r="G45" t="s">
+        <v>80</v>
+      </c>
+      <c r="H45" t="s">
+        <v>50</v>
+      </c>
+      <c r="I45" t="s">
+        <v>12</v>
+      </c>
+      <c r="J45">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="46" spans="1:10" x14ac:dyDescent="0.4">
+      <c r="A46">
+        <f t="shared" si="0"/>
+        <v>100044</v>
+      </c>
+      <c r="B46">
+        <f>INDEX(B:B,MATCH(100000,B:B,0),1)+(ROW()-MATCH(100000,B:B,0))</f>
+        <v>100044</v>
+      </c>
+      <c r="D46">
+        <v>8</v>
+      </c>
+      <c r="E46" t="s">
+        <v>113</v>
+      </c>
+      <c r="F46" t="s">
+        <v>108</v>
+      </c>
+      <c r="G46" t="s">
+        <v>107</v>
+      </c>
+      <c r="H46" t="s">
+        <v>38</v>
+      </c>
+      <c r="I46" t="s">
+        <v>37</v>
+      </c>
+      <c r="J46">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="47" spans="1:10" x14ac:dyDescent="0.4">
+      <c r="A47">
+        <f t="shared" si="0"/>
+        <v>100045</v>
+      </c>
+      <c r="B47">
+        <f>INDEX(B:B,MATCH(100000,B:B,0),1)+(ROW()-MATCH(100000,B:B,0))</f>
+        <v>100045</v>
+      </c>
+      <c r="D47">
+        <v>9</v>
+      </c>
+      <c r="E47" t="s">
+        <v>109</v>
+      </c>
+      <c r="F47" t="s">
+        <v>110</v>
+      </c>
+      <c r="G47" t="s">
+        <v>111</v>
+      </c>
+      <c r="H47" t="s">
+        <v>20</v>
+      </c>
+      <c r="I47" t="s">
+        <v>10</v>
+      </c>
+      <c r="J47">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="48" spans="1:10" x14ac:dyDescent="0.4">
+      <c r="A48">
+        <f t="shared" si="0"/>
+        <v>100046</v>
+      </c>
+      <c r="B48">
+        <f>INDEX(B:B,MATCH(100000,B:B,0),1)+(ROW()-MATCH(100000,B:B,0))</f>
+        <v>100046</v>
+      </c>
+      <c r="D48">
+        <v>10</v>
+      </c>
+      <c r="E48" t="s">
+        <v>112</v>
+      </c>
+      <c r="F48" t="s">
+        <v>114</v>
+      </c>
+      <c r="G48" t="s">
+        <v>115</v>
+      </c>
+      <c r="H48" t="s">
+        <v>26</v>
+      </c>
+      <c r="I48" t="s">
+        <v>11</v>
+      </c>
+      <c r="J48">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="49" spans="1:10" x14ac:dyDescent="0.4">
+      <c r="A49">
+        <f t="shared" si="0"/>
+        <v>100047</v>
+      </c>
+      <c r="B49">
+        <f>INDEX(B:B,MATCH(100000,B:B,0),1)+(ROW()-MATCH(100000,B:B,0))</f>
+        <v>100047</v>
+      </c>
+      <c r="D49">
+        <v>11</v>
+      </c>
+      <c r="E49" t="s">
+        <v>116</v>
+      </c>
+      <c r="F49" t="s">
+        <v>117</v>
+      </c>
+      <c r="G49" t="s">
+        <v>118</v>
+      </c>
+      <c r="H49" t="s">
+        <v>119</v>
+      </c>
+      <c r="I49" t="s">
+        <v>12</v>
+      </c>
+      <c r="J49">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="50" spans="1:10" s="3" customFormat="1" x14ac:dyDescent="0.4">
+      <c r="A50" s="3">
+        <f>ROW()-2+100000</f>
+        <v>100048</v>
+      </c>
+      <c r="B50" s="3">
+        <v>100000</v>
+      </c>
+      <c r="C50" s="3" t="s">
+        <v>382</v>
+      </c>
+      <c r="D50" s="3">
+        <v>0</v>
+      </c>
+      <c r="E50" s="3" t="s">
+        <v>383</v>
+      </c>
+      <c r="F50" s="3" t="s">
+        <v>371</v>
+      </c>
+      <c r="G50" s="3" t="s">
+        <v>52</v>
+      </c>
+      <c r="H50" s="3" t="s">
+        <v>86</v>
+      </c>
+      <c r="I50" s="3" t="s">
+        <v>9</v>
+      </c>
+      <c r="J50" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="51" spans="1:10" x14ac:dyDescent="0.4">
+      <c r="A51">
+        <f t="shared" si="0"/>
+        <v>100049</v>
+      </c>
+      <c r="B51">
+        <f>INDEX(B:B,MATCH(100000,B:B,0),1)+(ROW()-MATCH(100000,B:B,0))</f>
+        <v>100049</v>
+      </c>
+      <c r="D51">
+        <v>1</v>
+      </c>
+      <c r="E51" t="s">
+        <v>384</v>
+      </c>
+      <c r="F51" t="s">
+        <v>385</v>
+      </c>
+      <c r="G51" t="s">
+        <v>85</v>
+      </c>
+      <c r="H51" t="s">
+        <v>14</v>
+      </c>
+      <c r="I51" t="s">
+        <v>10</v>
+      </c>
+      <c r="J51">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="52" spans="1:10" x14ac:dyDescent="0.4">
+      <c r="A52">
+        <f t="shared" si="0"/>
+        <v>100050</v>
+      </c>
+      <c r="B52">
+        <f>INDEX(B:B,MATCH(100000,B:B,0),1)+(ROW()-MATCH(100000,B:B,0))</f>
+        <v>100050</v>
+      </c>
+      <c r="D52">
+        <v>2</v>
+      </c>
+      <c r="E52" t="s">
+        <v>372</v>
+      </c>
+      <c r="F52" t="s">
+        <v>373</v>
+      </c>
+      <c r="G52" t="s">
+        <v>374</v>
+      </c>
+      <c r="H52" t="s">
+        <v>22</v>
+      </c>
+      <c r="I52" t="s">
+        <v>11</v>
+      </c>
+      <c r="J52">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="53" spans="1:10" x14ac:dyDescent="0.4">
+      <c r="A53">
+        <f t="shared" si="0"/>
+        <v>100051</v>
+      </c>
+      <c r="B53">
+        <f>INDEX(B:B,MATCH(100000,B:B,0),1)+(ROW()-MATCH(100000,B:B,0))</f>
+        <v>100051</v>
+      </c>
+      <c r="D53">
+        <v>3</v>
+      </c>
+      <c r="E53" t="s">
+        <v>27</v>
+      </c>
+      <c r="F53" t="s">
+        <v>375</v>
+      </c>
+      <c r="G53" t="s">
+        <v>28</v>
+      </c>
+      <c r="H53" t="s">
+        <v>30</v>
+      </c>
+      <c r="I53" t="s">
+        <v>12</v>
+      </c>
+      <c r="J53">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="54" spans="1:10" x14ac:dyDescent="0.4">
+      <c r="A54">
+        <f t="shared" si="0"/>
+        <v>100052</v>
+      </c>
+      <c r="B54">
+        <f>INDEX(B:B,MATCH(100000,B:B,0),1)+(ROW()-MATCH(100000,B:B,0))</f>
+        <v>100052</v>
+      </c>
+      <c r="D54">
+        <v>4</v>
+      </c>
+      <c r="E54" t="s">
+        <v>376</v>
+      </c>
+      <c r="F54" t="s">
+        <v>377</v>
+      </c>
+      <c r="G54" t="s">
+        <v>42</v>
+      </c>
+      <c r="H54" t="s">
+        <v>18</v>
+      </c>
+      <c r="I54" t="s">
+        <v>36</v>
+      </c>
+      <c r="J54">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="55" spans="1:10" x14ac:dyDescent="0.4">
+      <c r="A55">
+        <f t="shared" si="0"/>
+        <v>100053</v>
+      </c>
+      <c r="B55">
+        <f>INDEX(B:B,MATCH(100000,B:B,0),1)+(ROW()-MATCH(100000,B:B,0))</f>
+        <v>100053</v>
+      </c>
+      <c r="D55">
+        <v>5</v>
+      </c>
+      <c r="E55" t="s">
+        <v>44</v>
+      </c>
+      <c r="F55" t="s">
+        <v>358</v>
+      </c>
+      <c r="G55" t="s">
+        <v>83</v>
+      </c>
+      <c r="H55" t="s">
+        <v>17</v>
+      </c>
+      <c r="I55" t="s">
+        <v>10</v>
+      </c>
+      <c r="J55">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="56" spans="1:10" x14ac:dyDescent="0.4">
+      <c r="A56">
+        <f t="shared" si="0"/>
+        <v>100054</v>
+      </c>
+      <c r="B56">
+        <f>INDEX(B:B,MATCH(100000,B:B,0),1)+(ROW()-MATCH(100000,B:B,0))</f>
+        <v>100054</v>
+      </c>
+      <c r="D56">
+        <v>6</v>
+      </c>
+      <c r="E56" t="s">
+        <v>23</v>
+      </c>
+      <c r="F56" t="s">
+        <v>79</v>
+      </c>
+      <c r="G56" t="s">
+        <v>78</v>
+      </c>
+      <c r="H56" t="s">
+        <v>48</v>
+      </c>
+      <c r="I56" t="s">
+        <v>11</v>
+      </c>
+      <c r="J56">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="57" spans="1:10" x14ac:dyDescent="0.4">
+      <c r="A57">
+        <f t="shared" si="0"/>
+        <v>100055</v>
+      </c>
+      <c r="B57">
+        <f>INDEX(B:B,MATCH(100000,B:B,0),1)+(ROW()-MATCH(100000,B:B,0))</f>
+        <v>100055</v>
+      </c>
+      <c r="D57">
+        <v>7</v>
+      </c>
+      <c r="E57" t="s">
+        <v>31</v>
+      </c>
+      <c r="F57" t="s">
+        <v>49</v>
+      </c>
+      <c r="G57" t="s">
+        <v>80</v>
+      </c>
+      <c r="H57" t="s">
+        <v>359</v>
+      </c>
+      <c r="I57" t="s">
+        <v>12</v>
+      </c>
+      <c r="J57">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="58" spans="1:10" x14ac:dyDescent="0.4">
+      <c r="A58">
+        <f t="shared" si="0"/>
+        <v>100056</v>
+      </c>
+      <c r="B58">
+        <f>INDEX(B:B,MATCH(100000,B:B,0),1)+(ROW()-MATCH(100000,B:B,0))</f>
+        <v>100056</v>
+      </c>
+      <c r="D58">
+        <v>8</v>
+      </c>
+      <c r="E58" t="s">
+        <v>365</v>
+      </c>
+      <c r="F58" t="s">
+        <v>361</v>
+      </c>
+      <c r="G58" t="s">
+        <v>362</v>
+      </c>
+      <c r="H58" t="s">
+        <v>38</v>
+      </c>
+      <c r="I58" t="s">
+        <v>37</v>
+      </c>
+      <c r="J58">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="59" spans="1:10" x14ac:dyDescent="0.4">
+      <c r="A59">
+        <f t="shared" si="0"/>
+        <v>100057</v>
+      </c>
+      <c r="B59">
+        <f>INDEX(B:B,MATCH(100000,B:B,0),1)+(ROW()-MATCH(100000,B:B,0))</f>
+        <v>100057</v>
+      </c>
+      <c r="D59">
+        <v>9</v>
+      </c>
+      <c r="E59" t="s">
+        <v>363</v>
+      </c>
+      <c r="F59" t="s">
+        <v>378</v>
+      </c>
+      <c r="G59" t="s">
+        <v>379</v>
+      </c>
+      <c r="H59" t="s">
+        <v>343</v>
+      </c>
+      <c r="I59" t="s">
+        <v>10</v>
+      </c>
+      <c r="J59">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="60" spans="1:10" x14ac:dyDescent="0.4">
+      <c r="A60">
+        <f t="shared" si="0"/>
+        <v>100058</v>
+      </c>
+      <c r="B60">
+        <f>INDEX(B:B,MATCH(100000,B:B,0),1)+(ROW()-MATCH(100000,B:B,0))</f>
+        <v>100058</v>
+      </c>
+      <c r="D60">
+        <v>10</v>
+      </c>
+      <c r="E60" t="s">
+        <v>364</v>
+      </c>
+      <c r="F60" t="s">
+        <v>366</v>
+      </c>
+      <c r="G60" t="s">
+        <v>367</v>
+      </c>
+      <c r="H60" t="s">
+        <v>26</v>
+      </c>
+      <c r="I60" t="s">
+        <v>11</v>
+      </c>
+      <c r="J60">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="61" spans="1:10" x14ac:dyDescent="0.4">
+      <c r="A61">
+        <f t="shared" si="0"/>
+        <v>100059</v>
+      </c>
+      <c r="B61">
+        <f>INDEX(B:B,MATCH(100000,B:B,0),1)+(ROW()-MATCH(100000,B:B,0))</f>
+        <v>100059</v>
+      </c>
+      <c r="D61">
+        <v>11</v>
+      </c>
+      <c r="E61" t="s">
+        <v>369</v>
+      </c>
+      <c r="F61" t="s">
+        <v>368</v>
+      </c>
+      <c r="G61" t="s">
+        <v>370</v>
+      </c>
+      <c r="H61" t="s">
+        <v>88</v>
+      </c>
+      <c r="I61" t="s">
+        <v>12</v>
+      </c>
+      <c r="J61">
         <v>1</v>
       </c>
     </row>

--- a/Assets/Resources/Excel/Entity_ContestCommentDataBase.xlsx
+++ b/Assets/Resources/Excel/Entity_ContestCommentDataBase.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29231"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29328"/>
   <workbookPr defaultThemeVersion="166925"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\aritashogo\Documents\Unity\Okashi_Atlier2\Assets\Resources\Excel\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{0C7E4AF3-2A0F-4C93-B87B-23D223729081}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{7023074C-02FC-4B8A-936C-D2BB22F71FD8}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="915" yWindow="390" windowWidth="25485" windowHeight="14370" activeTab="2" xr2:uid="{1DCE2773-8A3B-4011-B3F4-E2EABC03DB8B}"/>
+    <workbookView xWindow="1875" yWindow="1080" windowWidth="25485" windowHeight="14370" activeTab="3" xr2:uid="{1DCE2773-8A3B-4011-B3F4-E2EABC03DB8B}"/>
   </bookViews>
   <sheets>
     <sheet name="01_ContestComment" sheetId="1" r:id="rId1"/>
@@ -3624,17 +3624,6 @@
     <phoneticPr fontId="2"/>
   </si>
   <si>
-    <t>あまりキラキラ感はでていないようでした。</t>
-    <rPh sb="7" eb="8">
-      <t>カン</t>
-    </rPh>
-    <phoneticPr fontId="2"/>
-  </si>
-  <si>
-    <t>もっと、キラキラがほしいところです。</t>
-    <phoneticPr fontId="2"/>
-  </si>
-  <si>
     <t>芸術的なおかしという点でいうと..。</t>
     <rPh sb="0" eb="3">
       <t>ゲイジュツテキ</t>
@@ -4628,6 +4617,29 @@
   </si>
   <si>
     <t>Tea_Default</t>
+    <phoneticPr fontId="2"/>
+  </si>
+  <si>
+    <t>キラキラさが少し足りていないようですね..。</t>
+    <rPh sb="6" eb="7">
+      <t>スコ</t>
+    </rPh>
+    <rPh sb="8" eb="9">
+      <t>タ</t>
+    </rPh>
+    <phoneticPr fontId="2"/>
+  </si>
+  <si>
+    <t>もっと、キラキラさと輝きのあるお菓子に期待したいところです。</t>
+    <rPh sb="10" eb="11">
+      <t>カガヤ</t>
+    </rPh>
+    <rPh sb="16" eb="18">
+      <t>カシ</t>
+    </rPh>
+    <rPh sb="19" eb="21">
+      <t>キタイ</t>
+    </rPh>
     <phoneticPr fontId="2"/>
   </si>
 </sst>
@@ -7775,7 +7787,7 @@
         <v>86</v>
       </c>
       <c r="I2" s="3" t="s">
-        <v>380</v>
+        <v>378</v>
       </c>
       <c r="J2" s="3">
         <v>0</v>
@@ -8950,7 +8962,7 @@
         <v>86</v>
       </c>
       <c r="I2" s="3" t="s">
-        <v>381</v>
+        <v>379</v>
       </c>
       <c r="J2" s="3">
         <v>0</v>
@@ -8962,7 +8974,7 @@
         <v>100001</v>
       </c>
       <c r="B3">
-        <f>INDEX(B:B,MATCH(100000,B:B,0),1)+(ROW()-MATCH(100000,B:B,0))</f>
+        <f t="shared" ref="B3:B13" si="1">INDEX(B:B,MATCH(100000,B:B,0),1)+(ROW()-MATCH(100000,B:B,0))</f>
         <v>100001</v>
       </c>
       <c r="D3">
@@ -8993,7 +9005,7 @@
         <v>100002</v>
       </c>
       <c r="B4">
-        <f>INDEX(B:B,MATCH(100000,B:B,0),1)+(ROW()-MATCH(100000,B:B,0))</f>
+        <f t="shared" si="1"/>
         <v>100002</v>
       </c>
       <c r="D4">
@@ -9024,7 +9036,7 @@
         <v>100003</v>
       </c>
       <c r="B5">
-        <f>INDEX(B:B,MATCH(100000,B:B,0),1)+(ROW()-MATCH(100000,B:B,0))</f>
+        <f t="shared" si="1"/>
         <v>100003</v>
       </c>
       <c r="D5">
@@ -9055,7 +9067,7 @@
         <v>100004</v>
       </c>
       <c r="B6">
-        <f>INDEX(B:B,MATCH(100000,B:B,0),1)+(ROW()-MATCH(100000,B:B,0))</f>
+        <f t="shared" si="1"/>
         <v>100004</v>
       </c>
       <c r="D6">
@@ -9086,7 +9098,7 @@
         <v>100005</v>
       </c>
       <c r="B7">
-        <f>INDEX(B:B,MATCH(100000,B:B,0),1)+(ROW()-MATCH(100000,B:B,0))</f>
+        <f t="shared" si="1"/>
         <v>100005</v>
       </c>
       <c r="D7">
@@ -9117,7 +9129,7 @@
         <v>100006</v>
       </c>
       <c r="B8">
-        <f>INDEX(B:B,MATCH(100000,B:B,0),1)+(ROW()-MATCH(100000,B:B,0))</f>
+        <f t="shared" si="1"/>
         <v>100006</v>
       </c>
       <c r="D8">
@@ -9148,7 +9160,7 @@
         <v>100007</v>
       </c>
       <c r="B9">
-        <f>INDEX(B:B,MATCH(100000,B:B,0),1)+(ROW()-MATCH(100000,B:B,0))</f>
+        <f t="shared" si="1"/>
         <v>100007</v>
       </c>
       <c r="D9">
@@ -9179,7 +9191,7 @@
         <v>100008</v>
       </c>
       <c r="B10">
-        <f>INDEX(B:B,MATCH(100000,B:B,0),1)+(ROW()-MATCH(100000,B:B,0))</f>
+        <f t="shared" si="1"/>
         <v>100008</v>
       </c>
       <c r="D10">
@@ -9210,7 +9222,7 @@
         <v>100009</v>
       </c>
       <c r="B11">
-        <f>INDEX(B:B,MATCH(100000,B:B,0),1)+(ROW()-MATCH(100000,B:B,0))</f>
+        <f t="shared" si="1"/>
         <v>100009</v>
       </c>
       <c r="D11">
@@ -9241,7 +9253,7 @@
         <v>100010</v>
       </c>
       <c r="B12">
-        <f>INDEX(B:B,MATCH(100000,B:B,0),1)+(ROW()-MATCH(100000,B:B,0))</f>
+        <f t="shared" si="1"/>
         <v>100010</v>
       </c>
       <c r="D12">
@@ -9272,7 +9284,7 @@
         <v>100011</v>
       </c>
       <c r="B13">
-        <f>INDEX(B:B,MATCH(100000,B:B,0),1)+(ROW()-MATCH(100000,B:B,0))</f>
+        <f t="shared" si="1"/>
         <v>100011</v>
       </c>
       <c r="D13">
@@ -9306,16 +9318,16 @@
         <v>100000</v>
       </c>
       <c r="C14" s="3" t="s">
-        <v>336</v>
+        <v>334</v>
       </c>
       <c r="D14" s="3">
         <v>0</v>
       </c>
       <c r="E14" s="3" t="s">
-        <v>350</v>
+        <v>348</v>
       </c>
       <c r="F14" s="3" t="s">
-        <v>351</v>
+        <v>349</v>
       </c>
       <c r="G14" s="3" t="s">
         <v>52</v>
@@ -9336,7 +9348,7 @@
         <v>100013</v>
       </c>
       <c r="B15">
-        <f>INDEX(B:B,MATCH(100000,B:B,0),1)+(ROW()-MATCH(100000,B:B,0))</f>
+        <f t="shared" ref="B15:B25" si="2">INDEX(B:B,MATCH(100000,B:B,0),1)+(ROW()-MATCH(100000,B:B,0))</f>
         <v>100013</v>
       </c>
       <c r="D15">
@@ -9346,7 +9358,7 @@
         <v>16</v>
       </c>
       <c r="F15" t="s">
-        <v>352</v>
+        <v>350</v>
       </c>
       <c r="G15" t="s">
         <v>85</v>
@@ -9367,7 +9379,7 @@
         <v>100014</v>
       </c>
       <c r="B16">
-        <f>INDEX(B:B,MATCH(100000,B:B,0),1)+(ROW()-MATCH(100000,B:B,0))</f>
+        <f t="shared" si="2"/>
         <v>100014</v>
       </c>
       <c r="D16">
@@ -9377,10 +9389,10 @@
         <v>54</v>
       </c>
       <c r="F16" t="s">
-        <v>353</v>
+        <v>351</v>
       </c>
       <c r="G16" t="s">
-        <v>354</v>
+        <v>352</v>
       </c>
       <c r="H16" t="s">
         <v>22</v>
@@ -9398,7 +9410,7 @@
         <v>100015</v>
       </c>
       <c r="B17">
-        <f>INDEX(B:B,MATCH(100000,B:B,0),1)+(ROW()-MATCH(100000,B:B,0))</f>
+        <f t="shared" si="2"/>
         <v>100015</v>
       </c>
       <c r="D17">
@@ -9408,7 +9420,7 @@
         <v>27</v>
       </c>
       <c r="F17" t="s">
-        <v>355</v>
+        <v>353</v>
       </c>
       <c r="G17" t="s">
         <v>28</v>
@@ -9429,17 +9441,17 @@
         <v>100016</v>
       </c>
       <c r="B18">
-        <f>INDEX(B:B,MATCH(100000,B:B,0),1)+(ROW()-MATCH(100000,B:B,0))</f>
+        <f t="shared" si="2"/>
         <v>100016</v>
       </c>
       <c r="D18">
         <v>4</v>
       </c>
       <c r="E18" t="s">
-        <v>356</v>
+        <v>354</v>
       </c>
       <c r="F18" t="s">
-        <v>357</v>
+        <v>355</v>
       </c>
       <c r="G18" t="s">
         <v>42</v>
@@ -9460,7 +9472,7 @@
         <v>100017</v>
       </c>
       <c r="B19">
-        <f>INDEX(B:B,MATCH(100000,B:B,0),1)+(ROW()-MATCH(100000,B:B,0))</f>
+        <f t="shared" si="2"/>
         <v>100017</v>
       </c>
       <c r="D19">
@@ -9470,7 +9482,7 @@
         <v>44</v>
       </c>
       <c r="F19" t="s">
-        <v>358</v>
+        <v>356</v>
       </c>
       <c r="G19" t="s">
         <v>83</v>
@@ -9491,7 +9503,7 @@
         <v>100018</v>
       </c>
       <c r="B20">
-        <f>INDEX(B:B,MATCH(100000,B:B,0),1)+(ROW()-MATCH(100000,B:B,0))</f>
+        <f t="shared" si="2"/>
         <v>100018</v>
       </c>
       <c r="D20">
@@ -9522,7 +9534,7 @@
         <v>100019</v>
       </c>
       <c r="B21">
-        <f>INDEX(B:B,MATCH(100000,B:B,0),1)+(ROW()-MATCH(100000,B:B,0))</f>
+        <f t="shared" si="2"/>
         <v>100019</v>
       </c>
       <c r="D21">
@@ -9538,7 +9550,7 @@
         <v>80</v>
       </c>
       <c r="H21" t="s">
-        <v>359</v>
+        <v>357</v>
       </c>
       <c r="I21" t="s">
         <v>12</v>
@@ -9553,20 +9565,20 @@
         <v>100020</v>
       </c>
       <c r="B22">
-        <f>INDEX(B:B,MATCH(100000,B:B,0),1)+(ROW()-MATCH(100000,B:B,0))</f>
+        <f t="shared" si="2"/>
         <v>100020</v>
       </c>
       <c r="D22">
         <v>8</v>
       </c>
       <c r="E22" t="s">
-        <v>338</v>
+        <v>336</v>
       </c>
       <c r="F22" t="s">
+        <v>335</v>
+      </c>
+      <c r="G22" t="s">
         <v>337</v>
-      </c>
-      <c r="G22" t="s">
-        <v>339</v>
       </c>
       <c r="H22" t="s">
         <v>38</v>
@@ -9584,23 +9596,23 @@
         <v>100021</v>
       </c>
       <c r="B23">
-        <f>INDEX(B:B,MATCH(100000,B:B,0),1)+(ROW()-MATCH(100000,B:B,0))</f>
+        <f t="shared" si="2"/>
         <v>100021</v>
       </c>
       <c r="D23">
         <v>9</v>
       </c>
       <c r="E23" t="s">
+        <v>338</v>
+      </c>
+      <c r="F23" t="s">
+        <v>339</v>
+      </c>
+      <c r="G23" t="s">
         <v>340</v>
       </c>
-      <c r="F23" t="s">
+      <c r="H23" t="s">
         <v>341</v>
-      </c>
-      <c r="G23" t="s">
-        <v>342</v>
-      </c>
-      <c r="H23" t="s">
-        <v>343</v>
       </c>
       <c r="I23" t="s">
         <v>10</v>
@@ -9615,20 +9627,20 @@
         <v>100022</v>
       </c>
       <c r="B24">
-        <f>INDEX(B:B,MATCH(100000,B:B,0),1)+(ROW()-MATCH(100000,B:B,0))</f>
+        <f t="shared" si="2"/>
         <v>100022</v>
       </c>
       <c r="D24">
         <v>10</v>
       </c>
       <c r="E24" t="s">
+        <v>342</v>
+      </c>
+      <c r="F24" t="s">
+        <v>343</v>
+      </c>
+      <c r="G24" t="s">
         <v>344</v>
-      </c>
-      <c r="F24" t="s">
-        <v>345</v>
-      </c>
-      <c r="G24" t="s">
-        <v>346</v>
       </c>
       <c r="H24" t="s">
         <v>26</v>
@@ -9646,20 +9658,20 @@
         <v>100023</v>
       </c>
       <c r="B25">
-        <f>INDEX(B:B,MATCH(100000,B:B,0),1)+(ROW()-MATCH(100000,B:B,0))</f>
+        <f t="shared" si="2"/>
         <v>100023</v>
       </c>
       <c r="D25">
         <v>11</v>
       </c>
       <c r="E25" t="s">
+        <v>345</v>
+      </c>
+      <c r="F25" t="s">
+        <v>346</v>
+      </c>
+      <c r="G25" t="s">
         <v>347</v>
-      </c>
-      <c r="F25" t="s">
-        <v>348</v>
-      </c>
-      <c r="G25" t="s">
-        <v>349</v>
       </c>
       <c r="H25" t="s">
         <v>88</v>
@@ -9680,7 +9692,7 @@
         <v>100000</v>
       </c>
       <c r="C26" s="3" t="s">
-        <v>386</v>
+        <v>384</v>
       </c>
       <c r="D26" s="3">
         <v>0</v>
@@ -9710,7 +9722,7 @@
         <v>100025</v>
       </c>
       <c r="B27">
-        <f>INDEX(B:B,MATCH(100000,B:B,0),1)+(ROW()-MATCH(100000,B:B,0))</f>
+        <f t="shared" ref="B27:B37" si="3">INDEX(B:B,MATCH(100000,B:B,0),1)+(ROW()-MATCH(100000,B:B,0))</f>
         <v>100025</v>
       </c>
       <c r="D27">
@@ -9741,7 +9753,7 @@
         <v>100026</v>
       </c>
       <c r="B28">
-        <f>INDEX(B:B,MATCH(100000,B:B,0),1)+(ROW()-MATCH(100000,B:B,0))</f>
+        <f t="shared" si="3"/>
         <v>100026</v>
       </c>
       <c r="D28">
@@ -9772,7 +9784,7 @@
         <v>100027</v>
       </c>
       <c r="B29">
-        <f>INDEX(B:B,MATCH(100000,B:B,0),1)+(ROW()-MATCH(100000,B:B,0))</f>
+        <f t="shared" si="3"/>
         <v>100027</v>
       </c>
       <c r="D29">
@@ -9803,7 +9815,7 @@
         <v>100028</v>
       </c>
       <c r="B30">
-        <f>INDEX(B:B,MATCH(100000,B:B,0),1)+(ROW()-MATCH(100000,B:B,0))</f>
+        <f t="shared" si="3"/>
         <v>100028</v>
       </c>
       <c r="D30">
@@ -9834,7 +9846,7 @@
         <v>100029</v>
       </c>
       <c r="B31">
-        <f>INDEX(B:B,MATCH(100000,B:B,0),1)+(ROW()-MATCH(100000,B:B,0))</f>
+        <f t="shared" si="3"/>
         <v>100029</v>
       </c>
       <c r="D31">
@@ -9865,7 +9877,7 @@
         <v>100030</v>
       </c>
       <c r="B32">
-        <f>INDEX(B:B,MATCH(100000,B:B,0),1)+(ROW()-MATCH(100000,B:B,0))</f>
+        <f t="shared" si="3"/>
         <v>100030</v>
       </c>
       <c r="D32">
@@ -9896,7 +9908,7 @@
         <v>100031</v>
       </c>
       <c r="B33">
-        <f>INDEX(B:B,MATCH(100000,B:B,0),1)+(ROW()-MATCH(100000,B:B,0))</f>
+        <f t="shared" si="3"/>
         <v>100031</v>
       </c>
       <c r="D33">
@@ -9927,7 +9939,7 @@
         <v>100032</v>
       </c>
       <c r="B34">
-        <f>INDEX(B:B,MATCH(100000,B:B,0),1)+(ROW()-MATCH(100000,B:B,0))</f>
+        <f t="shared" si="3"/>
         <v>100032</v>
       </c>
       <c r="D34">
@@ -9958,7 +9970,7 @@
         <v>100033</v>
       </c>
       <c r="B35">
-        <f>INDEX(B:B,MATCH(100000,B:B,0),1)+(ROW()-MATCH(100000,B:B,0))</f>
+        <f t="shared" si="3"/>
         <v>100033</v>
       </c>
       <c r="D35">
@@ -9989,7 +10001,7 @@
         <v>100034</v>
       </c>
       <c r="B36">
-        <f>INDEX(B:B,MATCH(100000,B:B,0),1)+(ROW()-MATCH(100000,B:B,0))</f>
+        <f t="shared" si="3"/>
         <v>100034</v>
       </c>
       <c r="D36">
@@ -10020,7 +10032,7 @@
         <v>100035</v>
       </c>
       <c r="B37">
-        <f>INDEX(B:B,MATCH(100000,B:B,0),1)+(ROW()-MATCH(100000,B:B,0))</f>
+        <f t="shared" si="3"/>
         <v>100035</v>
       </c>
       <c r="D37">
@@ -10054,7 +10066,7 @@
         <v>100000</v>
       </c>
       <c r="C38" s="3" t="s">
-        <v>360</v>
+        <v>358</v>
       </c>
       <c r="D38" s="3">
         <v>0</v>
@@ -10084,7 +10096,7 @@
         <v>100037</v>
       </c>
       <c r="B39">
-        <f>INDEX(B:B,MATCH(100000,B:B,0),1)+(ROW()-MATCH(100000,B:B,0))</f>
+        <f t="shared" ref="B39:B49" si="4">INDEX(B:B,MATCH(100000,B:B,0),1)+(ROW()-MATCH(100000,B:B,0))</f>
         <v>100037</v>
       </c>
       <c r="D39">
@@ -10115,7 +10127,7 @@
         <v>100038</v>
       </c>
       <c r="B40">
-        <f>INDEX(B:B,MATCH(100000,B:B,0),1)+(ROW()-MATCH(100000,B:B,0))</f>
+        <f t="shared" si="4"/>
         <v>100038</v>
       </c>
       <c r="D40">
@@ -10146,7 +10158,7 @@
         <v>100039</v>
       </c>
       <c r="B41">
-        <f>INDEX(B:B,MATCH(100000,B:B,0),1)+(ROW()-MATCH(100000,B:B,0))</f>
+        <f t="shared" si="4"/>
         <v>100039</v>
       </c>
       <c r="D41">
@@ -10177,7 +10189,7 @@
         <v>100040</v>
       </c>
       <c r="B42">
-        <f>INDEX(B:B,MATCH(100000,B:B,0),1)+(ROW()-MATCH(100000,B:B,0))</f>
+        <f t="shared" si="4"/>
         <v>100040</v>
       </c>
       <c r="D42">
@@ -10208,7 +10220,7 @@
         <v>100041</v>
       </c>
       <c r="B43">
-        <f>INDEX(B:B,MATCH(100000,B:B,0),1)+(ROW()-MATCH(100000,B:B,0))</f>
+        <f t="shared" si="4"/>
         <v>100041</v>
       </c>
       <c r="D43">
@@ -10239,7 +10251,7 @@
         <v>100042</v>
       </c>
       <c r="B44">
-        <f>INDEX(B:B,MATCH(100000,B:B,0),1)+(ROW()-MATCH(100000,B:B,0))</f>
+        <f t="shared" si="4"/>
         <v>100042</v>
       </c>
       <c r="D44">
@@ -10270,7 +10282,7 @@
         <v>100043</v>
       </c>
       <c r="B45">
-        <f>INDEX(B:B,MATCH(100000,B:B,0),1)+(ROW()-MATCH(100000,B:B,0))</f>
+        <f t="shared" si="4"/>
         <v>100043</v>
       </c>
       <c r="D45">
@@ -10301,7 +10313,7 @@
         <v>100044</v>
       </c>
       <c r="B46">
-        <f>INDEX(B:B,MATCH(100000,B:B,0),1)+(ROW()-MATCH(100000,B:B,0))</f>
+        <f t="shared" si="4"/>
         <v>100044</v>
       </c>
       <c r="D46">
@@ -10332,7 +10344,7 @@
         <v>100045</v>
       </c>
       <c r="B47">
-        <f>INDEX(B:B,MATCH(100000,B:B,0),1)+(ROW()-MATCH(100000,B:B,0))</f>
+        <f t="shared" si="4"/>
         <v>100045</v>
       </c>
       <c r="D47">
@@ -10363,7 +10375,7 @@
         <v>100046</v>
       </c>
       <c r="B48">
-        <f>INDEX(B:B,MATCH(100000,B:B,0),1)+(ROW()-MATCH(100000,B:B,0))</f>
+        <f t="shared" si="4"/>
         <v>100046</v>
       </c>
       <c r="D48">
@@ -10394,7 +10406,7 @@
         <v>100047</v>
       </c>
       <c r="B49">
-        <f>INDEX(B:B,MATCH(100000,B:B,0),1)+(ROW()-MATCH(100000,B:B,0))</f>
+        <f t="shared" si="4"/>
         <v>100047</v>
       </c>
       <c r="D49">
@@ -10428,16 +10440,16 @@
         <v>100000</v>
       </c>
       <c r="C50" s="3" t="s">
-        <v>382</v>
+        <v>380</v>
       </c>
       <c r="D50" s="3">
         <v>0</v>
       </c>
       <c r="E50" s="3" t="s">
-        <v>383</v>
+        <v>381</v>
       </c>
       <c r="F50" s="3" t="s">
-        <v>371</v>
+        <v>369</v>
       </c>
       <c r="G50" s="3" t="s">
         <v>52</v>
@@ -10458,17 +10470,17 @@
         <v>100049</v>
       </c>
       <c r="B51">
-        <f>INDEX(B:B,MATCH(100000,B:B,0),1)+(ROW()-MATCH(100000,B:B,0))</f>
+        <f t="shared" ref="B51:B61" si="5">INDEX(B:B,MATCH(100000,B:B,0),1)+(ROW()-MATCH(100000,B:B,0))</f>
         <v>100049</v>
       </c>
       <c r="D51">
         <v>1</v>
       </c>
       <c r="E51" t="s">
-        <v>384</v>
+        <v>382</v>
       </c>
       <c r="F51" t="s">
-        <v>385</v>
+        <v>383</v>
       </c>
       <c r="G51" t="s">
         <v>85</v>
@@ -10489,20 +10501,20 @@
         <v>100050</v>
       </c>
       <c r="B52">
-        <f>INDEX(B:B,MATCH(100000,B:B,0),1)+(ROW()-MATCH(100000,B:B,0))</f>
+        <f t="shared" si="5"/>
         <v>100050</v>
       </c>
       <c r="D52">
         <v>2</v>
       </c>
       <c r="E52" t="s">
+        <v>370</v>
+      </c>
+      <c r="F52" t="s">
+        <v>371</v>
+      </c>
+      <c r="G52" t="s">
         <v>372</v>
-      </c>
-      <c r="F52" t="s">
-        <v>373</v>
-      </c>
-      <c r="G52" t="s">
-        <v>374</v>
       </c>
       <c r="H52" t="s">
         <v>22</v>
@@ -10520,7 +10532,7 @@
         <v>100051</v>
       </c>
       <c r="B53">
-        <f>INDEX(B:B,MATCH(100000,B:B,0),1)+(ROW()-MATCH(100000,B:B,0))</f>
+        <f t="shared" si="5"/>
         <v>100051</v>
       </c>
       <c r="D53">
@@ -10530,7 +10542,7 @@
         <v>27</v>
       </c>
       <c r="F53" t="s">
-        <v>375</v>
+        <v>373</v>
       </c>
       <c r="G53" t="s">
         <v>28</v>
@@ -10551,17 +10563,17 @@
         <v>100052</v>
       </c>
       <c r="B54">
-        <f>INDEX(B:B,MATCH(100000,B:B,0),1)+(ROW()-MATCH(100000,B:B,0))</f>
+        <f t="shared" si="5"/>
         <v>100052</v>
       </c>
       <c r="D54">
         <v>4</v>
       </c>
       <c r="E54" t="s">
-        <v>376</v>
+        <v>374</v>
       </c>
       <c r="F54" t="s">
-        <v>377</v>
+        <v>375</v>
       </c>
       <c r="G54" t="s">
         <v>42</v>
@@ -10582,7 +10594,7 @@
         <v>100053</v>
       </c>
       <c r="B55">
-        <f>INDEX(B:B,MATCH(100000,B:B,0),1)+(ROW()-MATCH(100000,B:B,0))</f>
+        <f t="shared" si="5"/>
         <v>100053</v>
       </c>
       <c r="D55">
@@ -10592,7 +10604,7 @@
         <v>44</v>
       </c>
       <c r="F55" t="s">
-        <v>358</v>
+        <v>356</v>
       </c>
       <c r="G55" t="s">
         <v>83</v>
@@ -10613,7 +10625,7 @@
         <v>100054</v>
       </c>
       <c r="B56">
-        <f>INDEX(B:B,MATCH(100000,B:B,0),1)+(ROW()-MATCH(100000,B:B,0))</f>
+        <f t="shared" si="5"/>
         <v>100054</v>
       </c>
       <c r="D56">
@@ -10644,7 +10656,7 @@
         <v>100055</v>
       </c>
       <c r="B57">
-        <f>INDEX(B:B,MATCH(100000,B:B,0),1)+(ROW()-MATCH(100000,B:B,0))</f>
+        <f t="shared" si="5"/>
         <v>100055</v>
       </c>
       <c r="D57">
@@ -10660,7 +10672,7 @@
         <v>80</v>
       </c>
       <c r="H57" t="s">
-        <v>359</v>
+        <v>357</v>
       </c>
       <c r="I57" t="s">
         <v>12</v>
@@ -10675,20 +10687,20 @@
         <v>100056</v>
       </c>
       <c r="B58">
-        <f>INDEX(B:B,MATCH(100000,B:B,0),1)+(ROW()-MATCH(100000,B:B,0))</f>
+        <f t="shared" si="5"/>
         <v>100056</v>
       </c>
       <c r="D58">
         <v>8</v>
       </c>
       <c r="E58" t="s">
-        <v>365</v>
+        <v>363</v>
       </c>
       <c r="F58" t="s">
-        <v>361</v>
+        <v>359</v>
       </c>
       <c r="G58" t="s">
-        <v>362</v>
+        <v>360</v>
       </c>
       <c r="H58" t="s">
         <v>38</v>
@@ -10706,23 +10718,23 @@
         <v>100057</v>
       </c>
       <c r="B59">
-        <f>INDEX(B:B,MATCH(100000,B:B,0),1)+(ROW()-MATCH(100000,B:B,0))</f>
+        <f t="shared" si="5"/>
         <v>100057</v>
       </c>
       <c r="D59">
         <v>9</v>
       </c>
       <c r="E59" t="s">
-        <v>363</v>
+        <v>361</v>
       </c>
       <c r="F59" t="s">
-        <v>378</v>
+        <v>376</v>
       </c>
       <c r="G59" t="s">
-        <v>379</v>
+        <v>377</v>
       </c>
       <c r="H59" t="s">
-        <v>343</v>
+        <v>341</v>
       </c>
       <c r="I59" t="s">
         <v>10</v>
@@ -10737,20 +10749,20 @@
         <v>100058</v>
       </c>
       <c r="B60">
-        <f>INDEX(B:B,MATCH(100000,B:B,0),1)+(ROW()-MATCH(100000,B:B,0))</f>
+        <f t="shared" si="5"/>
         <v>100058</v>
       </c>
       <c r="D60">
         <v>10</v>
       </c>
       <c r="E60" t="s">
+        <v>362</v>
+      </c>
+      <c r="F60" t="s">
         <v>364</v>
       </c>
-      <c r="F60" t="s">
-        <v>366</v>
-      </c>
       <c r="G60" t="s">
-        <v>367</v>
+        <v>365</v>
       </c>
       <c r="H60" t="s">
         <v>26</v>
@@ -10768,20 +10780,20 @@
         <v>100059</v>
       </c>
       <c r="B61">
-        <f>INDEX(B:B,MATCH(100000,B:B,0),1)+(ROW()-MATCH(100000,B:B,0))</f>
+        <f t="shared" si="5"/>
         <v>100059</v>
       </c>
       <c r="D61">
         <v>11</v>
       </c>
       <c r="E61" t="s">
-        <v>369</v>
+        <v>367</v>
       </c>
       <c r="F61" t="s">
+        <v>366</v>
+      </c>
+      <c r="G61" t="s">
         <v>368</v>
-      </c>
-      <c r="G61" t="s">
-        <v>370</v>
       </c>
       <c r="H61" t="s">
         <v>88</v>
@@ -11391,10 +11403,10 @@
         <v>23</v>
       </c>
       <c r="F20" t="s">
-        <v>332</v>
+        <v>330</v>
       </c>
       <c r="G20" t="s">
-        <v>333</v>
+        <v>331</v>
       </c>
       <c r="H20" t="s">
         <v>247</v>
@@ -11514,7 +11526,7 @@
         <v>270</v>
       </c>
       <c r="H24" t="s">
-        <v>331</v>
+        <v>329</v>
       </c>
       <c r="J24">
         <v>0</v>
@@ -11628,7 +11640,7 @@
         <v>279</v>
       </c>
       <c r="G28" t="s">
-        <v>334</v>
+        <v>332</v>
       </c>
       <c r="H28" t="s">
         <v>280</v>
@@ -11656,7 +11668,7 @@
         <v>278</v>
       </c>
       <c r="G29" t="s">
-        <v>335</v>
+        <v>333</v>
       </c>
       <c r="H29" t="s">
         <v>202</v>
@@ -11767,7 +11779,7 @@
         <v>3</v>
       </c>
       <c r="E33" t="s">
-        <v>309</v>
+        <v>307</v>
       </c>
       <c r="F33" t="s">
         <v>289</v>
@@ -11800,10 +11812,10 @@
         <v>208</v>
       </c>
       <c r="F34" s="3" t="s">
-        <v>316</v>
+        <v>314</v>
       </c>
       <c r="G34" s="3" t="s">
-        <v>317</v>
+        <v>315</v>
       </c>
       <c r="H34" s="3" t="s">
         <v>18</v>
@@ -11828,16 +11840,16 @@
         <v>1</v>
       </c>
       <c r="E35" t="s">
+        <v>310</v>
+      </c>
+      <c r="F35" t="s">
+        <v>311</v>
+      </c>
+      <c r="G35" t="s">
         <v>312</v>
       </c>
-      <c r="F35" t="s">
+      <c r="H35" t="s">
         <v>313</v>
-      </c>
-      <c r="G35" t="s">
-        <v>314</v>
-      </c>
-      <c r="H35" t="s">
-        <v>315</v>
       </c>
       <c r="J35">
         <v>0</v>
@@ -11859,10 +11871,10 @@
         <v>23</v>
       </c>
       <c r="F36" t="s">
-        <v>310</v>
+        <v>308</v>
       </c>
       <c r="G36" t="s">
-        <v>311</v>
+        <v>309</v>
       </c>
       <c r="H36" t="s">
         <v>261</v>
@@ -11887,10 +11899,10 @@
         <v>306</v>
       </c>
       <c r="F37" t="s">
-        <v>307</v>
+        <v>385</v>
       </c>
       <c r="G37" t="s">
-        <v>308</v>
+        <v>386</v>
       </c>
       <c r="H37" t="s">
         <v>202</v>
@@ -11917,13 +11929,13 @@
         <v>208</v>
       </c>
       <c r="F38" s="3" t="s">
-        <v>327</v>
+        <v>325</v>
       </c>
       <c r="G38" s="3" t="s">
-        <v>330</v>
+        <v>328</v>
       </c>
       <c r="H38" s="3" t="s">
-        <v>328</v>
+        <v>326</v>
       </c>
       <c r="I38" s="3" t="s">
         <v>220</v>
@@ -11945,16 +11957,16 @@
         <v>1</v>
       </c>
       <c r="E39" t="s">
+        <v>322</v>
+      </c>
+      <c r="F39" t="s">
+        <v>327</v>
+      </c>
+      <c r="G39" t="s">
+        <v>323</v>
+      </c>
+      <c r="H39" t="s">
         <v>324</v>
-      </c>
-      <c r="F39" t="s">
-        <v>329</v>
-      </c>
-      <c r="G39" t="s">
-        <v>325</v>
-      </c>
-      <c r="H39" t="s">
-        <v>326</v>
       </c>
       <c r="J39">
         <v>0</v>
@@ -11976,13 +11988,13 @@
         <v>23</v>
       </c>
       <c r="F40" t="s">
+        <v>318</v>
+      </c>
+      <c r="G40" t="s">
         <v>320</v>
       </c>
-      <c r="G40" t="s">
-        <v>322</v>
-      </c>
       <c r="H40" t="s">
-        <v>323</v>
+        <v>321</v>
       </c>
       <c r="J40">
         <v>0</v>
@@ -12001,13 +12013,13 @@
         <v>3</v>
       </c>
       <c r="E41" t="s">
-        <v>318</v>
+        <v>316</v>
       </c>
       <c r="F41" t="s">
+        <v>317</v>
+      </c>
+      <c r="G41" t="s">
         <v>319</v>
-      </c>
-      <c r="G41" t="s">
-        <v>321</v>
       </c>
       <c r="H41" t="s">
         <v>247</v>
